--- a/Part2_PlatformBenchmarks_Results_v1.0.0.xlsx
+++ b/Part2_PlatformBenchmarks_Results_v1.0.0.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="506">
   <si>
     <t xml:space="preserve">Arduino Benchmark Suite – Part 2: Platform Benchmarks</t>
   </si>
@@ -4074,7 +4074,9 @@
       <c r="OU4" s="5"/>
       <c r="OV4" s="5"/>
       <c r="OW4" s="5"/>
-      <c r="OX4" s="5"/>
+      <c r="OX4" s="5" t="n">
+        <v>5.41</v>
+      </c>
       <c r="OY4" s="5"/>
       <c r="OZ4" s="5"/>
       <c r="PA4" s="5"/>
@@ -4517,7 +4519,9 @@
       <c r="OU5" s="5"/>
       <c r="OV5" s="5"/>
       <c r="OW5" s="5"/>
-      <c r="OX5" s="5"/>
+      <c r="OX5" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="OY5" s="5"/>
       <c r="OZ5" s="5"/>
       <c r="PA5" s="5"/>
@@ -4960,7 +4964,9 @@
       <c r="OU6" s="5"/>
       <c r="OV6" s="5"/>
       <c r="OW6" s="5"/>
-      <c r="OX6" s="5"/>
+      <c r="OX6" s="5" t="n">
+        <v>7.05</v>
+      </c>
       <c r="OY6" s="5"/>
       <c r="OZ6" s="5"/>
       <c r="PA6" s="5"/>
@@ -5403,7 +5409,9 @@
       <c r="OU7" s="5"/>
       <c r="OV7" s="5"/>
       <c r="OW7" s="5"/>
-      <c r="OX7" s="5"/>
+      <c r="OX7" s="5" t="n">
+        <v>9.82</v>
+      </c>
       <c r="OY7" s="5"/>
       <c r="OZ7" s="5"/>
       <c r="PA7" s="5"/>
@@ -5846,7 +5854,9 @@
       <c r="OU8" s="5"/>
       <c r="OV8" s="5"/>
       <c r="OW8" s="5"/>
-      <c r="OX8" s="5"/>
+      <c r="OX8" s="5" t="n">
+        <v>9.36</v>
+      </c>
       <c r="OY8" s="5"/>
       <c r="OZ8" s="5"/>
       <c r="PA8" s="5"/>
@@ -6289,7 +6299,9 @@
       <c r="OU9" s="5"/>
       <c r="OV9" s="5"/>
       <c r="OW9" s="5"/>
-      <c r="OX9" s="5"/>
+      <c r="OX9" s="5" t="n">
+        <v>4.54</v>
+      </c>
       <c r="OY9" s="5"/>
       <c r="OZ9" s="5"/>
       <c r="PA9" s="5"/>
@@ -6732,7 +6744,9 @@
       <c r="OU10" s="5"/>
       <c r="OV10" s="5"/>
       <c r="OW10" s="5"/>
-      <c r="OX10" s="5"/>
+      <c r="OX10" s="5" t="n">
+        <v>7.96</v>
+      </c>
       <c r="OY10" s="5"/>
       <c r="OZ10" s="5"/>
       <c r="PA10" s="5"/>
@@ -7175,7 +7189,9 @@
       <c r="OU11" s="5"/>
       <c r="OV11" s="5"/>
       <c r="OW11" s="5"/>
-      <c r="OX11" s="5"/>
+      <c r="OX11" s="5" t="n">
+        <v>8.64</v>
+      </c>
       <c r="OY11" s="5"/>
       <c r="OZ11" s="5"/>
       <c r="PA11" s="5"/>
@@ -7618,7 +7634,9 @@
       <c r="OU12" s="5"/>
       <c r="OV12" s="5"/>
       <c r="OW12" s="5"/>
-      <c r="OX12" s="5"/>
+      <c r="OX12" s="5" t="n">
+        <v>7.9</v>
+      </c>
       <c r="OY12" s="5"/>
       <c r="OZ12" s="5"/>
       <c r="PA12" s="5"/>
@@ -8061,7 +8079,9 @@
       <c r="OU13" s="5"/>
       <c r="OV13" s="5"/>
       <c r="OW13" s="5"/>
-      <c r="OX13" s="5"/>
+      <c r="OX13" s="5" t="n">
+        <v>9.41</v>
+      </c>
       <c r="OY13" s="5"/>
       <c r="OZ13" s="5"/>
       <c r="PA13" s="5"/>
@@ -8504,7 +8524,9 @@
       <c r="OU14" s="5"/>
       <c r="OV14" s="5"/>
       <c r="OW14" s="5"/>
-      <c r="OX14" s="5"/>
+      <c r="OX14" s="5" t="n">
+        <v>55.39</v>
+      </c>
       <c r="OY14" s="5"/>
       <c r="OZ14" s="5"/>
       <c r="PA14" s="5"/>
@@ -8947,7 +8969,9 @@
       <c r="OU15" s="5"/>
       <c r="OV15" s="5"/>
       <c r="OW15" s="5"/>
-      <c r="OX15" s="5"/>
+      <c r="OX15" s="5" t="n">
+        <v>17.58</v>
+      </c>
       <c r="OY15" s="5"/>
       <c r="OZ15" s="5"/>
       <c r="PA15" s="5"/>
@@ -9390,7 +9414,9 @@
       <c r="OU16" s="5"/>
       <c r="OV16" s="5"/>
       <c r="OW16" s="5"/>
-      <c r="OX16" s="5"/>
+      <c r="OX16" s="5" t="n">
+        <v>11.52</v>
+      </c>
       <c r="OY16" s="5"/>
       <c r="OZ16" s="5"/>
       <c r="PA16" s="5"/>
@@ -9833,7 +9859,9 @@
       <c r="OU17" s="5"/>
       <c r="OV17" s="5"/>
       <c r="OW17" s="5"/>
-      <c r="OX17" s="5"/>
+      <c r="OX17" s="5" t="n">
+        <v>65.52</v>
+      </c>
       <c r="OY17" s="5"/>
       <c r="OZ17" s="5"/>
       <c r="PA17" s="5"/>
@@ -10276,7 +10304,9 @@
       <c r="OU18" s="5"/>
       <c r="OV18" s="5"/>
       <c r="OW18" s="5"/>
-      <c r="OX18" s="5"/>
+      <c r="OX18" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="OY18" s="5"/>
       <c r="OZ18" s="5"/>
       <c r="PA18" s="5"/>
@@ -10719,7 +10749,9 @@
       <c r="OU19" s="5"/>
       <c r="OV19" s="5"/>
       <c r="OW19" s="5"/>
-      <c r="OX19" s="5"/>
+      <c r="OX19" s="5" t="n">
+        <v>8</v>
+      </c>
       <c r="OY19" s="5"/>
       <c r="OZ19" s="5"/>
       <c r="PA19" s="5"/>
@@ -11162,7 +11194,9 @@
       <c r="OU20" s="5"/>
       <c r="OV20" s="5"/>
       <c r="OW20" s="5"/>
-      <c r="OX20" s="5"/>
+      <c r="OX20" s="5" t="n">
+        <v>46</v>
+      </c>
       <c r="OY20" s="5"/>
       <c r="OZ20" s="5"/>
       <c r="PA20" s="5"/>
@@ -11605,7 +11639,9 @@
       <c r="OU21" s="5"/>
       <c r="OV21" s="5"/>
       <c r="OW21" s="5"/>
-      <c r="OX21" s="5"/>
+      <c r="OX21" s="5" t="n">
+        <v>0.003</v>
+      </c>
       <c r="OY21" s="5"/>
       <c r="OZ21" s="5"/>
       <c r="PA21" s="5"/>
@@ -12048,7 +12084,9 @@
       <c r="OU22" s="5"/>
       <c r="OV22" s="5"/>
       <c r="OW22" s="5"/>
-      <c r="OX22" s="5"/>
+      <c r="OX22" s="5" t="n">
+        <v>0.5</v>
+      </c>
       <c r="OY22" s="5"/>
       <c r="OZ22" s="5"/>
       <c r="PA22" s="5"/>
@@ -12491,7 +12529,9 @@
       <c r="OU23" s="5"/>
       <c r="OV23" s="5"/>
       <c r="OW23" s="5"/>
-      <c r="OX23" s="5"/>
+      <c r="OX23" s="5" t="n">
+        <v>344</v>
+      </c>
       <c r="OY23" s="5"/>
       <c r="OZ23" s="5"/>
       <c r="PA23" s="5"/>
@@ -12934,7 +12974,9 @@
       <c r="OU24" s="5"/>
       <c r="OV24" s="5"/>
       <c r="OW24" s="5"/>
-      <c r="OX24" s="5"/>
+      <c r="OX24" s="5" t="n">
+        <v>43</v>
+      </c>
       <c r="OY24" s="5"/>
       <c r="OZ24" s="5"/>
       <c r="PA24" s="5"/>
@@ -13377,7 +13419,9 @@
       <c r="OU25" s="5"/>
       <c r="OV25" s="5"/>
       <c r="OW25" s="5"/>
-      <c r="OX25" s="5"/>
+      <c r="OX25" s="5" t="n">
+        <v>2.67</v>
+      </c>
       <c r="OY25" s="5"/>
       <c r="OZ25" s="5"/>
       <c r="PA25" s="5"/>
@@ -13820,7 +13864,9 @@
       <c r="OU26" s="5"/>
       <c r="OV26" s="5"/>
       <c r="OW26" s="5"/>
-      <c r="OX26" s="5"/>
+      <c r="OX26" s="5" t="n">
+        <v>0.04</v>
+      </c>
       <c r="OY26" s="5"/>
       <c r="OZ26" s="5"/>
       <c r="PA26" s="5"/>
@@ -14263,7 +14309,9 @@
       <c r="OU27" s="5"/>
       <c r="OV27" s="5"/>
       <c r="OW27" s="5"/>
-      <c r="OX27" s="5"/>
+      <c r="OX27" s="5" t="n">
+        <v>0.04</v>
+      </c>
       <c r="OY27" s="5"/>
       <c r="OZ27" s="5"/>
       <c r="PA27" s="5"/>
@@ -14706,7 +14754,9 @@
       <c r="OU28" s="5"/>
       <c r="OV28" s="5"/>
       <c r="OW28" s="5"/>
-      <c r="OX28" s="5"/>
+      <c r="OX28" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="OY28" s="5"/>
       <c r="OZ28" s="5"/>
       <c r="PA28" s="5"/>
@@ -15149,7 +15199,9 @@
       <c r="OU29" s="5"/>
       <c r="OV29" s="5"/>
       <c r="OW29" s="5"/>
-      <c r="OX29" s="5"/>
+      <c r="OX29" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="OY29" s="5"/>
       <c r="OZ29" s="5"/>
       <c r="PA29" s="5"/>
@@ -15592,7 +15644,9 @@
       <c r="OU30" s="5"/>
       <c r="OV30" s="5"/>
       <c r="OW30" s="5"/>
-      <c r="OX30" s="5"/>
+      <c r="OX30" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="OY30" s="5"/>
       <c r="OZ30" s="5"/>
       <c r="PA30" s="5"/>
@@ -16035,7 +16089,9 @@
       <c r="OU31" s="5"/>
       <c r="OV31" s="5"/>
       <c r="OW31" s="5"/>
-      <c r="OX31" s="5"/>
+      <c r="OX31" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="OY31" s="5"/>
       <c r="OZ31" s="5"/>
       <c r="PA31" s="5"/>
@@ -16478,7 +16534,9 @@
       <c r="OU32" s="5"/>
       <c r="OV32" s="5"/>
       <c r="OW32" s="5"/>
-      <c r="OX32" s="5"/>
+      <c r="OX32" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="OY32" s="5"/>
       <c r="OZ32" s="5"/>
       <c r="PA32" s="5"/>
@@ -16921,7 +16979,9 @@
       <c r="OU33" s="5"/>
       <c r="OV33" s="5"/>
       <c r="OW33" s="5"/>
-      <c r="OX33" s="5"/>
+      <c r="OX33" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="OY33" s="5"/>
       <c r="OZ33" s="5"/>
       <c r="PA33" s="5"/>
@@ -17364,7 +17424,9 @@
       <c r="OU34" s="5"/>
       <c r="OV34" s="5"/>
       <c r="OW34" s="5"/>
-      <c r="OX34" s="5"/>
+      <c r="OX34" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="OY34" s="5"/>
       <c r="OZ34" s="5"/>
       <c r="PA34" s="5"/>
@@ -17807,7 +17869,9 @@
       <c r="OU35" s="5"/>
       <c r="OV35" s="5"/>
       <c r="OW35" s="5"/>
-      <c r="OX35" s="5"/>
+      <c r="OX35" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="OY35" s="5"/>
       <c r="OZ35" s="5"/>
       <c r="PA35" s="5"/>
@@ -18250,7 +18314,9 @@
       <c r="OU36" s="5"/>
       <c r="OV36" s="5"/>
       <c r="OW36" s="5"/>
-      <c r="OX36" s="5"/>
+      <c r="OX36" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="OY36" s="5"/>
       <c r="OZ36" s="5"/>
       <c r="PA36" s="5"/>
@@ -18693,7 +18759,9 @@
       <c r="OU37" s="5"/>
       <c r="OV37" s="5"/>
       <c r="OW37" s="5"/>
-      <c r="OX37" s="5"/>
+      <c r="OX37" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="OY37" s="5"/>
       <c r="OZ37" s="5"/>
       <c r="PA37" s="5"/>
@@ -19136,7 +19204,9 @@
       <c r="OU38" s="5"/>
       <c r="OV38" s="5"/>
       <c r="OW38" s="5"/>
-      <c r="OX38" s="5"/>
+      <c r="OX38" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="OY38" s="5"/>
       <c r="OZ38" s="5"/>
       <c r="PA38" s="5"/>
@@ -19579,7 +19649,9 @@
       <c r="OU39" s="5"/>
       <c r="OV39" s="5"/>
       <c r="OW39" s="5"/>
-      <c r="OX39" s="5"/>
+      <c r="OX39" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="OY39" s="5"/>
       <c r="OZ39" s="5"/>
       <c r="PA39" s="5"/>
@@ -20022,7 +20094,9 @@
       <c r="OU40" s="5"/>
       <c r="OV40" s="5"/>
       <c r="OW40" s="5"/>
-      <c r="OX40" s="5"/>
+      <c r="OX40" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="OY40" s="5"/>
       <c r="OZ40" s="5"/>
       <c r="PA40" s="5"/>
@@ -20465,7 +20539,9 @@
       <c r="OU41" s="5"/>
       <c r="OV41" s="5"/>
       <c r="OW41" s="5"/>
-      <c r="OX41" s="5"/>
+      <c r="OX41" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="OY41" s="5"/>
       <c r="OZ41" s="5"/>
       <c r="PA41" s="5"/>
@@ -20908,7 +20984,9 @@
       <c r="OU42" s="5"/>
       <c r="OV42" s="5"/>
       <c r="OW42" s="5"/>
-      <c r="OX42" s="5"/>
+      <c r="OX42" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="OY42" s="5"/>
       <c r="OZ42" s="5"/>
       <c r="PA42" s="5"/>
@@ -21351,7 +21429,9 @@
       <c r="OU43" s="5"/>
       <c r="OV43" s="5"/>
       <c r="OW43" s="5"/>
-      <c r="OX43" s="5"/>
+      <c r="OX43" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="OY43" s="5"/>
       <c r="OZ43" s="5"/>
       <c r="PA43" s="5"/>
@@ -21794,7 +21874,9 @@
       <c r="OU44" s="5"/>
       <c r="OV44" s="5"/>
       <c r="OW44" s="5"/>
-      <c r="OX44" s="5"/>
+      <c r="OX44" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="OY44" s="5"/>
       <c r="OZ44" s="5"/>
       <c r="PA44" s="5"/>
@@ -22237,7 +22319,9 @@
       <c r="OU45" s="5"/>
       <c r="OV45" s="5"/>
       <c r="OW45" s="5"/>
-      <c r="OX45" s="5"/>
+      <c r="OX45" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="OY45" s="5"/>
       <c r="OZ45" s="5"/>
       <c r="PA45" s="5"/>
@@ -22680,7 +22764,9 @@
       <c r="OU46" s="5"/>
       <c r="OV46" s="5"/>
       <c r="OW46" s="5"/>
-      <c r="OX46" s="5"/>
+      <c r="OX46" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="OY46" s="5"/>
       <c r="OZ46" s="5"/>
       <c r="PA46" s="5"/>
@@ -23123,7 +23209,9 @@
       <c r="OU47" s="5"/>
       <c r="OV47" s="5"/>
       <c r="OW47" s="5"/>
-      <c r="OX47" s="5"/>
+      <c r="OX47" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="OY47" s="5"/>
       <c r="OZ47" s="5"/>
       <c r="PA47" s="5"/>
@@ -23566,7 +23654,9 @@
       <c r="OU48" s="5"/>
       <c r="OV48" s="5"/>
       <c r="OW48" s="5"/>
-      <c r="OX48" s="5"/>
+      <c r="OX48" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="OY48" s="5"/>
       <c r="OZ48" s="5"/>
       <c r="PA48" s="5"/>
@@ -24009,7 +24099,9 @@
       <c r="OU49" s="5"/>
       <c r="OV49" s="5"/>
       <c r="OW49" s="5"/>
-      <c r="OX49" s="5"/>
+      <c r="OX49" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="OY49" s="5"/>
       <c r="OZ49" s="5"/>
       <c r="PA49" s="5"/>
@@ -24452,7 +24544,9 @@
       <c r="OU50" s="5"/>
       <c r="OV50" s="5"/>
       <c r="OW50" s="5"/>
-      <c r="OX50" s="5"/>
+      <c r="OX50" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="OY50" s="5"/>
       <c r="OZ50" s="5"/>
       <c r="PA50" s="5"/>
@@ -24895,7 +24989,9 @@
       <c r="OU51" s="5"/>
       <c r="OV51" s="5"/>
       <c r="OW51" s="5"/>
-      <c r="OX51" s="5"/>
+      <c r="OX51" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="OY51" s="5"/>
       <c r="OZ51" s="5"/>
       <c r="PA51" s="5"/>
@@ -25338,7 +25434,9 @@
       <c r="OU52" s="5"/>
       <c r="OV52" s="5"/>
       <c r="OW52" s="5"/>
-      <c r="OX52" s="5"/>
+      <c r="OX52" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="OY52" s="5"/>
       <c r="OZ52" s="5"/>
       <c r="PA52" s="5"/>
@@ -25781,7 +25879,9 @@
       <c r="OU53" s="5"/>
       <c r="OV53" s="5"/>
       <c r="OW53" s="5"/>
-      <c r="OX53" s="5"/>
+      <c r="OX53" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="OY53" s="5"/>
       <c r="OZ53" s="5"/>
       <c r="PA53" s="5"/>
@@ -26224,7 +26324,9 @@
       <c r="OU54" s="5"/>
       <c r="OV54" s="5"/>
       <c r="OW54" s="5"/>
-      <c r="OX54" s="5"/>
+      <c r="OX54" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="OY54" s="5"/>
       <c r="OZ54" s="5"/>
       <c r="PA54" s="5"/>
@@ -26667,7 +26769,9 @@
       <c r="OU55" s="5"/>
       <c r="OV55" s="5"/>
       <c r="OW55" s="5"/>
-      <c r="OX55" s="5"/>
+      <c r="OX55" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="OY55" s="5"/>
       <c r="OZ55" s="5"/>
       <c r="PA55" s="5"/>
@@ -27110,7 +27214,9 @@
       <c r="OU56" s="5"/>
       <c r="OV56" s="5"/>
       <c r="OW56" s="5"/>
-      <c r="OX56" s="5"/>
+      <c r="OX56" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="OY56" s="5"/>
       <c r="OZ56" s="5"/>
       <c r="PA56" s="5"/>
@@ -27553,7 +27659,9 @@
       <c r="OU57" s="5"/>
       <c r="OV57" s="5"/>
       <c r="OW57" s="5"/>
-      <c r="OX57" s="5"/>
+      <c r="OX57" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="OY57" s="5"/>
       <c r="OZ57" s="5"/>
       <c r="PA57" s="5"/>
@@ -27996,7 +28104,9 @@
       <c r="OU58" s="5"/>
       <c r="OV58" s="5"/>
       <c r="OW58" s="5"/>
-      <c r="OX58" s="5"/>
+      <c r="OX58" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="OY58" s="5"/>
       <c r="OZ58" s="5"/>
       <c r="PA58" s="5"/>
@@ -28439,7 +28549,9 @@
       <c r="OU59" s="5"/>
       <c r="OV59" s="5"/>
       <c r="OW59" s="5"/>
-      <c r="OX59" s="5"/>
+      <c r="OX59" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="OY59" s="5"/>
       <c r="OZ59" s="5"/>
       <c r="PA59" s="5"/>
@@ -28882,7 +28994,9 @@
       <c r="OU60" s="5"/>
       <c r="OV60" s="5"/>
       <c r="OW60" s="5"/>
-      <c r="OX60" s="5"/>
+      <c r="OX60" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="OY60" s="5"/>
       <c r="OZ60" s="5"/>
       <c r="PA60" s="5"/>
@@ -29325,7 +29439,9 @@
       <c r="OU61" s="5"/>
       <c r="OV61" s="5"/>
       <c r="OW61" s="5"/>
-      <c r="OX61" s="5"/>
+      <c r="OX61" s="5" t="n">
+        <v>992</v>
+      </c>
       <c r="OY61" s="5"/>
       <c r="OZ61" s="5"/>
       <c r="PA61" s="5"/>
@@ -29768,7 +29884,9 @@
       <c r="OU62" s="5"/>
       <c r="OV62" s="5"/>
       <c r="OW62" s="5"/>
-      <c r="OX62" s="5"/>
+      <c r="OX62" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="OY62" s="5"/>
       <c r="OZ62" s="5"/>
       <c r="PA62" s="5"/>
@@ -30211,7 +30329,9 @@
       <c r="OU63" s="5"/>
       <c r="OV63" s="5"/>
       <c r="OW63" s="5"/>
-      <c r="OX63" s="5"/>
+      <c r="OX63" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="OY63" s="5"/>
       <c r="OZ63" s="5"/>
       <c r="PA63" s="5"/>

--- a/Part2_PlatformBenchmarks_Results_v1.0.0.xlsx
+++ b/Part2_PlatformBenchmarks_Results_v1.0.0.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="508">
   <si>
     <t xml:space="preserve">Arduino Benchmark Suite – Part 2: Platform Benchmarks</t>
   </si>
@@ -265,6 +265,9 @@
     <t xml:space="preserve">ESP32-S3-DevKitM-1</t>
   </si>
   <si>
+    <t xml:space="preserve">ESP32-C3-Dev-Module</t>
+  </si>
+  <si>
     <t xml:space="preserve">ESP32-C3-DevKitM-1</t>
   </si>
   <si>
@@ -1423,10 +1426,10 @@
     <t xml:space="preserve">EC signing (ops/sec)</t>
   </si>
   <si>
-    <t xml:space="preserve">SHA1 String (ops/ms)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SHA1 Buffer (ops/ms)</t>
+    <t xml:space="preserve">Hex encode (ops/ms)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHA1 (ops/ms)</t>
   </si>
   <si>
     <t xml:space="preserve">MD5 (ops/ms)</t>
@@ -1436,6 +1439,9 @@
   </si>
   <si>
     <t xml:space="preserve">SHA512 (ops/ms)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PBKDF2-HMAC-SHA256 (ops/ms)</t>
   </si>
   <si>
     <t xml:space="preserve">Hardware AES Encrypt (ops/ms)</t>
@@ -1931,13 +1937,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:PI63"/>
+  <dimension ref="A1:PJ64"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="38.02"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="9.87"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="425" min="4" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="426" min="4" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2368,6 +2374,7 @@
       <c r="PG1" s="2"/>
       <c r="PH1" s="2"/>
       <c r="PI1" s="2"/>
+      <c r="PJ1" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
@@ -3645,13 +3652,16 @@
       <c r="PI3" s="3" t="s">
         <v>425</v>
       </c>
+      <c r="PJ3" s="3" t="s">
+        <v>426</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>3.45</v>
@@ -3741,7 +3751,9 @@
       <c r="BZ4" s="5"/>
       <c r="CA4" s="5"/>
       <c r="CB4" s="5"/>
-      <c r="CC4" s="5"/>
+      <c r="CC4" s="5" t="n">
+        <v>21.55</v>
+      </c>
       <c r="CD4" s="5"/>
       <c r="CE4" s="5"/>
       <c r="CF4" s="5"/>
@@ -4074,35 +4086,36 @@
       <c r="OU4" s="5"/>
       <c r="OV4" s="5"/>
       <c r="OW4" s="5"/>
-      <c r="OX4" s="5" t="n">
+      <c r="OX4" s="5"/>
+      <c r="OY4" s="5" t="n">
         <v>5.41</v>
       </c>
-      <c r="OY4" s="5"/>
       <c r="OZ4" s="5"/>
       <c r="PA4" s="5"/>
       <c r="PB4" s="5"/>
       <c r="PC4" s="5"/>
       <c r="PD4" s="5"/>
       <c r="PE4" s="5"/>
-      <c r="PF4" s="5" t="n">
+      <c r="PF4" s="5"/>
+      <c r="PG4" s="5" t="n">
         <v>3.45</v>
       </c>
-      <c r="PG4" s="5"/>
       <c r="PH4" s="5"/>
       <c r="PI4" s="5"/>
+      <c r="PJ4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5" t="n">
@@ -4111,7 +4124,7 @@
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
       <c r="I5" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
@@ -4141,7 +4154,7 @@
       <c r="AI5" s="5"/>
       <c r="AJ5" s="5"/>
       <c r="AK5" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL5" s="5"/>
       <c r="AM5" s="5"/>
@@ -4186,7 +4199,9 @@
       <c r="BZ5" s="5"/>
       <c r="CA5" s="5"/>
       <c r="CB5" s="5"/>
-      <c r="CC5" s="5"/>
+      <c r="CC5" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="CD5" s="5"/>
       <c r="CE5" s="5"/>
       <c r="CF5" s="5"/>
@@ -4519,29 +4534,30 @@
       <c r="OU5" s="5"/>
       <c r="OV5" s="5"/>
       <c r="OW5" s="5"/>
-      <c r="OX5" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="OY5" s="5"/>
+      <c r="OX5" s="5"/>
+      <c r="OY5" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OZ5" s="5"/>
       <c r="PA5" s="5"/>
       <c r="PB5" s="5"/>
       <c r="PC5" s="5"/>
       <c r="PD5" s="5"/>
       <c r="PE5" s="5"/>
-      <c r="PF5" s="5" t="n">
+      <c r="PF5" s="5"/>
+      <c r="PG5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="PG5" s="5"/>
       <c r="PH5" s="5"/>
       <c r="PI5" s="5"/>
+      <c r="PJ5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>4.48</v>
@@ -4556,7 +4572,7 @@
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
@@ -4631,7 +4647,9 @@
       <c r="BZ6" s="5"/>
       <c r="CA6" s="5"/>
       <c r="CB6" s="5"/>
-      <c r="CC6" s="5"/>
+      <c r="CC6" s="5" t="n">
+        <v>46.99</v>
+      </c>
       <c r="CD6" s="5"/>
       <c r="CE6" s="5"/>
       <c r="CF6" s="5"/>
@@ -4964,29 +4982,30 @@
       <c r="OU6" s="5"/>
       <c r="OV6" s="5"/>
       <c r="OW6" s="5"/>
-      <c r="OX6" s="5" t="n">
+      <c r="OX6" s="5"/>
+      <c r="OY6" s="5" t="n">
         <v>7.05</v>
       </c>
-      <c r="OY6" s="5"/>
       <c r="OZ6" s="5"/>
       <c r="PA6" s="5"/>
       <c r="PB6" s="5"/>
       <c r="PC6" s="5"/>
       <c r="PD6" s="5"/>
       <c r="PE6" s="5"/>
-      <c r="PF6" s="5" t="n">
+      <c r="PF6" s="5"/>
+      <c r="PG6" s="5" t="n">
         <v>4.48</v>
       </c>
-      <c r="PG6" s="5"/>
       <c r="PH6" s="5"/>
       <c r="PI6" s="5"/>
+      <c r="PJ6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C7" s="5" t="n">
         <v>6.24</v>
@@ -5001,7 +5020,7 @@
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
       <c r="I7" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
@@ -5076,7 +5095,9 @@
       <c r="BZ7" s="5"/>
       <c r="CA7" s="5"/>
       <c r="CB7" s="5"/>
-      <c r="CC7" s="5"/>
+      <c r="CC7" s="5" t="n">
+        <v>49.26</v>
+      </c>
       <c r="CD7" s="5"/>
       <c r="CE7" s="5"/>
       <c r="CF7" s="5"/>
@@ -5409,29 +5430,30 @@
       <c r="OU7" s="5"/>
       <c r="OV7" s="5"/>
       <c r="OW7" s="5"/>
-      <c r="OX7" s="5" t="n">
+      <c r="OX7" s="5"/>
+      <c r="OY7" s="5" t="n">
         <v>9.82</v>
       </c>
-      <c r="OY7" s="5"/>
       <c r="OZ7" s="5"/>
       <c r="PA7" s="5"/>
       <c r="PB7" s="5"/>
       <c r="PC7" s="5"/>
       <c r="PD7" s="5"/>
       <c r="PE7" s="5"/>
-      <c r="PF7" s="5" t="n">
+      <c r="PF7" s="5"/>
+      <c r="PG7" s="5" t="n">
         <v>6.24</v>
       </c>
-      <c r="PG7" s="5"/>
       <c r="PH7" s="5"/>
       <c r="PI7" s="5"/>
+      <c r="PJ7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>5.94</v>
@@ -5446,7 +5468,7 @@
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
       <c r="I8" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
@@ -5521,7 +5543,9 @@
       <c r="BZ8" s="5"/>
       <c r="CA8" s="5"/>
       <c r="CB8" s="5"/>
-      <c r="CC8" s="5"/>
+      <c r="CC8" s="5" t="n">
+        <v>43.82</v>
+      </c>
       <c r="CD8" s="5"/>
       <c r="CE8" s="5"/>
       <c r="CF8" s="5"/>
@@ -5854,29 +5878,30 @@
       <c r="OU8" s="5"/>
       <c r="OV8" s="5"/>
       <c r="OW8" s="5"/>
-      <c r="OX8" s="5" t="n">
+      <c r="OX8" s="5"/>
+      <c r="OY8" s="5" t="n">
         <v>9.36</v>
       </c>
-      <c r="OY8" s="5"/>
       <c r="OZ8" s="5"/>
       <c r="PA8" s="5"/>
       <c r="PB8" s="5"/>
       <c r="PC8" s="5"/>
       <c r="PD8" s="5"/>
       <c r="PE8" s="5"/>
-      <c r="PF8" s="5" t="n">
+      <c r="PF8" s="5"/>
+      <c r="PG8" s="5" t="n">
         <v>5.94</v>
       </c>
-      <c r="PG8" s="5"/>
       <c r="PH8" s="5"/>
       <c r="PI8" s="5"/>
+      <c r="PJ8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C9" s="5" t="n">
         <v>2.89</v>
@@ -5891,7 +5916,7 @@
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
       <c r="I9" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
@@ -5966,7 +5991,9 @@
       <c r="BZ9" s="5"/>
       <c r="CA9" s="5"/>
       <c r="CB9" s="5"/>
-      <c r="CC9" s="5"/>
+      <c r="CC9" s="5" t="n">
+        <v>15.08</v>
+      </c>
       <c r="CD9" s="5"/>
       <c r="CE9" s="5"/>
       <c r="CF9" s="5"/>
@@ -6299,29 +6326,30 @@
       <c r="OU9" s="5"/>
       <c r="OV9" s="5"/>
       <c r="OW9" s="5"/>
-      <c r="OX9" s="5" t="n">
+      <c r="OX9" s="5"/>
+      <c r="OY9" s="5" t="n">
         <v>4.54</v>
       </c>
-      <c r="OY9" s="5"/>
       <c r="OZ9" s="5"/>
       <c r="PA9" s="5"/>
       <c r="PB9" s="5"/>
       <c r="PC9" s="5"/>
       <c r="PD9" s="5"/>
       <c r="PE9" s="5"/>
-      <c r="PF9" s="5" t="n">
+      <c r="PF9" s="5"/>
+      <c r="PG9" s="5" t="n">
         <v>2.89</v>
       </c>
-      <c r="PG9" s="5"/>
       <c r="PH9" s="5"/>
       <c r="PI9" s="5"/>
+      <c r="PJ9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C10" s="5" t="n">
         <v>5.08</v>
@@ -6336,7 +6364,7 @@
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
       <c r="I10" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
@@ -6411,7 +6439,9 @@
       <c r="BZ10" s="5"/>
       <c r="CA10" s="5"/>
       <c r="CB10" s="5"/>
-      <c r="CC10" s="5"/>
+      <c r="CC10" s="5" t="n">
+        <v>41.88</v>
+      </c>
       <c r="CD10" s="5"/>
       <c r="CE10" s="5"/>
       <c r="CF10" s="5"/>
@@ -6744,29 +6774,30 @@
       <c r="OU10" s="5"/>
       <c r="OV10" s="5"/>
       <c r="OW10" s="5"/>
-      <c r="OX10" s="5" t="n">
+      <c r="OX10" s="5"/>
+      <c r="OY10" s="5" t="n">
         <v>7.96</v>
       </c>
-      <c r="OY10" s="5"/>
       <c r="OZ10" s="5"/>
       <c r="PA10" s="5"/>
       <c r="PB10" s="5"/>
       <c r="PC10" s="5"/>
       <c r="PD10" s="5"/>
       <c r="PE10" s="5"/>
-      <c r="PF10" s="5" t="n">
+      <c r="PF10" s="5"/>
+      <c r="PG10" s="5" t="n">
         <v>5.08</v>
       </c>
-      <c r="PG10" s="5"/>
       <c r="PH10" s="5"/>
       <c r="PI10" s="5"/>
+      <c r="PJ10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>5.52</v>
@@ -6781,7 +6812,7 @@
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
       <c r="I11" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
@@ -6856,7 +6887,9 @@
       <c r="BZ11" s="5"/>
       <c r="CA11" s="5"/>
       <c r="CB11" s="5"/>
-      <c r="CC11" s="5"/>
+      <c r="CC11" s="5" t="n">
+        <v>36.89</v>
+      </c>
       <c r="CD11" s="5"/>
       <c r="CE11" s="5"/>
       <c r="CF11" s="5"/>
@@ -7189,29 +7222,30 @@
       <c r="OU11" s="5"/>
       <c r="OV11" s="5"/>
       <c r="OW11" s="5"/>
-      <c r="OX11" s="5" t="n">
+      <c r="OX11" s="5"/>
+      <c r="OY11" s="5" t="n">
         <v>8.64</v>
       </c>
-      <c r="OY11" s="5"/>
       <c r="OZ11" s="5"/>
       <c r="PA11" s="5"/>
       <c r="PB11" s="5"/>
       <c r="PC11" s="5"/>
       <c r="PD11" s="5"/>
       <c r="PE11" s="5"/>
-      <c r="PF11" s="5" t="n">
+      <c r="PF11" s="5"/>
+      <c r="PG11" s="5" t="n">
         <v>5.52</v>
       </c>
-      <c r="PG11" s="5"/>
       <c r="PH11" s="5"/>
       <c r="PI11" s="5"/>
+      <c r="PJ11" s="5"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C12" s="5" t="n">
         <v>5.06</v>
@@ -7226,7 +7260,7 @@
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
       <c r="I12" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J12" s="5"/>
       <c r="K12" s="5"/>
@@ -7301,7 +7335,9 @@
       <c r="BZ12" s="5"/>
       <c r="CA12" s="5"/>
       <c r="CB12" s="5"/>
-      <c r="CC12" s="5"/>
+      <c r="CC12" s="5" t="n">
+        <v>38.04</v>
+      </c>
       <c r="CD12" s="5"/>
       <c r="CE12" s="5"/>
       <c r="CF12" s="5"/>
@@ -7634,29 +7670,30 @@
       <c r="OU12" s="5"/>
       <c r="OV12" s="5"/>
       <c r="OW12" s="5"/>
-      <c r="OX12" s="5" t="n">
+      <c r="OX12" s="5"/>
+      <c r="OY12" s="5" t="n">
         <v>7.9</v>
       </c>
-      <c r="OY12" s="5"/>
       <c r="OZ12" s="5"/>
       <c r="PA12" s="5"/>
       <c r="PB12" s="5"/>
       <c r="PC12" s="5"/>
       <c r="PD12" s="5"/>
       <c r="PE12" s="5"/>
-      <c r="PF12" s="5" t="n">
+      <c r="PF12" s="5"/>
+      <c r="PG12" s="5" t="n">
         <v>5.06</v>
       </c>
-      <c r="PG12" s="5"/>
       <c r="PH12" s="5"/>
       <c r="PI12" s="5"/>
+      <c r="PJ12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C13" s="5" t="n">
         <v>5.99</v>
@@ -7671,7 +7708,7 @@
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
@@ -7746,7 +7783,9 @@
       <c r="BZ13" s="5"/>
       <c r="CA13" s="5"/>
       <c r="CB13" s="5"/>
-      <c r="CC13" s="5"/>
+      <c r="CC13" s="5" t="n">
+        <v>35.4</v>
+      </c>
       <c r="CD13" s="5"/>
       <c r="CE13" s="5"/>
       <c r="CF13" s="5"/>
@@ -8079,29 +8118,30 @@
       <c r="OU13" s="5"/>
       <c r="OV13" s="5"/>
       <c r="OW13" s="5"/>
-      <c r="OX13" s="5" t="n">
+      <c r="OX13" s="5"/>
+      <c r="OY13" s="5" t="n">
         <v>9.41</v>
       </c>
-      <c r="OY13" s="5"/>
       <c r="OZ13" s="5"/>
       <c r="PA13" s="5"/>
       <c r="PB13" s="5"/>
       <c r="PC13" s="5"/>
       <c r="PD13" s="5"/>
       <c r="PE13" s="5"/>
-      <c r="PF13" s="5" t="n">
+      <c r="PF13" s="5"/>
+      <c r="PG13" s="5" t="n">
         <v>5.99</v>
       </c>
-      <c r="PG13" s="5"/>
       <c r="PH13" s="5"/>
       <c r="PI13" s="5"/>
+      <c r="PJ13" s="5"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>35.47</v>
@@ -8116,7 +8156,7 @@
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
       <c r="I14" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
@@ -8191,7 +8231,9 @@
       <c r="BZ14" s="5"/>
       <c r="CA14" s="5"/>
       <c r="CB14" s="5"/>
-      <c r="CC14" s="5"/>
+      <c r="CC14" s="5" t="n">
+        <v>408.5</v>
+      </c>
       <c r="CD14" s="5"/>
       <c r="CE14" s="5"/>
       <c r="CF14" s="5"/>
@@ -8524,29 +8566,30 @@
       <c r="OU14" s="5"/>
       <c r="OV14" s="5"/>
       <c r="OW14" s="5"/>
-      <c r="OX14" s="5" t="n">
+      <c r="OX14" s="5"/>
+      <c r="OY14" s="5" t="n">
         <v>55.39</v>
       </c>
-      <c r="OY14" s="5"/>
       <c r="OZ14" s="5"/>
       <c r="PA14" s="5"/>
       <c r="PB14" s="5"/>
       <c r="PC14" s="5"/>
       <c r="PD14" s="5"/>
       <c r="PE14" s="5"/>
-      <c r="PF14" s="5" t="n">
+      <c r="PF14" s="5"/>
+      <c r="PG14" s="5" t="n">
         <v>35.47</v>
       </c>
-      <c r="PG14" s="5"/>
       <c r="PH14" s="5"/>
       <c r="PI14" s="5"/>
+      <c r="PJ14" s="5"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C15" s="5" t="n">
         <v>17.76</v>
@@ -8636,7 +8679,9 @@
       <c r="BZ15" s="5"/>
       <c r="CA15" s="5"/>
       <c r="CB15" s="5"/>
-      <c r="CC15" s="5"/>
+      <c r="CC15" s="5" t="n">
+        <v>204.96</v>
+      </c>
       <c r="CD15" s="5"/>
       <c r="CE15" s="5"/>
       <c r="CF15" s="5"/>
@@ -8969,29 +9014,30 @@
       <c r="OU15" s="5"/>
       <c r="OV15" s="5"/>
       <c r="OW15" s="5"/>
-      <c r="OX15" s="5" t="n">
+      <c r="OX15" s="5"/>
+      <c r="OY15" s="5" t="n">
         <v>17.58</v>
       </c>
-      <c r="OY15" s="5"/>
       <c r="OZ15" s="5"/>
       <c r="PA15" s="5"/>
       <c r="PB15" s="5"/>
       <c r="PC15" s="5"/>
       <c r="PD15" s="5"/>
       <c r="PE15" s="5"/>
-      <c r="PF15" s="5" t="n">
+      <c r="PF15" s="5"/>
+      <c r="PG15" s="5" t="n">
         <v>17.76</v>
       </c>
-      <c r="PG15" s="5"/>
       <c r="PH15" s="5"/>
       <c r="PI15" s="5"/>
+      <c r="PJ15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C16" s="5" t="n">
         <v>11.52</v>
@@ -9081,7 +9127,9 @@
       <c r="BZ16" s="5"/>
       <c r="CA16" s="5"/>
       <c r="CB16" s="5"/>
-      <c r="CC16" s="5"/>
+      <c r="CC16" s="5" t="n">
+        <v>11.52</v>
+      </c>
       <c r="CD16" s="5"/>
       <c r="CE16" s="5"/>
       <c r="CF16" s="5"/>
@@ -9414,29 +9462,30 @@
       <c r="OU16" s="5"/>
       <c r="OV16" s="5"/>
       <c r="OW16" s="5"/>
-      <c r="OX16" s="5" t="n">
+      <c r="OX16" s="5"/>
+      <c r="OY16" s="5" t="n">
         <v>11.52</v>
       </c>
-      <c r="OY16" s="5"/>
       <c r="OZ16" s="5"/>
       <c r="PA16" s="5"/>
       <c r="PB16" s="5"/>
       <c r="PC16" s="5"/>
       <c r="PD16" s="5"/>
       <c r="PE16" s="5"/>
-      <c r="PF16" s="5" t="n">
+      <c r="PF16" s="5"/>
+      <c r="PG16" s="5" t="n">
         <v>11.52</v>
       </c>
-      <c r="PG16" s="5"/>
       <c r="PH16" s="5"/>
       <c r="PI16" s="5"/>
+      <c r="PJ16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C17" s="5" t="n">
         <v>64.85</v>
@@ -9526,7 +9575,9 @@
       <c r="BZ17" s="5"/>
       <c r="CA17" s="5"/>
       <c r="CB17" s="5"/>
-      <c r="CC17" s="5"/>
+      <c r="CC17" s="5" t="n">
+        <v>5.62</v>
+      </c>
       <c r="CD17" s="5"/>
       <c r="CE17" s="5"/>
       <c r="CF17" s="5"/>
@@ -9859,29 +9910,30 @@
       <c r="OU17" s="5"/>
       <c r="OV17" s="5"/>
       <c r="OW17" s="5"/>
-      <c r="OX17" s="5" t="n">
+      <c r="OX17" s="5"/>
+      <c r="OY17" s="5" t="n">
         <v>65.52</v>
       </c>
-      <c r="OY17" s="5"/>
       <c r="OZ17" s="5"/>
       <c r="PA17" s="5"/>
       <c r="PB17" s="5"/>
       <c r="PC17" s="5"/>
       <c r="PD17" s="5"/>
       <c r="PE17" s="5"/>
-      <c r="PF17" s="5" t="n">
+      <c r="PF17" s="5"/>
+      <c r="PG17" s="5" t="n">
         <v>64.85</v>
       </c>
-      <c r="PG17" s="5"/>
       <c r="PH17" s="5"/>
       <c r="PI17" s="5"/>
+      <c r="PJ17" s="5"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C18" s="5" t="n">
         <v>0</v>
@@ -9971,7 +10023,9 @@
       <c r="BZ18" s="5"/>
       <c r="CA18" s="5"/>
       <c r="CB18" s="5"/>
-      <c r="CC18" s="5"/>
+      <c r="CC18" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="CD18" s="5"/>
       <c r="CE18" s="5"/>
       <c r="CF18" s="5"/>
@@ -10304,29 +10358,30 @@
       <c r="OU18" s="5"/>
       <c r="OV18" s="5"/>
       <c r="OW18" s="5"/>
-      <c r="OX18" s="5" t="n">
+      <c r="OX18" s="5"/>
+      <c r="OY18" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="OY18" s="5"/>
       <c r="OZ18" s="5"/>
       <c r="PA18" s="5"/>
       <c r="PB18" s="5"/>
       <c r="PC18" s="5"/>
       <c r="PD18" s="5"/>
       <c r="PE18" s="5"/>
-      <c r="PF18" s="5" t="n">
+      <c r="PF18" s="5"/>
+      <c r="PG18" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="PG18" s="5"/>
       <c r="PH18" s="5"/>
       <c r="PI18" s="5"/>
+      <c r="PJ18" s="5"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C19" s="5" t="n">
         <v>4</v>
@@ -10416,7 +10471,9 @@
       <c r="BZ19" s="5"/>
       <c r="CA19" s="5"/>
       <c r="CB19" s="5"/>
-      <c r="CC19" s="5"/>
+      <c r="CC19" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="CD19" s="5"/>
       <c r="CE19" s="5"/>
       <c r="CF19" s="5"/>
@@ -10749,29 +10806,30 @@
       <c r="OU19" s="5"/>
       <c r="OV19" s="5"/>
       <c r="OW19" s="5"/>
-      <c r="OX19" s="5" t="n">
+      <c r="OX19" s="5"/>
+      <c r="OY19" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="OY19" s="5"/>
       <c r="OZ19" s="5"/>
       <c r="PA19" s="5"/>
       <c r="PB19" s="5"/>
       <c r="PC19" s="5"/>
       <c r="PD19" s="5"/>
       <c r="PE19" s="5"/>
-      <c r="PF19" s="5" t="n">
+      <c r="PF19" s="5"/>
+      <c r="PG19" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="PG19" s="5"/>
       <c r="PH19" s="5"/>
       <c r="PI19" s="5"/>
+      <c r="PJ19" s="5"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C20" s="5" t="n">
         <v>108</v>
@@ -10861,7 +10919,9 @@
       <c r="BZ20" s="5"/>
       <c r="CA20" s="5"/>
       <c r="CB20" s="5"/>
-      <c r="CC20" s="5"/>
+      <c r="CC20" s="5" t="n">
+        <v>9</v>
+      </c>
       <c r="CD20" s="5"/>
       <c r="CE20" s="5"/>
       <c r="CF20" s="5"/>
@@ -11194,29 +11254,30 @@
       <c r="OU20" s="5"/>
       <c r="OV20" s="5"/>
       <c r="OW20" s="5"/>
-      <c r="OX20" s="5" t="n">
+      <c r="OX20" s="5"/>
+      <c r="OY20" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="OY20" s="5"/>
       <c r="OZ20" s="5"/>
       <c r="PA20" s="5"/>
       <c r="PB20" s="5"/>
       <c r="PC20" s="5"/>
       <c r="PD20" s="5"/>
       <c r="PE20" s="5"/>
-      <c r="PF20" s="5" t="n">
+      <c r="PF20" s="5"/>
+      <c r="PG20" s="5" t="n">
         <v>108</v>
       </c>
-      <c r="PG20" s="5"/>
       <c r="PH20" s="5"/>
       <c r="PI20" s="5"/>
+      <c r="PJ20" s="5"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C21" s="5" t="n">
         <v>0</v>
@@ -11306,7 +11367,9 @@
       <c r="BZ21" s="5"/>
       <c r="CA21" s="5"/>
       <c r="CB21" s="5"/>
-      <c r="CC21" s="5"/>
+      <c r="CC21" s="5" t="n">
+        <v>0.007</v>
+      </c>
       <c r="CD21" s="5"/>
       <c r="CE21" s="5"/>
       <c r="CF21" s="5"/>
@@ -11639,29 +11702,30 @@
       <c r="OU21" s="5"/>
       <c r="OV21" s="5"/>
       <c r="OW21" s="5"/>
-      <c r="OX21" s="5" t="n">
+      <c r="OX21" s="5"/>
+      <c r="OY21" s="5" t="n">
         <v>0.003</v>
       </c>
-      <c r="OY21" s="5"/>
       <c r="OZ21" s="5"/>
       <c r="PA21" s="5"/>
       <c r="PB21" s="5"/>
       <c r="PC21" s="5"/>
       <c r="PD21" s="5"/>
       <c r="PE21" s="5"/>
-      <c r="PF21" s="5" t="n">
+      <c r="PF21" s="5"/>
+      <c r="PG21" s="5" t="n">
         <v>0.003</v>
       </c>
-      <c r="PG21" s="5"/>
       <c r="PH21" s="5"/>
       <c r="PI21" s="5"/>
+      <c r="PJ21" s="5"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C22" s="5" t="n">
         <v>1.6</v>
@@ -11751,7 +11815,9 @@
       <c r="BZ22" s="5"/>
       <c r="CA22" s="5"/>
       <c r="CB22" s="5"/>
-      <c r="CC22" s="5"/>
+      <c r="CC22" s="5" t="n">
+        <v>0.4</v>
+      </c>
       <c r="CD22" s="5"/>
       <c r="CE22" s="5"/>
       <c r="CF22" s="5"/>
@@ -12084,29 +12150,30 @@
       <c r="OU22" s="5"/>
       <c r="OV22" s="5"/>
       <c r="OW22" s="5"/>
-      <c r="OX22" s="5" t="n">
+      <c r="OX22" s="5"/>
+      <c r="OY22" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="OY22" s="5"/>
       <c r="OZ22" s="5"/>
       <c r="PA22" s="5"/>
       <c r="PB22" s="5"/>
       <c r="PC22" s="5"/>
       <c r="PD22" s="5"/>
       <c r="PE22" s="5"/>
-      <c r="PF22" s="5" t="n">
+      <c r="PF22" s="5"/>
+      <c r="PG22" s="5" t="n">
         <v>1.7</v>
       </c>
-      <c r="PG22" s="5"/>
       <c r="PH22" s="5"/>
       <c r="PI22" s="5"/>
+      <c r="PJ22" s="5"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C23" s="5" t="n">
         <v>14</v>
@@ -12196,7 +12263,9 @@
       <c r="BZ23" s="5"/>
       <c r="CA23" s="5"/>
       <c r="CB23" s="5"/>
-      <c r="CC23" s="5"/>
+      <c r="CC23" s="5" t="n">
+        <v>81</v>
+      </c>
       <c r="CD23" s="5"/>
       <c r="CE23" s="5"/>
       <c r="CF23" s="5"/>
@@ -12529,29 +12598,30 @@
       <c r="OU23" s="5"/>
       <c r="OV23" s="5"/>
       <c r="OW23" s="5"/>
-      <c r="OX23" s="5" t="n">
+      <c r="OX23" s="5"/>
+      <c r="OY23" s="5" t="n">
         <v>344</v>
       </c>
-      <c r="OY23" s="5"/>
       <c r="OZ23" s="5"/>
       <c r="PA23" s="5"/>
       <c r="PB23" s="5"/>
       <c r="PC23" s="5"/>
       <c r="PD23" s="5"/>
       <c r="PE23" s="5"/>
-      <c r="PF23" s="5" t="n">
+      <c r="PF23" s="5"/>
+      <c r="PG23" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="PG23" s="5"/>
       <c r="PH23" s="5"/>
       <c r="PI23" s="5"/>
+      <c r="PJ23" s="5"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C24" s="5" t="n">
         <v>45</v>
@@ -12641,7 +12711,9 @@
       <c r="BZ24" s="5"/>
       <c r="CA24" s="5"/>
       <c r="CB24" s="5"/>
-      <c r="CC24" s="5"/>
+      <c r="CC24" s="5" t="n">
+        <v>64</v>
+      </c>
       <c r="CD24" s="5"/>
       <c r="CE24" s="5"/>
       <c r="CF24" s="5"/>
@@ -12974,29 +13046,30 @@
       <c r="OU24" s="5"/>
       <c r="OV24" s="5"/>
       <c r="OW24" s="5"/>
-      <c r="OX24" s="5" t="n">
+      <c r="OX24" s="5"/>
+      <c r="OY24" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="OY24" s="5"/>
       <c r="OZ24" s="5"/>
       <c r="PA24" s="5"/>
       <c r="PB24" s="5"/>
       <c r="PC24" s="5"/>
       <c r="PD24" s="5"/>
       <c r="PE24" s="5"/>
-      <c r="PF24" s="5" t="n">
+      <c r="PF24" s="5"/>
+      <c r="PG24" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="PG24" s="5"/>
       <c r="PH24" s="5"/>
       <c r="PI24" s="5"/>
+      <c r="PJ24" s="5"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C25" s="5" t="n">
         <v>5.67</v>
@@ -13086,7 +13159,9 @@
       <c r="BZ25" s="5"/>
       <c r="CA25" s="5"/>
       <c r="CB25" s="5"/>
-      <c r="CC25" s="5"/>
+      <c r="CC25" s="5" t="n">
+        <v>0.26</v>
+      </c>
       <c r="CD25" s="5"/>
       <c r="CE25" s="5"/>
       <c r="CF25" s="5"/>
@@ -13419,29 +13494,30 @@
       <c r="OU25" s="5"/>
       <c r="OV25" s="5"/>
       <c r="OW25" s="5"/>
-      <c r="OX25" s="5" t="n">
+      <c r="OX25" s="5"/>
+      <c r="OY25" s="5" t="n">
         <v>2.67</v>
       </c>
-      <c r="OY25" s="5"/>
       <c r="OZ25" s="5"/>
       <c r="PA25" s="5"/>
       <c r="PB25" s="5"/>
       <c r="PC25" s="5"/>
       <c r="PD25" s="5"/>
       <c r="PE25" s="5"/>
-      <c r="PF25" s="5" t="n">
+      <c r="PF25" s="5"/>
+      <c r="PG25" s="5" t="n">
         <v>5.67</v>
       </c>
-      <c r="PG25" s="5"/>
       <c r="PH25" s="5"/>
       <c r="PI25" s="5"/>
+      <c r="PJ25" s="5"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C26" s="5" t="n">
         <v>7.39</v>
@@ -13456,7 +13532,7 @@
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
       <c r="I26" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
@@ -13531,7 +13607,9 @@
       <c r="BZ26" s="5"/>
       <c r="CA26" s="5"/>
       <c r="CB26" s="5"/>
-      <c r="CC26" s="5"/>
+      <c r="CC26" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="CD26" s="5"/>
       <c r="CE26" s="5"/>
       <c r="CF26" s="5"/>
@@ -13864,29 +13942,30 @@
       <c r="OU26" s="5"/>
       <c r="OV26" s="5"/>
       <c r="OW26" s="5"/>
-      <c r="OX26" s="5" t="n">
+      <c r="OX26" s="5"/>
+      <c r="OY26" s="5" t="n">
         <v>0.04</v>
       </c>
-      <c r="OY26" s="5"/>
       <c r="OZ26" s="5"/>
       <c r="PA26" s="5"/>
       <c r="PB26" s="5"/>
       <c r="PC26" s="5"/>
       <c r="PD26" s="5"/>
       <c r="PE26" s="5"/>
-      <c r="PF26" s="5" t="n">
+      <c r="PF26" s="5"/>
+      <c r="PG26" s="5" t="n">
         <v>7.39</v>
       </c>
-      <c r="PG26" s="5"/>
       <c r="PH26" s="5"/>
       <c r="PI26" s="5"/>
+      <c r="PJ26" s="5"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C27" s="5" t="n">
         <v>17.41</v>
@@ -13901,7 +13980,7 @@
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
       <c r="I27" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
@@ -13976,7 +14055,9 @@
       <c r="BZ27" s="5"/>
       <c r="CA27" s="5"/>
       <c r="CB27" s="5"/>
-      <c r="CC27" s="5"/>
+      <c r="CC27" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="CD27" s="5"/>
       <c r="CE27" s="5"/>
       <c r="CF27" s="5"/>
@@ -14309,44 +14390,45 @@
       <c r="OU27" s="5"/>
       <c r="OV27" s="5"/>
       <c r="OW27" s="5"/>
-      <c r="OX27" s="5" t="n">
+      <c r="OX27" s="5"/>
+      <c r="OY27" s="5" t="n">
         <v>0.04</v>
       </c>
-      <c r="OY27" s="5"/>
       <c r="OZ27" s="5"/>
       <c r="PA27" s="5"/>
       <c r="PB27" s="5"/>
       <c r="PC27" s="5"/>
       <c r="PD27" s="5"/>
       <c r="PE27" s="5"/>
-      <c r="PF27" s="5" t="n">
+      <c r="PF27" s="5"/>
+      <c r="PG27" s="5" t="n">
         <v>17.49</v>
       </c>
-      <c r="PG27" s="5"/>
       <c r="PH27" s="5"/>
       <c r="PI27" s="5"/>
+      <c r="PJ27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D28" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
       <c r="I28" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
@@ -14376,7 +14458,7 @@
       <c r="AI28" s="5"/>
       <c r="AJ28" s="5"/>
       <c r="AK28" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL28" s="5"/>
       <c r="AM28" s="5"/>
@@ -14421,7 +14503,9 @@
       <c r="BZ28" s="5"/>
       <c r="CA28" s="5"/>
       <c r="CB28" s="5"/>
-      <c r="CC28" s="5"/>
+      <c r="CC28" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="CD28" s="5"/>
       <c r="CE28" s="5"/>
       <c r="CF28" s="5"/>
@@ -14754,44 +14838,45 @@
       <c r="OU28" s="5"/>
       <c r="OV28" s="5"/>
       <c r="OW28" s="5"/>
-      <c r="OX28" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="OY28" s="5"/>
+      <c r="OX28" s="5"/>
+      <c r="OY28" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OZ28" s="5"/>
       <c r="PA28" s="5"/>
       <c r="PB28" s="5"/>
       <c r="PC28" s="5"/>
       <c r="PD28" s="5"/>
       <c r="PE28" s="5"/>
-      <c r="PF28" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="PG28" s="5"/>
+      <c r="PF28" s="5"/>
+      <c r="PG28" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PH28" s="5"/>
       <c r="PI28" s="5"/>
+      <c r="PJ28" s="5"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E29" s="5"/>
       <c r="F29" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
       <c r="I29" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
@@ -14821,7 +14906,7 @@
       <c r="AI29" s="5"/>
       <c r="AJ29" s="5"/>
       <c r="AK29" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL29" s="5"/>
       <c r="AM29" s="5"/>
@@ -14866,7 +14951,9 @@
       <c r="BZ29" s="5"/>
       <c r="CA29" s="5"/>
       <c r="CB29" s="5"/>
-      <c r="CC29" s="5"/>
+      <c r="CC29" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="CD29" s="5"/>
       <c r="CE29" s="5"/>
       <c r="CF29" s="5"/>
@@ -15199,44 +15286,45 @@
       <c r="OU29" s="5"/>
       <c r="OV29" s="5"/>
       <c r="OW29" s="5"/>
-      <c r="OX29" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="OY29" s="5"/>
+      <c r="OX29" s="5"/>
+      <c r="OY29" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OZ29" s="5"/>
       <c r="PA29" s="5"/>
       <c r="PB29" s="5"/>
       <c r="PC29" s="5"/>
       <c r="PD29" s="5"/>
       <c r="PE29" s="5"/>
-      <c r="PF29" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="PG29" s="5"/>
+      <c r="PF29" s="5"/>
+      <c r="PG29" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PH29" s="5"/>
       <c r="PI29" s="5"/>
+      <c r="PJ29" s="5"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D30" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E30" s="5"/>
       <c r="F30" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
       <c r="I30" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J30" s="5"/>
       <c r="K30" s="5"/>
@@ -15266,7 +15354,7 @@
       <c r="AI30" s="5"/>
       <c r="AJ30" s="5"/>
       <c r="AK30" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL30" s="5"/>
       <c r="AM30" s="5"/>
@@ -15311,7 +15399,9 @@
       <c r="BZ30" s="5"/>
       <c r="CA30" s="5"/>
       <c r="CB30" s="5"/>
-      <c r="CC30" s="5"/>
+      <c r="CC30" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="CD30" s="5"/>
       <c r="CE30" s="5"/>
       <c r="CF30" s="5"/>
@@ -15644,44 +15734,45 @@
       <c r="OU30" s="5"/>
       <c r="OV30" s="5"/>
       <c r="OW30" s="5"/>
-      <c r="OX30" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="OY30" s="5"/>
+      <c r="OX30" s="5"/>
+      <c r="OY30" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OZ30" s="5"/>
       <c r="PA30" s="5"/>
       <c r="PB30" s="5"/>
       <c r="PC30" s="5"/>
       <c r="PD30" s="5"/>
       <c r="PE30" s="5"/>
-      <c r="PF30" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="PG30" s="5"/>
+      <c r="PF30" s="5"/>
+      <c r="PG30" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PH30" s="5"/>
       <c r="PI30" s="5"/>
+      <c r="PJ30" s="5"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="B31" s="5" t="s">
         <v>461</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>460</v>
-      </c>
       <c r="C31" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D31" s="5" t="n">
         <v>5068.28</v>
       </c>
       <c r="E31" s="5"/>
       <c r="F31" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
       <c r="I31" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J31" s="5"/>
       <c r="K31" s="5"/>
@@ -15711,7 +15802,7 @@
       <c r="AI31" s="5"/>
       <c r="AJ31" s="5"/>
       <c r="AK31" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL31" s="5"/>
       <c r="AM31" s="5"/>
@@ -15756,7 +15847,9 @@
       <c r="BZ31" s="5"/>
       <c r="CA31" s="5"/>
       <c r="CB31" s="5"/>
-      <c r="CC31" s="5"/>
+      <c r="CC31" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="CD31" s="5"/>
       <c r="CE31" s="5"/>
       <c r="CF31" s="5"/>
@@ -16089,44 +16182,45 @@
       <c r="OU31" s="5"/>
       <c r="OV31" s="5"/>
       <c r="OW31" s="5"/>
-      <c r="OX31" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="OY31" s="5"/>
+      <c r="OX31" s="5"/>
+      <c r="OY31" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OZ31" s="5"/>
       <c r="PA31" s="5"/>
       <c r="PB31" s="5"/>
       <c r="PC31" s="5"/>
       <c r="PD31" s="5"/>
       <c r="PE31" s="5"/>
-      <c r="PF31" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="PG31" s="5"/>
+      <c r="PF31" s="5"/>
+      <c r="PG31" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PH31" s="5"/>
       <c r="PI31" s="5"/>
+      <c r="PJ31" s="5"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D32" s="5" t="n">
         <v>5.155</v>
       </c>
       <c r="E32" s="5"/>
       <c r="F32" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
       <c r="I32" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J32" s="5"/>
       <c r="K32" s="5"/>
@@ -16156,7 +16250,7 @@
       <c r="AI32" s="5"/>
       <c r="AJ32" s="5"/>
       <c r="AK32" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL32" s="5"/>
       <c r="AM32" s="5"/>
@@ -16201,7 +16295,9 @@
       <c r="BZ32" s="5"/>
       <c r="CA32" s="5"/>
       <c r="CB32" s="5"/>
-      <c r="CC32" s="5"/>
+      <c r="CC32" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="CD32" s="5"/>
       <c r="CE32" s="5"/>
       <c r="CF32" s="5"/>
@@ -16534,44 +16630,45 @@
       <c r="OU32" s="5"/>
       <c r="OV32" s="5"/>
       <c r="OW32" s="5"/>
-      <c r="OX32" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="OY32" s="5"/>
+      <c r="OX32" s="5"/>
+      <c r="OY32" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OZ32" s="5"/>
       <c r="PA32" s="5"/>
       <c r="PB32" s="5"/>
       <c r="PC32" s="5"/>
       <c r="PD32" s="5"/>
       <c r="PE32" s="5"/>
-      <c r="PF32" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="PG32" s="5"/>
+      <c r="PF32" s="5"/>
+      <c r="PG32" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PH32" s="5"/>
       <c r="PI32" s="5"/>
+      <c r="PJ32" s="5"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D33" s="5" t="n">
         <v>128000000</v>
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
       <c r="I33" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
@@ -16601,7 +16698,7 @@
       <c r="AI33" s="5"/>
       <c r="AJ33" s="5"/>
       <c r="AK33" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL33" s="5"/>
       <c r="AM33" s="5"/>
@@ -16646,7 +16743,9 @@
       <c r="BZ33" s="5"/>
       <c r="CA33" s="5"/>
       <c r="CB33" s="5"/>
-      <c r="CC33" s="5"/>
+      <c r="CC33" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="CD33" s="5"/>
       <c r="CE33" s="5"/>
       <c r="CF33" s="5"/>
@@ -16979,44 +17078,45 @@
       <c r="OU33" s="5"/>
       <c r="OV33" s="5"/>
       <c r="OW33" s="5"/>
-      <c r="OX33" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="OY33" s="5"/>
+      <c r="OX33" s="5"/>
+      <c r="OY33" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OZ33" s="5"/>
       <c r="PA33" s="5"/>
       <c r="PB33" s="5"/>
       <c r="PC33" s="5"/>
       <c r="PD33" s="5"/>
       <c r="PE33" s="5"/>
-      <c r="PF33" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="PG33" s="5"/>
+      <c r="PF33" s="5"/>
+      <c r="PG33" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PH33" s="5"/>
       <c r="PI33" s="5"/>
+      <c r="PJ33" s="5"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D34" s="5" t="n">
         <v>5.16</v>
       </c>
       <c r="E34" s="5"/>
       <c r="F34" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
       <c r="I34" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J34" s="5"/>
       <c r="K34" s="5"/>
@@ -17046,7 +17146,7 @@
       <c r="AI34" s="5"/>
       <c r="AJ34" s="5"/>
       <c r="AK34" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL34" s="5"/>
       <c r="AM34" s="5"/>
@@ -17091,7 +17191,9 @@
       <c r="BZ34" s="5"/>
       <c r="CA34" s="5"/>
       <c r="CB34" s="5"/>
-      <c r="CC34" s="5"/>
+      <c r="CC34" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="CD34" s="5"/>
       <c r="CE34" s="5"/>
       <c r="CF34" s="5"/>
@@ -17424,44 +17526,45 @@
       <c r="OU34" s="5"/>
       <c r="OV34" s="5"/>
       <c r="OW34" s="5"/>
-      <c r="OX34" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="OY34" s="5"/>
+      <c r="OX34" s="5"/>
+      <c r="OY34" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OZ34" s="5"/>
       <c r="PA34" s="5"/>
       <c r="PB34" s="5"/>
       <c r="PC34" s="5"/>
       <c r="PD34" s="5"/>
       <c r="PE34" s="5"/>
-      <c r="PF34" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="PG34" s="5"/>
+      <c r="PF34" s="5"/>
+      <c r="PG34" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PH34" s="5"/>
       <c r="PI34" s="5"/>
+      <c r="PJ34" s="5"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E35" s="5"/>
       <c r="F35" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
       <c r="I35" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J35" s="5"/>
       <c r="K35" s="5"/>
@@ -17491,7 +17594,7 @@
       <c r="AI35" s="5"/>
       <c r="AJ35" s="5"/>
       <c r="AK35" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL35" s="5"/>
       <c r="AM35" s="5"/>
@@ -17536,7 +17639,9 @@
       <c r="BZ35" s="5"/>
       <c r="CA35" s="5"/>
       <c r="CB35" s="5"/>
-      <c r="CC35" s="5"/>
+      <c r="CC35" s="5" t="n">
+        <v>2.02</v>
+      </c>
       <c r="CD35" s="5"/>
       <c r="CE35" s="5"/>
       <c r="CF35" s="5"/>
@@ -17869,44 +17974,45 @@
       <c r="OU35" s="5"/>
       <c r="OV35" s="5"/>
       <c r="OW35" s="5"/>
-      <c r="OX35" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="OY35" s="5"/>
+      <c r="OX35" s="5"/>
+      <c r="OY35" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OZ35" s="5"/>
       <c r="PA35" s="5"/>
       <c r="PB35" s="5"/>
       <c r="PC35" s="5"/>
       <c r="PD35" s="5"/>
       <c r="PE35" s="5"/>
-      <c r="PF35" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="PG35" s="5"/>
+      <c r="PF35" s="5"/>
+      <c r="PG35" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PH35" s="5"/>
       <c r="PI35" s="5"/>
+      <c r="PJ35" s="5"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E36" s="5"/>
       <c r="F36" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
       <c r="I36" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J36" s="5"/>
       <c r="K36" s="5"/>
@@ -17936,7 +18042,7 @@
       <c r="AI36" s="5"/>
       <c r="AJ36" s="5"/>
       <c r="AK36" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL36" s="5"/>
       <c r="AM36" s="5"/>
@@ -17981,7 +18087,9 @@
       <c r="BZ36" s="5"/>
       <c r="CA36" s="5"/>
       <c r="CB36" s="5"/>
-      <c r="CC36" s="5"/>
+      <c r="CC36" s="5" t="n">
+        <v>30.1</v>
+      </c>
       <c r="CD36" s="5"/>
       <c r="CE36" s="5"/>
       <c r="CF36" s="5"/>
@@ -18314,44 +18422,45 @@
       <c r="OU36" s="5"/>
       <c r="OV36" s="5"/>
       <c r="OW36" s="5"/>
-      <c r="OX36" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="OY36" s="5"/>
+      <c r="OX36" s="5"/>
+      <c r="OY36" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OZ36" s="5"/>
       <c r="PA36" s="5"/>
       <c r="PB36" s="5"/>
       <c r="PC36" s="5"/>
       <c r="PD36" s="5"/>
       <c r="PE36" s="5"/>
-      <c r="PF36" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="PG36" s="5"/>
+      <c r="PF36" s="5"/>
+      <c r="PG36" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PH36" s="5"/>
       <c r="PI36" s="5"/>
+      <c r="PJ36" s="5"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E37" s="5"/>
       <c r="F37" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
       <c r="I37" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
@@ -18381,7 +18490,7 @@
       <c r="AI37" s="5"/>
       <c r="AJ37" s="5"/>
       <c r="AK37" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL37" s="5"/>
       <c r="AM37" s="5"/>
@@ -18426,7 +18535,9 @@
       <c r="BZ37" s="5"/>
       <c r="CA37" s="5"/>
       <c r="CB37" s="5"/>
-      <c r="CC37" s="5"/>
+      <c r="CC37" s="5" t="n">
+        <v>39.86</v>
+      </c>
       <c r="CD37" s="5"/>
       <c r="CE37" s="5"/>
       <c r="CF37" s="5"/>
@@ -18759,44 +18870,45 @@
       <c r="OU37" s="5"/>
       <c r="OV37" s="5"/>
       <c r="OW37" s="5"/>
-      <c r="OX37" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="OY37" s="5"/>
+      <c r="OX37" s="5"/>
+      <c r="OY37" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OZ37" s="5"/>
       <c r="PA37" s="5"/>
       <c r="PB37" s="5"/>
       <c r="PC37" s="5"/>
       <c r="PD37" s="5"/>
       <c r="PE37" s="5"/>
-      <c r="PF37" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="PG37" s="5"/>
+      <c r="PF37" s="5"/>
+      <c r="PG37" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PH37" s="5"/>
       <c r="PI37" s="5"/>
+      <c r="PJ37" s="5"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E38" s="5"/>
       <c r="F38" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
       <c r="I38" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J38" s="5"/>
       <c r="K38" s="5"/>
@@ -18826,7 +18938,7 @@
       <c r="AI38" s="5"/>
       <c r="AJ38" s="5"/>
       <c r="AK38" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL38" s="5"/>
       <c r="AM38" s="5"/>
@@ -18871,7 +18983,9 @@
       <c r="BZ38" s="5"/>
       <c r="CA38" s="5"/>
       <c r="CB38" s="5"/>
-      <c r="CC38" s="5"/>
+      <c r="CC38" s="5" t="n">
+        <v>28.87</v>
+      </c>
       <c r="CD38" s="5"/>
       <c r="CE38" s="5"/>
       <c r="CF38" s="5"/>
@@ -19204,44 +19318,45 @@
       <c r="OU38" s="5"/>
       <c r="OV38" s="5"/>
       <c r="OW38" s="5"/>
-      <c r="OX38" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="OY38" s="5"/>
+      <c r="OX38" s="5"/>
+      <c r="OY38" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OZ38" s="5"/>
       <c r="PA38" s="5"/>
       <c r="PB38" s="5"/>
       <c r="PC38" s="5"/>
       <c r="PD38" s="5"/>
       <c r="PE38" s="5"/>
-      <c r="PF38" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="PG38" s="5"/>
+      <c r="PF38" s="5"/>
+      <c r="PG38" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PH38" s="5"/>
       <c r="PI38" s="5"/>
+      <c r="PJ38" s="5"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E39" s="5"/>
       <c r="F39" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
       <c r="I39" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J39" s="5"/>
       <c r="K39" s="5"/>
@@ -19271,7 +19386,7 @@
       <c r="AI39" s="5"/>
       <c r="AJ39" s="5"/>
       <c r="AK39" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL39" s="5"/>
       <c r="AM39" s="5"/>
@@ -19316,7 +19431,9 @@
       <c r="BZ39" s="5"/>
       <c r="CA39" s="5"/>
       <c r="CB39" s="5"/>
-      <c r="CC39" s="5"/>
+      <c r="CC39" s="5" t="n">
+        <v>5.57</v>
+      </c>
       <c r="CD39" s="5"/>
       <c r="CE39" s="5"/>
       <c r="CF39" s="5"/>
@@ -19649,44 +19766,45 @@
       <c r="OU39" s="5"/>
       <c r="OV39" s="5"/>
       <c r="OW39" s="5"/>
-      <c r="OX39" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="OY39" s="5"/>
+      <c r="OX39" s="5"/>
+      <c r="OY39" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OZ39" s="5"/>
       <c r="PA39" s="5"/>
       <c r="PB39" s="5"/>
       <c r="PC39" s="5"/>
       <c r="PD39" s="5"/>
       <c r="PE39" s="5"/>
-      <c r="PF39" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="PG39" s="5"/>
+      <c r="PF39" s="5"/>
+      <c r="PG39" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PH39" s="5"/>
       <c r="PI39" s="5"/>
+      <c r="PJ39" s="5"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E40" s="5"/>
       <c r="F40" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
       <c r="I40" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J40" s="5"/>
       <c r="K40" s="5"/>
@@ -19716,7 +19834,7 @@
       <c r="AI40" s="5"/>
       <c r="AJ40" s="5"/>
       <c r="AK40" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL40" s="5"/>
       <c r="AM40" s="5"/>
@@ -19761,7 +19879,9 @@
       <c r="BZ40" s="5"/>
       <c r="CA40" s="5"/>
       <c r="CB40" s="5"/>
-      <c r="CC40" s="5"/>
+      <c r="CC40" s="5" t="n">
+        <v>0.04</v>
+      </c>
       <c r="CD40" s="5"/>
       <c r="CE40" s="5"/>
       <c r="CF40" s="5"/>
@@ -20094,44 +20214,45 @@
       <c r="OU40" s="5"/>
       <c r="OV40" s="5"/>
       <c r="OW40" s="5"/>
-      <c r="OX40" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="OY40" s="5"/>
+      <c r="OX40" s="5"/>
+      <c r="OY40" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OZ40" s="5"/>
       <c r="PA40" s="5"/>
       <c r="PB40" s="5"/>
       <c r="PC40" s="5"/>
       <c r="PD40" s="5"/>
       <c r="PE40" s="5"/>
-      <c r="PF40" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="PG40" s="5"/>
+      <c r="PF40" s="5"/>
+      <c r="PG40" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PH40" s="5"/>
       <c r="PI40" s="5"/>
+      <c r="PJ40" s="5"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E41" s="5"/>
       <c r="F41" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
       <c r="I41" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
@@ -20161,7 +20282,7 @@
       <c r="AI41" s="5"/>
       <c r="AJ41" s="5"/>
       <c r="AK41" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL41" s="5"/>
       <c r="AM41" s="5"/>
@@ -20206,7 +20327,9 @@
       <c r="BZ41" s="5"/>
       <c r="CA41" s="5"/>
       <c r="CB41" s="5"/>
-      <c r="CC41" s="5"/>
+      <c r="CC41" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="CD41" s="5"/>
       <c r="CE41" s="5"/>
       <c r="CF41" s="5"/>
@@ -20539,44 +20662,45 @@
       <c r="OU41" s="5"/>
       <c r="OV41" s="5"/>
       <c r="OW41" s="5"/>
-      <c r="OX41" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="OY41" s="5"/>
+      <c r="OX41" s="5"/>
+      <c r="OY41" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OZ41" s="5"/>
       <c r="PA41" s="5"/>
       <c r="PB41" s="5"/>
       <c r="PC41" s="5"/>
       <c r="PD41" s="5"/>
       <c r="PE41" s="5"/>
-      <c r="PF41" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="PG41" s="5"/>
+      <c r="PF41" s="5"/>
+      <c r="PG41" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PH41" s="5"/>
       <c r="PI41" s="5"/>
+      <c r="PJ41" s="5"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="D42" s="5" t="n">
-        <v>9142.04</v>
+        <v>430</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>430</v>
       </c>
       <c r="E42" s="5"/>
       <c r="F42" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
       <c r="I42" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J42" s="5"/>
       <c r="K42" s="5"/>
@@ -20606,7 +20730,7 @@
       <c r="AI42" s="5"/>
       <c r="AJ42" s="5"/>
       <c r="AK42" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL42" s="5"/>
       <c r="AM42" s="5"/>
@@ -20651,7 +20775,9 @@
       <c r="BZ42" s="5"/>
       <c r="CA42" s="5"/>
       <c r="CB42" s="5"/>
-      <c r="CC42" s="5"/>
+      <c r="CC42" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="CD42" s="5"/>
       <c r="CE42" s="5"/>
       <c r="CF42" s="5"/>
@@ -20984,44 +21110,45 @@
       <c r="OU42" s="5"/>
       <c r="OV42" s="5"/>
       <c r="OW42" s="5"/>
-      <c r="OX42" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="OY42" s="5"/>
+      <c r="OX42" s="5"/>
+      <c r="OY42" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OZ42" s="5"/>
       <c r="PA42" s="5"/>
       <c r="PB42" s="5"/>
       <c r="PC42" s="5"/>
       <c r="PD42" s="5"/>
       <c r="PE42" s="5"/>
-      <c r="PF42" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="PG42" s="5"/>
+      <c r="PF42" s="5"/>
+      <c r="PG42" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PH42" s="5"/>
       <c r="PI42" s="5"/>
+      <c r="PJ42" s="5"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>9142.04</v>
       </c>
       <c r="E43" s="5"/>
       <c r="F43" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
-      <c r="I43" s="5" t="n">
-        <v>8.21</v>
+      <c r="I43" s="5" t="s">
+        <v>430</v>
       </c>
       <c r="J43" s="5"/>
       <c r="K43" s="5"/>
@@ -21051,7 +21178,7 @@
       <c r="AI43" s="5"/>
       <c r="AJ43" s="5"/>
       <c r="AK43" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL43" s="5"/>
       <c r="AM43" s="5"/>
@@ -21096,7 +21223,9 @@
       <c r="BZ43" s="5"/>
       <c r="CA43" s="5"/>
       <c r="CB43" s="5"/>
-      <c r="CC43" s="5"/>
+      <c r="CC43" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="CD43" s="5"/>
       <c r="CE43" s="5"/>
       <c r="CF43" s="5"/>
@@ -21429,44 +21558,45 @@
       <c r="OU43" s="5"/>
       <c r="OV43" s="5"/>
       <c r="OW43" s="5"/>
-      <c r="OX43" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="OY43" s="5"/>
+      <c r="OX43" s="5"/>
+      <c r="OY43" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OZ43" s="5"/>
       <c r="PA43" s="5"/>
       <c r="PB43" s="5"/>
       <c r="PC43" s="5"/>
       <c r="PD43" s="5"/>
       <c r="PE43" s="5"/>
-      <c r="PF43" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="PG43" s="5"/>
+      <c r="PF43" s="5"/>
+      <c r="PG43" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PH43" s="5"/>
       <c r="PI43" s="5"/>
+      <c r="PJ43" s="5"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>477</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E44" s="5"/>
       <c r="F44" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
-      <c r="I44" s="5" t="s">
-        <v>429</v>
+      <c r="I44" s="5" t="n">
+        <v>8.21</v>
       </c>
       <c r="J44" s="5"/>
       <c r="K44" s="5"/>
@@ -21496,7 +21626,7 @@
       <c r="AI44" s="5"/>
       <c r="AJ44" s="5"/>
       <c r="AK44" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL44" s="5"/>
       <c r="AM44" s="5"/>
@@ -21541,7 +21671,9 @@
       <c r="BZ44" s="5"/>
       <c r="CA44" s="5"/>
       <c r="CB44" s="5"/>
-      <c r="CC44" s="5"/>
+      <c r="CC44" s="5" t="n">
+        <v>1303.78</v>
+      </c>
       <c r="CD44" s="5"/>
       <c r="CE44" s="5"/>
       <c r="CF44" s="5"/>
@@ -21874,44 +22006,45 @@
       <c r="OU44" s="5"/>
       <c r="OV44" s="5"/>
       <c r="OW44" s="5"/>
-      <c r="OX44" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="OY44" s="5"/>
+      <c r="OX44" s="5"/>
+      <c r="OY44" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OZ44" s="5"/>
       <c r="PA44" s="5"/>
       <c r="PB44" s="5"/>
       <c r="PC44" s="5"/>
       <c r="PD44" s="5"/>
       <c r="PE44" s="5"/>
-      <c r="PF44" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="PG44" s="5"/>
+      <c r="PF44" s="5"/>
+      <c r="PG44" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PH44" s="5"/>
       <c r="PI44" s="5"/>
+      <c r="PJ44" s="5"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E45" s="5"/>
       <c r="F45" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
       <c r="I45" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J45" s="5"/>
       <c r="K45" s="5"/>
@@ -21941,7 +22074,7 @@
       <c r="AI45" s="5"/>
       <c r="AJ45" s="5"/>
       <c r="AK45" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL45" s="5"/>
       <c r="AM45" s="5"/>
@@ -21986,7 +22119,9 @@
       <c r="BZ45" s="5"/>
       <c r="CA45" s="5"/>
       <c r="CB45" s="5"/>
-      <c r="CC45" s="5"/>
+      <c r="CC45" s="5" t="n">
+        <v>555845</v>
+      </c>
       <c r="CD45" s="5"/>
       <c r="CE45" s="5"/>
       <c r="CF45" s="5"/>
@@ -22319,44 +22454,45 @@
       <c r="OU45" s="5"/>
       <c r="OV45" s="5"/>
       <c r="OW45" s="5"/>
-      <c r="OX45" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="OY45" s="5"/>
+      <c r="OX45" s="5"/>
+      <c r="OY45" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OZ45" s="5"/>
       <c r="PA45" s="5"/>
       <c r="PB45" s="5"/>
       <c r="PC45" s="5"/>
       <c r="PD45" s="5"/>
       <c r="PE45" s="5"/>
-      <c r="PF45" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="PG45" s="5"/>
+      <c r="PF45" s="5"/>
+      <c r="PG45" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PH45" s="5"/>
       <c r="PI45" s="5"/>
+      <c r="PJ45" s="5"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E46" s="5"/>
       <c r="F46" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
       <c r="I46" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J46" s="5"/>
       <c r="K46" s="5"/>
@@ -22386,7 +22522,7 @@
       <c r="AI46" s="5"/>
       <c r="AJ46" s="5"/>
       <c r="AK46" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL46" s="5"/>
       <c r="AM46" s="5"/>
@@ -22431,7 +22567,9 @@
       <c r="BZ46" s="5"/>
       <c r="CA46" s="5"/>
       <c r="CB46" s="5"/>
-      <c r="CC46" s="5"/>
+      <c r="CC46" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="CD46" s="5"/>
       <c r="CE46" s="5"/>
       <c r="CF46" s="5"/>
@@ -22764,44 +22902,45 @@
       <c r="OU46" s="5"/>
       <c r="OV46" s="5"/>
       <c r="OW46" s="5"/>
-      <c r="OX46" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="OY46" s="5"/>
+      <c r="OX46" s="5"/>
+      <c r="OY46" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OZ46" s="5"/>
       <c r="PA46" s="5"/>
       <c r="PB46" s="5"/>
       <c r="PC46" s="5"/>
       <c r="PD46" s="5"/>
       <c r="PE46" s="5"/>
-      <c r="PF46" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="PG46" s="5"/>
+      <c r="PF46" s="5"/>
+      <c r="PG46" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PH46" s="5"/>
       <c r="PI46" s="5"/>
+      <c r="PJ46" s="5"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>481</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E47" s="5"/>
       <c r="F47" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
       <c r="I47" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J47" s="5"/>
       <c r="K47" s="5"/>
@@ -22830,8 +22969,8 @@
       <c r="AH47" s="5"/>
       <c r="AI47" s="5"/>
       <c r="AJ47" s="5"/>
-      <c r="AK47" s="5" t="n">
-        <v>22324</v>
+      <c r="AK47" s="5" t="s">
+        <v>430</v>
       </c>
       <c r="AL47" s="5"/>
       <c r="AM47" s="5"/>
@@ -22876,7 +23015,9 @@
       <c r="BZ47" s="5"/>
       <c r="CA47" s="5"/>
       <c r="CB47" s="5"/>
-      <c r="CC47" s="5"/>
+      <c r="CC47" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="CD47" s="5"/>
       <c r="CE47" s="5"/>
       <c r="CF47" s="5"/>
@@ -23209,44 +23350,45 @@
       <c r="OU47" s="5"/>
       <c r="OV47" s="5"/>
       <c r="OW47" s="5"/>
-      <c r="OX47" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="OY47" s="5"/>
+      <c r="OX47" s="5"/>
+      <c r="OY47" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OZ47" s="5"/>
       <c r="PA47" s="5"/>
       <c r="PB47" s="5"/>
       <c r="PC47" s="5"/>
       <c r="PD47" s="5"/>
       <c r="PE47" s="5"/>
-      <c r="PF47" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="PG47" s="5"/>
+      <c r="PF47" s="5"/>
+      <c r="PG47" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PH47" s="5"/>
       <c r="PI47" s="5"/>
+      <c r="PJ47" s="5"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>442</v>
+        <v>483</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E48" s="5"/>
       <c r="F48" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
       <c r="I48" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J48" s="5"/>
       <c r="K48" s="5"/>
@@ -23276,7 +23418,7 @@
       <c r="AI48" s="5"/>
       <c r="AJ48" s="5"/>
       <c r="AK48" s="5" t="n">
-        <v>1892.4</v>
+        <v>22324</v>
       </c>
       <c r="AL48" s="5"/>
       <c r="AM48" s="5"/>
@@ -23321,7 +23463,9 @@
       <c r="BZ48" s="5"/>
       <c r="CA48" s="5"/>
       <c r="CB48" s="5"/>
-      <c r="CC48" s="5"/>
+      <c r="CC48" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="CD48" s="5"/>
       <c r="CE48" s="5"/>
       <c r="CF48" s="5"/>
@@ -23654,44 +23798,45 @@
       <c r="OU48" s="5"/>
       <c r="OV48" s="5"/>
       <c r="OW48" s="5"/>
-      <c r="OX48" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="OY48" s="5"/>
+      <c r="OX48" s="5"/>
+      <c r="OY48" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OZ48" s="5"/>
       <c r="PA48" s="5"/>
       <c r="PB48" s="5"/>
       <c r="PC48" s="5"/>
       <c r="PD48" s="5"/>
       <c r="PE48" s="5"/>
-      <c r="PF48" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="PG48" s="5"/>
+      <c r="PF48" s="5"/>
+      <c r="PG48" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PH48" s="5"/>
       <c r="PI48" s="5"/>
+      <c r="PJ48" s="5"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
         <v>482</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>483</v>
+        <v>443</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="D49" s="5" t="n">
-        <v>161.03</v>
+        <v>430</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>430</v>
       </c>
       <c r="E49" s="5"/>
       <c r="F49" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
       <c r="I49" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J49" s="5"/>
       <c r="K49" s="5"/>
@@ -23720,8 +23865,8 @@
       <c r="AH49" s="5"/>
       <c r="AI49" s="5"/>
       <c r="AJ49" s="5"/>
-      <c r="AK49" s="5" t="s">
-        <v>429</v>
+      <c r="AK49" s="5" t="n">
+        <v>1892.4</v>
       </c>
       <c r="AL49" s="5"/>
       <c r="AM49" s="5"/>
@@ -23766,7 +23911,9 @@
       <c r="BZ49" s="5"/>
       <c r="CA49" s="5"/>
       <c r="CB49" s="5"/>
-      <c r="CC49" s="5"/>
+      <c r="CC49" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="CD49" s="5"/>
       <c r="CE49" s="5"/>
       <c r="CF49" s="5"/>
@@ -24099,44 +24246,45 @@
       <c r="OU49" s="5"/>
       <c r="OV49" s="5"/>
       <c r="OW49" s="5"/>
-      <c r="OX49" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="OY49" s="5"/>
+      <c r="OX49" s="5"/>
+      <c r="OY49" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OZ49" s="5"/>
       <c r="PA49" s="5"/>
       <c r="PB49" s="5"/>
       <c r="PC49" s="5"/>
       <c r="PD49" s="5"/>
       <c r="PE49" s="5"/>
-      <c r="PF49" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="PG49" s="5"/>
+      <c r="PF49" s="5"/>
+      <c r="PG49" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PH49" s="5"/>
       <c r="PI49" s="5"/>
+      <c r="PJ49" s="5"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>26.5</v>
+        <v>161.03</v>
       </c>
       <c r="E50" s="5"/>
       <c r="F50" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
       <c r="I50" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J50" s="5"/>
       <c r="K50" s="5"/>
@@ -24166,7 +24314,7 @@
       <c r="AI50" s="5"/>
       <c r="AJ50" s="5"/>
       <c r="AK50" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL50" s="5"/>
       <c r="AM50" s="5"/>
@@ -24211,7 +24359,9 @@
       <c r="BZ50" s="5"/>
       <c r="CA50" s="5"/>
       <c r="CB50" s="5"/>
-      <c r="CC50" s="5"/>
+      <c r="CC50" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="CD50" s="5"/>
       <c r="CE50" s="5"/>
       <c r="CF50" s="5"/>
@@ -24544,44 +24694,45 @@
       <c r="OU50" s="5"/>
       <c r="OV50" s="5"/>
       <c r="OW50" s="5"/>
-      <c r="OX50" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="OY50" s="5"/>
+      <c r="OX50" s="5"/>
+      <c r="OY50" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OZ50" s="5"/>
       <c r="PA50" s="5"/>
       <c r="PB50" s="5"/>
       <c r="PC50" s="5"/>
       <c r="PD50" s="5"/>
       <c r="PE50" s="5"/>
-      <c r="PF50" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="PG50" s="5"/>
+      <c r="PF50" s="5"/>
+      <c r="PG50" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PH50" s="5"/>
       <c r="PI50" s="5"/>
+      <c r="PJ50" s="5"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>486</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>101.85</v>
+        <v>26.5</v>
       </c>
       <c r="E51" s="5"/>
       <c r="F51" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J51" s="5"/>
       <c r="K51" s="5"/>
@@ -24611,7 +24762,7 @@
       <c r="AI51" s="5"/>
       <c r="AJ51" s="5"/>
       <c r="AK51" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL51" s="5"/>
       <c r="AM51" s="5"/>
@@ -24656,7 +24807,9 @@
       <c r="BZ51" s="5"/>
       <c r="CA51" s="5"/>
       <c r="CB51" s="5"/>
-      <c r="CC51" s="5"/>
+      <c r="CC51" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="CD51" s="5"/>
       <c r="CE51" s="5"/>
       <c r="CF51" s="5"/>
@@ -24989,44 +25142,45 @@
       <c r="OU51" s="5"/>
       <c r="OV51" s="5"/>
       <c r="OW51" s="5"/>
-      <c r="OX51" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="OY51" s="5"/>
+      <c r="OX51" s="5"/>
+      <c r="OY51" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OZ51" s="5"/>
       <c r="PA51" s="5"/>
       <c r="PB51" s="5"/>
       <c r="PC51" s="5"/>
       <c r="PD51" s="5"/>
       <c r="PE51" s="5"/>
-      <c r="PF51" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="PG51" s="5"/>
+      <c r="PF51" s="5"/>
+      <c r="PG51" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PH51" s="5"/>
       <c r="PI51" s="5"/>
+      <c r="PJ51" s="5"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>103.1</v>
+        <v>101.85</v>
       </c>
       <c r="E52" s="5"/>
       <c r="F52" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
       <c r="I52" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J52" s="5"/>
       <c r="K52" s="5"/>
@@ -25056,7 +25210,7 @@
       <c r="AI52" s="5"/>
       <c r="AJ52" s="5"/>
       <c r="AK52" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL52" s="5"/>
       <c r="AM52" s="5"/>
@@ -25101,7 +25255,9 @@
       <c r="BZ52" s="5"/>
       <c r="CA52" s="5"/>
       <c r="CB52" s="5"/>
-      <c r="CC52" s="5"/>
+      <c r="CC52" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="CD52" s="5"/>
       <c r="CE52" s="5"/>
       <c r="CF52" s="5"/>
@@ -25434,44 +25590,45 @@
       <c r="OU52" s="5"/>
       <c r="OV52" s="5"/>
       <c r="OW52" s="5"/>
-      <c r="OX52" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="OY52" s="5"/>
+      <c r="OX52" s="5"/>
+      <c r="OY52" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OZ52" s="5"/>
       <c r="PA52" s="5"/>
       <c r="PB52" s="5"/>
       <c r="PC52" s="5"/>
       <c r="PD52" s="5"/>
       <c r="PE52" s="5"/>
-      <c r="PF52" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="PG52" s="5"/>
+      <c r="PF52" s="5"/>
+      <c r="PG52" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PH52" s="5"/>
       <c r="PI52" s="5"/>
+      <c r="PJ52" s="5"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>489</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>60.29</v>
+        <v>103.1</v>
       </c>
       <c r="E53" s="5"/>
       <c r="F53" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
       <c r="I53" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J53" s="5"/>
       <c r="K53" s="5"/>
@@ -25501,7 +25658,7 @@
       <c r="AI53" s="5"/>
       <c r="AJ53" s="5"/>
       <c r="AK53" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL53" s="5"/>
       <c r="AM53" s="5"/>
@@ -25546,7 +25703,9 @@
       <c r="BZ53" s="5"/>
       <c r="CA53" s="5"/>
       <c r="CB53" s="5"/>
-      <c r="CC53" s="5"/>
+      <c r="CC53" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="CD53" s="5"/>
       <c r="CE53" s="5"/>
       <c r="CF53" s="5"/>
@@ -25879,44 +26038,45 @@
       <c r="OU53" s="5"/>
       <c r="OV53" s="5"/>
       <c r="OW53" s="5"/>
-      <c r="OX53" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="OY53" s="5"/>
+      <c r="OX53" s="5"/>
+      <c r="OY53" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OZ53" s="5"/>
       <c r="PA53" s="5"/>
       <c r="PB53" s="5"/>
       <c r="PC53" s="5"/>
       <c r="PD53" s="5"/>
       <c r="PE53" s="5"/>
-      <c r="PF53" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="PG53" s="5"/>
+      <c r="PF53" s="5"/>
+      <c r="PG53" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PH53" s="5"/>
       <c r="PI53" s="5"/>
+      <c r="PJ53" s="5"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>5.49</v>
+        <v>60.29</v>
       </c>
       <c r="E54" s="5"/>
       <c r="F54" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
       <c r="I54" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J54" s="5"/>
       <c r="K54" s="5"/>
@@ -25946,7 +26106,7 @@
       <c r="AI54" s="5"/>
       <c r="AJ54" s="5"/>
       <c r="AK54" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL54" s="5"/>
       <c r="AM54" s="5"/>
@@ -25991,7 +26151,9 @@
       <c r="BZ54" s="5"/>
       <c r="CA54" s="5"/>
       <c r="CB54" s="5"/>
-      <c r="CC54" s="5"/>
+      <c r="CC54" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="CD54" s="5"/>
       <c r="CE54" s="5"/>
       <c r="CF54" s="5"/>
@@ -26324,44 +26486,45 @@
       <c r="OU54" s="5"/>
       <c r="OV54" s="5"/>
       <c r="OW54" s="5"/>
-      <c r="OX54" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="OY54" s="5"/>
+      <c r="OX54" s="5"/>
+      <c r="OY54" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OZ54" s="5"/>
       <c r="PA54" s="5"/>
       <c r="PB54" s="5"/>
       <c r="PC54" s="5"/>
       <c r="PD54" s="5"/>
       <c r="PE54" s="5"/>
-      <c r="PF54" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="PG54" s="5"/>
+      <c r="PF54" s="5"/>
+      <c r="PG54" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PH54" s="5"/>
       <c r="PI54" s="5"/>
+      <c r="PJ54" s="5"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>-0.431</v>
+        <v>5.49</v>
       </c>
       <c r="E55" s="5"/>
       <c r="F55" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
       <c r="I55" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J55" s="5"/>
       <c r="K55" s="5"/>
@@ -26391,7 +26554,7 @@
       <c r="AI55" s="5"/>
       <c r="AJ55" s="5"/>
       <c r="AK55" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL55" s="5"/>
       <c r="AM55" s="5"/>
@@ -26436,7 +26599,9 @@
       <c r="BZ55" s="5"/>
       <c r="CA55" s="5"/>
       <c r="CB55" s="5"/>
-      <c r="CC55" s="5"/>
+      <c r="CC55" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="CD55" s="5"/>
       <c r="CE55" s="5"/>
       <c r="CF55" s="5"/>
@@ -26769,44 +26934,45 @@
       <c r="OU55" s="5"/>
       <c r="OV55" s="5"/>
       <c r="OW55" s="5"/>
-      <c r="OX55" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="OY55" s="5"/>
+      <c r="OX55" s="5"/>
+      <c r="OY55" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OZ55" s="5"/>
       <c r="PA55" s="5"/>
       <c r="PB55" s="5"/>
       <c r="PC55" s="5"/>
       <c r="PD55" s="5"/>
       <c r="PE55" s="5"/>
-      <c r="PF55" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="PG55" s="5"/>
+      <c r="PF55" s="5"/>
+      <c r="PG55" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PH55" s="5"/>
       <c r="PI55" s="5"/>
+      <c r="PJ55" s="5"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>493</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>-0.431</v>
       </c>
       <c r="E56" s="5"/>
       <c r="F56" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
       <c r="I56" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J56" s="5"/>
       <c r="K56" s="5"/>
@@ -26836,7 +27002,7 @@
       <c r="AI56" s="5"/>
       <c r="AJ56" s="5"/>
       <c r="AK56" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL56" s="5"/>
       <c r="AM56" s="5"/>
@@ -26881,7 +27047,9 @@
       <c r="BZ56" s="5"/>
       <c r="CA56" s="5"/>
       <c r="CB56" s="5"/>
-      <c r="CC56" s="5"/>
+      <c r="CC56" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="CD56" s="5"/>
       <c r="CE56" s="5"/>
       <c r="CF56" s="5"/>
@@ -27214,22 +27382,23 @@
       <c r="OU56" s="5"/>
       <c r="OV56" s="5"/>
       <c r="OW56" s="5"/>
-      <c r="OX56" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="OY56" s="5"/>
+      <c r="OX56" s="5"/>
+      <c r="OY56" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OZ56" s="5"/>
       <c r="PA56" s="5"/>
       <c r="PB56" s="5"/>
       <c r="PC56" s="5"/>
       <c r="PD56" s="5"/>
       <c r="PE56" s="5"/>
-      <c r="PF56" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="PG56" s="5"/>
+      <c r="PF56" s="5"/>
+      <c r="PG56" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PH56" s="5"/>
       <c r="PI56" s="5"/>
+      <c r="PJ56" s="5"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
@@ -27239,19 +27408,19 @@
         <v>495</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E57" s="5"/>
       <c r="F57" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
       <c r="I57" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J57" s="5"/>
       <c r="K57" s="5"/>
@@ -27281,7 +27450,7 @@
       <c r="AI57" s="5"/>
       <c r="AJ57" s="5"/>
       <c r="AK57" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL57" s="5"/>
       <c r="AM57" s="5"/>
@@ -27326,7 +27495,9 @@
       <c r="BZ57" s="5"/>
       <c r="CA57" s="5"/>
       <c r="CB57" s="5"/>
-      <c r="CC57" s="5"/>
+      <c r="CC57" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="CD57" s="5"/>
       <c r="CE57" s="5"/>
       <c r="CF57" s="5"/>
@@ -27659,22 +27830,23 @@
       <c r="OU57" s="5"/>
       <c r="OV57" s="5"/>
       <c r="OW57" s="5"/>
-      <c r="OX57" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="OY57" s="5"/>
+      <c r="OX57" s="5"/>
+      <c r="OY57" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OZ57" s="5"/>
       <c r="PA57" s="5"/>
       <c r="PB57" s="5"/>
       <c r="PC57" s="5"/>
       <c r="PD57" s="5"/>
       <c r="PE57" s="5"/>
-      <c r="PF57" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="PG57" s="5"/>
+      <c r="PF57" s="5"/>
+      <c r="PG57" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PH57" s="5"/>
       <c r="PI57" s="5"/>
+      <c r="PJ57" s="5"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="s">
@@ -27684,19 +27856,19 @@
         <v>497</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E58" s="5"/>
       <c r="F58" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
       <c r="I58" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J58" s="5"/>
       <c r="K58" s="5"/>
@@ -27726,7 +27898,7 @@
       <c r="AI58" s="5"/>
       <c r="AJ58" s="5"/>
       <c r="AK58" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL58" s="5"/>
       <c r="AM58" s="5"/>
@@ -27771,7 +27943,9 @@
       <c r="BZ58" s="5"/>
       <c r="CA58" s="5"/>
       <c r="CB58" s="5"/>
-      <c r="CC58" s="5"/>
+      <c r="CC58" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="CD58" s="5"/>
       <c r="CE58" s="5"/>
       <c r="CF58" s="5"/>
@@ -28104,44 +28278,45 @@
       <c r="OU58" s="5"/>
       <c r="OV58" s="5"/>
       <c r="OW58" s="5"/>
-      <c r="OX58" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="OY58" s="5"/>
+      <c r="OX58" s="5"/>
+      <c r="OY58" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OZ58" s="5"/>
       <c r="PA58" s="5"/>
       <c r="PB58" s="5"/>
       <c r="PC58" s="5"/>
       <c r="PD58" s="5"/>
       <c r="PE58" s="5"/>
-      <c r="PF58" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="PG58" s="5"/>
+      <c r="PF58" s="5"/>
+      <c r="PG58" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PH58" s="5"/>
       <c r="PI58" s="5"/>
+      <c r="PJ58" s="5"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="4" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E59" s="5"/>
       <c r="F59" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
       <c r="I59" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J59" s="5"/>
       <c r="K59" s="5"/>
@@ -28171,7 +28346,7 @@
       <c r="AI59" s="5"/>
       <c r="AJ59" s="5"/>
       <c r="AK59" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL59" s="5"/>
       <c r="AM59" s="5"/>
@@ -28216,7 +28391,9 @@
       <c r="BZ59" s="5"/>
       <c r="CA59" s="5"/>
       <c r="CB59" s="5"/>
-      <c r="CC59" s="5"/>
+      <c r="CC59" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="CD59" s="5"/>
       <c r="CE59" s="5"/>
       <c r="CF59" s="5"/>
@@ -28549,44 +28726,45 @@
       <c r="OU59" s="5"/>
       <c r="OV59" s="5"/>
       <c r="OW59" s="5"/>
-      <c r="OX59" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="OY59" s="5"/>
+      <c r="OX59" s="5"/>
+      <c r="OY59" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OZ59" s="5"/>
       <c r="PA59" s="5"/>
       <c r="PB59" s="5"/>
       <c r="PC59" s="5"/>
       <c r="PD59" s="5"/>
       <c r="PE59" s="5"/>
-      <c r="PF59" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="PG59" s="5"/>
+      <c r="PF59" s="5"/>
+      <c r="PG59" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PH59" s="5"/>
       <c r="PI59" s="5"/>
+      <c r="PJ59" s="5"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="4" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>500</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E60" s="5"/>
       <c r="F60" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
       <c r="I60" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J60" s="5"/>
       <c r="K60" s="5"/>
@@ -28616,7 +28794,7 @@
       <c r="AI60" s="5"/>
       <c r="AJ60" s="5"/>
       <c r="AK60" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL60" s="5"/>
       <c r="AM60" s="5"/>
@@ -28661,7 +28839,9 @@
       <c r="BZ60" s="5"/>
       <c r="CA60" s="5"/>
       <c r="CB60" s="5"/>
-      <c r="CC60" s="5"/>
+      <c r="CC60" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="CD60" s="5"/>
       <c r="CE60" s="5"/>
       <c r="CF60" s="5"/>
@@ -28994,22 +29174,23 @@
       <c r="OU60" s="5"/>
       <c r="OV60" s="5"/>
       <c r="OW60" s="5"/>
-      <c r="OX60" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="OY60" s="5"/>
+      <c r="OX60" s="5"/>
+      <c r="OY60" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OZ60" s="5"/>
       <c r="PA60" s="5"/>
       <c r="PB60" s="5"/>
       <c r="PC60" s="5"/>
       <c r="PD60" s="5"/>
       <c r="PE60" s="5"/>
-      <c r="PF60" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="PG60" s="5"/>
+      <c r="PF60" s="5"/>
+      <c r="PG60" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PH60" s="5"/>
       <c r="PI60" s="5"/>
+      <c r="PJ60" s="5"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="4" t="s">
@@ -29018,20 +29199,20 @@
       <c r="B61" s="5" t="s">
         <v>502</v>
       </c>
-      <c r="C61" s="5" t="n">
-        <v>56</v>
+      <c r="C61" s="5" t="s">
+        <v>430</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E61" s="5"/>
-      <c r="F61" s="5" t="n">
-        <v>520</v>
+      <c r="F61" s="5" t="s">
+        <v>430</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
       <c r="I61" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J61" s="5"/>
       <c r="K61" s="5"/>
@@ -29060,8 +29241,8 @@
       <c r="AH61" s="5"/>
       <c r="AI61" s="5"/>
       <c r="AJ61" s="5"/>
-      <c r="AK61" s="5" t="n">
-        <v>660</v>
+      <c r="AK61" s="5" t="s">
+        <v>430</v>
       </c>
       <c r="AL61" s="5"/>
       <c r="AM61" s="5"/>
@@ -29106,7 +29287,9 @@
       <c r="BZ61" s="5"/>
       <c r="CA61" s="5"/>
       <c r="CB61" s="5"/>
-      <c r="CC61" s="5"/>
+      <c r="CC61" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="CD61" s="5"/>
       <c r="CE61" s="5"/>
       <c r="CF61" s="5"/>
@@ -29439,44 +29622,45 @@
       <c r="OU61" s="5"/>
       <c r="OV61" s="5"/>
       <c r="OW61" s="5"/>
-      <c r="OX61" s="5" t="n">
-        <v>992</v>
-      </c>
-      <c r="OY61" s="5"/>
+      <c r="OX61" s="5"/>
+      <c r="OY61" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OZ61" s="5"/>
       <c r="PA61" s="5"/>
       <c r="PB61" s="5"/>
       <c r="PC61" s="5"/>
       <c r="PD61" s="5"/>
       <c r="PE61" s="5"/>
-      <c r="PF61" s="5" t="n">
-        <v>484</v>
-      </c>
-      <c r="PG61" s="5"/>
+      <c r="PF61" s="5"/>
+      <c r="PG61" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PH61" s="5"/>
       <c r="PI61" s="5"/>
+      <c r="PJ61" s="5"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>503</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="D62" s="5" t="n">
-        <v>86</v>
+        <v>504</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>430</v>
       </c>
       <c r="E62" s="5"/>
-      <c r="F62" s="5" t="s">
-        <v>429</v>
+      <c r="F62" s="5" t="n">
+        <v>520</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
       <c r="I62" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J62" s="5"/>
       <c r="K62" s="5"/>
@@ -29505,8 +29689,8 @@
       <c r="AH62" s="5"/>
       <c r="AI62" s="5"/>
       <c r="AJ62" s="5"/>
-      <c r="AK62" s="5" t="s">
-        <v>429</v>
+      <c r="AK62" s="5" t="n">
+        <v>660</v>
       </c>
       <c r="AL62" s="5"/>
       <c r="AM62" s="5"/>
@@ -29551,7 +29735,9 @@
       <c r="BZ62" s="5"/>
       <c r="CA62" s="5"/>
       <c r="CB62" s="5"/>
-      <c r="CC62" s="5"/>
+      <c r="CC62" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="CD62" s="5"/>
       <c r="CE62" s="5"/>
       <c r="CF62" s="5"/>
@@ -29884,44 +30070,45 @@
       <c r="OU62" s="5"/>
       <c r="OV62" s="5"/>
       <c r="OW62" s="5"/>
-      <c r="OX62" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="OY62" s="5"/>
+      <c r="OX62" s="5"/>
+      <c r="OY62" s="5" t="n">
+        <v>992</v>
+      </c>
       <c r="OZ62" s="5"/>
       <c r="PA62" s="5"/>
       <c r="PB62" s="5"/>
       <c r="PC62" s="5"/>
       <c r="PD62" s="5"/>
       <c r="PE62" s="5"/>
-      <c r="PF62" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="PG62" s="5"/>
+      <c r="PF62" s="5"/>
+      <c r="PG62" s="5" t="n">
+        <v>484</v>
+      </c>
       <c r="PH62" s="5"/>
       <c r="PI62" s="5"/>
+      <c r="PJ62" s="5"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="4" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>505</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
+      </c>
+      <c r="D63" s="5" t="n">
+        <v>86</v>
       </c>
       <c r="E63" s="5"/>
       <c r="F63" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
       <c r="I63" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J63" s="5"/>
       <c r="K63" s="5"/>
@@ -29951,7 +30138,7 @@
       <c r="AI63" s="5"/>
       <c r="AJ63" s="5"/>
       <c r="AK63" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL63" s="5"/>
       <c r="AM63" s="5"/>
@@ -29996,7 +30183,9 @@
       <c r="BZ63" s="5"/>
       <c r="CA63" s="5"/>
       <c r="CB63" s="5"/>
-      <c r="CC63" s="5"/>
+      <c r="CC63" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="CD63" s="5"/>
       <c r="CE63" s="5"/>
       <c r="CF63" s="5"/>
@@ -30329,26 +30518,475 @@
       <c r="OU63" s="5"/>
       <c r="OV63" s="5"/>
       <c r="OW63" s="5"/>
-      <c r="OX63" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="OY63" s="5"/>
+      <c r="OX63" s="5"/>
+      <c r="OY63" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OZ63" s="5"/>
       <c r="PA63" s="5"/>
       <c r="PB63" s="5"/>
       <c r="PC63" s="5"/>
       <c r="PD63" s="5"/>
       <c r="PE63" s="5"/>
-      <c r="PF63" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="PG63" s="5"/>
+      <c r="PF63" s="5"/>
+      <c r="PG63" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PH63" s="5"/>
       <c r="PI63" s="5"/>
+      <c r="PJ63" s="5"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="E64" s="5"/>
+      <c r="F64" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="G64" s="5"/>
+      <c r="H64" s="5"/>
+      <c r="I64" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="J64" s="5"/>
+      <c r="K64" s="5"/>
+      <c r="L64" s="5"/>
+      <c r="M64" s="5"/>
+      <c r="N64" s="5"/>
+      <c r="O64" s="5"/>
+      <c r="P64" s="5"/>
+      <c r="Q64" s="5"/>
+      <c r="R64" s="5"/>
+      <c r="S64" s="5"/>
+      <c r="T64" s="5"/>
+      <c r="U64" s="5"/>
+      <c r="V64" s="5"/>
+      <c r="W64" s="5"/>
+      <c r="X64" s="5"/>
+      <c r="Y64" s="5"/>
+      <c r="Z64" s="5"/>
+      <c r="AA64" s="5"/>
+      <c r="AB64" s="5"/>
+      <c r="AC64" s="5"/>
+      <c r="AD64" s="5"/>
+      <c r="AE64" s="5"/>
+      <c r="AF64" s="5"/>
+      <c r="AG64" s="5"/>
+      <c r="AH64" s="5"/>
+      <c r="AI64" s="5"/>
+      <c r="AJ64" s="5"/>
+      <c r="AK64" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="AL64" s="5"/>
+      <c r="AM64" s="5"/>
+      <c r="AN64" s="5"/>
+      <c r="AO64" s="5"/>
+      <c r="AP64" s="5"/>
+      <c r="AQ64" s="5"/>
+      <c r="AR64" s="5"/>
+      <c r="AS64" s="5"/>
+      <c r="AT64" s="5"/>
+      <c r="AU64" s="5"/>
+      <c r="AV64" s="5"/>
+      <c r="AW64" s="5"/>
+      <c r="AX64" s="5"/>
+      <c r="AY64" s="5"/>
+      <c r="AZ64" s="5"/>
+      <c r="BA64" s="5"/>
+      <c r="BB64" s="5"/>
+      <c r="BC64" s="5"/>
+      <c r="BD64" s="5"/>
+      <c r="BE64" s="5"/>
+      <c r="BF64" s="5"/>
+      <c r="BG64" s="5"/>
+      <c r="BH64" s="5"/>
+      <c r="BI64" s="5"/>
+      <c r="BJ64" s="5"/>
+      <c r="BK64" s="5"/>
+      <c r="BL64" s="5"/>
+      <c r="BM64" s="5"/>
+      <c r="BN64" s="5"/>
+      <c r="BO64" s="5"/>
+      <c r="BP64" s="5"/>
+      <c r="BQ64" s="5"/>
+      <c r="BR64" s="5"/>
+      <c r="BS64" s="5"/>
+      <c r="BT64" s="5"/>
+      <c r="BU64" s="5"/>
+      <c r="BV64" s="5"/>
+      <c r="BW64" s="5"/>
+      <c r="BX64" s="5"/>
+      <c r="BY64" s="5"/>
+      <c r="BZ64" s="5"/>
+      <c r="CA64" s="5"/>
+      <c r="CB64" s="5"/>
+      <c r="CC64" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="CD64" s="5"/>
+      <c r="CE64" s="5"/>
+      <c r="CF64" s="5"/>
+      <c r="CG64" s="5"/>
+      <c r="CH64" s="5"/>
+      <c r="CI64" s="5"/>
+      <c r="CJ64" s="5"/>
+      <c r="CK64" s="5"/>
+      <c r="CL64" s="5"/>
+      <c r="CM64" s="5"/>
+      <c r="CN64" s="5"/>
+      <c r="CO64" s="5"/>
+      <c r="CP64" s="5"/>
+      <c r="CQ64" s="5"/>
+      <c r="CR64" s="5"/>
+      <c r="CS64" s="5"/>
+      <c r="CT64" s="5"/>
+      <c r="CU64" s="5"/>
+      <c r="CV64" s="5"/>
+      <c r="CW64" s="5"/>
+      <c r="CX64" s="5"/>
+      <c r="CY64" s="5"/>
+      <c r="CZ64" s="5"/>
+      <c r="DA64" s="5"/>
+      <c r="DB64" s="5"/>
+      <c r="DC64" s="5"/>
+      <c r="DD64" s="5"/>
+      <c r="DE64" s="5"/>
+      <c r="DF64" s="5"/>
+      <c r="DG64" s="5"/>
+      <c r="DH64" s="5"/>
+      <c r="DI64" s="5"/>
+      <c r="DJ64" s="5"/>
+      <c r="DK64" s="5"/>
+      <c r="DL64" s="5"/>
+      <c r="DM64" s="5"/>
+      <c r="DN64" s="5"/>
+      <c r="DO64" s="5"/>
+      <c r="DP64" s="5"/>
+      <c r="DQ64" s="5"/>
+      <c r="DR64" s="5"/>
+      <c r="DS64" s="5"/>
+      <c r="DT64" s="5"/>
+      <c r="DU64" s="5"/>
+      <c r="DV64" s="5"/>
+      <c r="DW64" s="5"/>
+      <c r="DX64" s="5"/>
+      <c r="DY64" s="5"/>
+      <c r="DZ64" s="5"/>
+      <c r="EA64" s="5"/>
+      <c r="EB64" s="5"/>
+      <c r="EC64" s="5"/>
+      <c r="ED64" s="5"/>
+      <c r="EE64" s="5"/>
+      <c r="EF64" s="5"/>
+      <c r="EG64" s="5"/>
+      <c r="EH64" s="5"/>
+      <c r="EI64" s="5"/>
+      <c r="EJ64" s="5"/>
+      <c r="EK64" s="5"/>
+      <c r="EL64" s="5"/>
+      <c r="EM64" s="5"/>
+      <c r="EN64" s="5"/>
+      <c r="EO64" s="5"/>
+      <c r="EP64" s="5"/>
+      <c r="EQ64" s="5"/>
+      <c r="ER64" s="5"/>
+      <c r="ES64" s="5"/>
+      <c r="ET64" s="5"/>
+      <c r="EU64" s="5"/>
+      <c r="EV64" s="5"/>
+      <c r="EW64" s="5"/>
+      <c r="EX64" s="5"/>
+      <c r="EY64" s="5"/>
+      <c r="EZ64" s="5"/>
+      <c r="FA64" s="5"/>
+      <c r="FB64" s="5"/>
+      <c r="FC64" s="5"/>
+      <c r="FD64" s="5"/>
+      <c r="FE64" s="5"/>
+      <c r="FF64" s="5"/>
+      <c r="FG64" s="5"/>
+      <c r="FH64" s="5"/>
+      <c r="FI64" s="5"/>
+      <c r="FJ64" s="5"/>
+      <c r="FK64" s="5"/>
+      <c r="FL64" s="5"/>
+      <c r="FM64" s="5"/>
+      <c r="FN64" s="5"/>
+      <c r="FO64" s="5"/>
+      <c r="FP64" s="5"/>
+      <c r="FQ64" s="5"/>
+      <c r="FR64" s="5"/>
+      <c r="FS64" s="5"/>
+      <c r="FT64" s="5"/>
+      <c r="FU64" s="5"/>
+      <c r="FV64" s="5"/>
+      <c r="FW64" s="5"/>
+      <c r="FX64" s="5"/>
+      <c r="FY64" s="5"/>
+      <c r="FZ64" s="5"/>
+      <c r="GA64" s="5"/>
+      <c r="GB64" s="5"/>
+      <c r="GC64" s="5"/>
+      <c r="GD64" s="5"/>
+      <c r="GE64" s="5"/>
+      <c r="GF64" s="5"/>
+      <c r="GG64" s="5"/>
+      <c r="GH64" s="5"/>
+      <c r="GI64" s="5"/>
+      <c r="GJ64" s="5"/>
+      <c r="GK64" s="5"/>
+      <c r="GL64" s="5"/>
+      <c r="GM64" s="5"/>
+      <c r="GN64" s="5"/>
+      <c r="GO64" s="5"/>
+      <c r="GP64" s="5"/>
+      <c r="GQ64" s="5"/>
+      <c r="GR64" s="5"/>
+      <c r="GS64" s="5"/>
+      <c r="GT64" s="5"/>
+      <c r="GU64" s="5"/>
+      <c r="GV64" s="5"/>
+      <c r="GW64" s="5"/>
+      <c r="GX64" s="5"/>
+      <c r="GY64" s="5"/>
+      <c r="GZ64" s="5"/>
+      <c r="HA64" s="5"/>
+      <c r="HB64" s="5"/>
+      <c r="HC64" s="5"/>
+      <c r="HD64" s="5"/>
+      <c r="HE64" s="5"/>
+      <c r="HF64" s="5"/>
+      <c r="HG64" s="5"/>
+      <c r="HH64" s="5"/>
+      <c r="HI64" s="5"/>
+      <c r="HJ64" s="5"/>
+      <c r="HK64" s="5"/>
+      <c r="HL64" s="5"/>
+      <c r="HM64" s="5"/>
+      <c r="HN64" s="5"/>
+      <c r="HO64" s="5"/>
+      <c r="HP64" s="5"/>
+      <c r="HQ64" s="5"/>
+      <c r="HR64" s="5"/>
+      <c r="HS64" s="5"/>
+      <c r="HT64" s="5"/>
+      <c r="HU64" s="5"/>
+      <c r="HV64" s="5"/>
+      <c r="HW64" s="5"/>
+      <c r="HX64" s="5"/>
+      <c r="HY64" s="5"/>
+      <c r="HZ64" s="5"/>
+      <c r="IA64" s="5"/>
+      <c r="IB64" s="5"/>
+      <c r="IC64" s="5"/>
+      <c r="ID64" s="5"/>
+      <c r="IE64" s="5"/>
+      <c r="IF64" s="5"/>
+      <c r="IG64" s="5"/>
+      <c r="IH64" s="5"/>
+      <c r="II64" s="5"/>
+      <c r="IJ64" s="5"/>
+      <c r="IK64" s="5"/>
+      <c r="IL64" s="5"/>
+      <c r="IM64" s="5"/>
+      <c r="IN64" s="5"/>
+      <c r="IO64" s="5"/>
+      <c r="IP64" s="5"/>
+      <c r="IQ64" s="5"/>
+      <c r="IR64" s="5"/>
+      <c r="IS64" s="5"/>
+      <c r="IT64" s="5"/>
+      <c r="IU64" s="5"/>
+      <c r="IV64" s="5"/>
+      <c r="IW64" s="5"/>
+      <c r="IX64" s="5"/>
+      <c r="IY64" s="5"/>
+      <c r="IZ64" s="5"/>
+      <c r="JA64" s="5"/>
+      <c r="JB64" s="5"/>
+      <c r="JC64" s="5"/>
+      <c r="JD64" s="5"/>
+      <c r="JE64" s="5"/>
+      <c r="JF64" s="5"/>
+      <c r="JG64" s="5"/>
+      <c r="JH64" s="5"/>
+      <c r="JI64" s="5"/>
+      <c r="JJ64" s="5"/>
+      <c r="JK64" s="5"/>
+      <c r="JL64" s="5"/>
+      <c r="JM64" s="5"/>
+      <c r="JN64" s="5"/>
+      <c r="JO64" s="5"/>
+      <c r="JP64" s="5"/>
+      <c r="JQ64" s="5"/>
+      <c r="JR64" s="5"/>
+      <c r="JS64" s="5"/>
+      <c r="JT64" s="5"/>
+      <c r="JU64" s="5"/>
+      <c r="JV64" s="5"/>
+      <c r="JW64" s="5"/>
+      <c r="JX64" s="5"/>
+      <c r="JY64" s="5"/>
+      <c r="JZ64" s="5"/>
+      <c r="KA64" s="5"/>
+      <c r="KB64" s="5"/>
+      <c r="KC64" s="5"/>
+      <c r="KD64" s="5"/>
+      <c r="KE64" s="5"/>
+      <c r="KF64" s="5"/>
+      <c r="KG64" s="5"/>
+      <c r="KH64" s="5"/>
+      <c r="KI64" s="5"/>
+      <c r="KJ64" s="5"/>
+      <c r="KK64" s="5"/>
+      <c r="KL64" s="5"/>
+      <c r="KM64" s="5"/>
+      <c r="KN64" s="5"/>
+      <c r="KO64" s="5"/>
+      <c r="KP64" s="5"/>
+      <c r="KQ64" s="5"/>
+      <c r="KR64" s="5"/>
+      <c r="KS64" s="5"/>
+      <c r="KT64" s="5"/>
+      <c r="KU64" s="5"/>
+      <c r="KV64" s="5"/>
+      <c r="KW64" s="5"/>
+      <c r="KX64" s="5"/>
+      <c r="KY64" s="5"/>
+      <c r="KZ64" s="5"/>
+      <c r="LA64" s="5"/>
+      <c r="LB64" s="5"/>
+      <c r="LC64" s="5"/>
+      <c r="LD64" s="5"/>
+      <c r="LE64" s="5"/>
+      <c r="LF64" s="5"/>
+      <c r="LG64" s="5"/>
+      <c r="LH64" s="5"/>
+      <c r="LI64" s="5"/>
+      <c r="LJ64" s="5"/>
+      <c r="LK64" s="5"/>
+      <c r="LL64" s="5"/>
+      <c r="LM64" s="5"/>
+      <c r="LN64" s="5"/>
+      <c r="LO64" s="5"/>
+      <c r="LP64" s="5"/>
+      <c r="LQ64" s="5"/>
+      <c r="LR64" s="5"/>
+      <c r="LS64" s="5"/>
+      <c r="LT64" s="5"/>
+      <c r="LU64" s="5"/>
+      <c r="LV64" s="5"/>
+      <c r="LW64" s="5"/>
+      <c r="LX64" s="5"/>
+      <c r="LY64" s="5"/>
+      <c r="LZ64" s="5"/>
+      <c r="MA64" s="5"/>
+      <c r="MB64" s="5"/>
+      <c r="MC64" s="5"/>
+      <c r="MD64" s="5"/>
+      <c r="ME64" s="5"/>
+      <c r="MF64" s="5"/>
+      <c r="MG64" s="5"/>
+      <c r="MH64" s="5"/>
+      <c r="MI64" s="5"/>
+      <c r="MJ64" s="5"/>
+      <c r="MK64" s="5"/>
+      <c r="ML64" s="5"/>
+      <c r="MM64" s="5"/>
+      <c r="MN64" s="5"/>
+      <c r="MO64" s="5"/>
+      <c r="MP64" s="5"/>
+      <c r="MQ64" s="5"/>
+      <c r="MR64" s="5"/>
+      <c r="MS64" s="5"/>
+      <c r="MT64" s="5"/>
+      <c r="MU64" s="5"/>
+      <c r="MV64" s="5"/>
+      <c r="MW64" s="5"/>
+      <c r="MX64" s="5"/>
+      <c r="MY64" s="5"/>
+      <c r="MZ64" s="5"/>
+      <c r="NA64" s="5"/>
+      <c r="NB64" s="5"/>
+      <c r="NC64" s="5"/>
+      <c r="ND64" s="5"/>
+      <c r="NE64" s="5"/>
+      <c r="NF64" s="5"/>
+      <c r="NG64" s="5"/>
+      <c r="NH64" s="5"/>
+      <c r="NI64" s="5"/>
+      <c r="NJ64" s="5"/>
+      <c r="NK64" s="5"/>
+      <c r="NL64" s="5"/>
+      <c r="NM64" s="5"/>
+      <c r="NN64" s="5"/>
+      <c r="NO64" s="5"/>
+      <c r="NP64" s="5"/>
+      <c r="NQ64" s="5"/>
+      <c r="NR64" s="5"/>
+      <c r="NS64" s="5"/>
+      <c r="NT64" s="5"/>
+      <c r="NU64" s="5"/>
+      <c r="NV64" s="5"/>
+      <c r="NW64" s="5"/>
+      <c r="NX64" s="5"/>
+      <c r="NY64" s="5"/>
+      <c r="NZ64" s="5"/>
+      <c r="OA64" s="5"/>
+      <c r="OB64" s="5"/>
+      <c r="OC64" s="5"/>
+      <c r="OD64" s="5"/>
+      <c r="OE64" s="5"/>
+      <c r="OF64" s="5"/>
+      <c r="OG64" s="5"/>
+      <c r="OH64" s="5"/>
+      <c r="OI64" s="5"/>
+      <c r="OJ64" s="5"/>
+      <c r="OK64" s="5"/>
+      <c r="OL64" s="5"/>
+      <c r="OM64" s="5"/>
+      <c r="ON64" s="5"/>
+      <c r="OO64" s="5"/>
+      <c r="OP64" s="5"/>
+      <c r="OQ64" s="5"/>
+      <c r="OR64" s="5"/>
+      <c r="OS64" s="5"/>
+      <c r="OT64" s="5"/>
+      <c r="OU64" s="5"/>
+      <c r="OV64" s="5"/>
+      <c r="OW64" s="5"/>
+      <c r="OX64" s="5"/>
+      <c r="OY64" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="OZ64" s="5"/>
+      <c r="PA64" s="5"/>
+      <c r="PB64" s="5"/>
+      <c r="PC64" s="5"/>
+      <c r="PD64" s="5"/>
+      <c r="PE64" s="5"/>
+      <c r="PF64" s="5"/>
+      <c r="PG64" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="PH64" s="5"/>
+      <c r="PI64" s="5"/>
+      <c r="PJ64" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:PI1"/>
+    <mergeCell ref="A1:PJ1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Part2_PlatformBenchmarks_Results_v1.0.0.xlsx
+++ b/Part2_PlatformBenchmarks_Results_v1.0.0.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="511">
   <si>
     <t xml:space="preserve">Arduino Benchmark Suite – Part 2: Platform Benchmarks</t>
   </si>
@@ -1502,6 +1502,15 @@
   </si>
   <si>
     <t xml:space="preserve">Accuracy (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVRAM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Writes (bytes/ms)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reads (bytes/ms)</t>
   </si>
   <si>
     <t xml:space="preserve">Touch</t>
@@ -1937,7 +1946,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:PJ64"/>
+  <dimension ref="A1:PJ66"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.31"/>
@@ -4086,7 +4095,9 @@
       <c r="OU4" s="5"/>
       <c r="OV4" s="5"/>
       <c r="OW4" s="5"/>
-      <c r="OX4" s="5"/>
+      <c r="OX4" s="5" t="n">
+        <v>3.45</v>
+      </c>
       <c r="OY4" s="5" t="n">
         <v>5.41</v>
       </c>
@@ -4534,7 +4545,9 @@
       <c r="OU5" s="5"/>
       <c r="OV5" s="5"/>
       <c r="OW5" s="5"/>
-      <c r="OX5" s="5"/>
+      <c r="OX5" s="5" t="n">
+        <v>0.41</v>
+      </c>
       <c r="OY5" s="5" t="s">
         <v>430</v>
       </c>
@@ -4982,7 +4995,9 @@
       <c r="OU6" s="5"/>
       <c r="OV6" s="5"/>
       <c r="OW6" s="5"/>
-      <c r="OX6" s="5"/>
+      <c r="OX6" s="5" t="n">
+        <v>4.48</v>
+      </c>
       <c r="OY6" s="5" t="n">
         <v>7.05</v>
       </c>
@@ -5430,7 +5445,9 @@
       <c r="OU7" s="5"/>
       <c r="OV7" s="5"/>
       <c r="OW7" s="5"/>
-      <c r="OX7" s="5"/>
+      <c r="OX7" s="5" t="n">
+        <v>6.24</v>
+      </c>
       <c r="OY7" s="5" t="n">
         <v>9.82</v>
       </c>
@@ -5878,7 +5895,9 @@
       <c r="OU8" s="5"/>
       <c r="OV8" s="5"/>
       <c r="OW8" s="5"/>
-      <c r="OX8" s="5"/>
+      <c r="OX8" s="5" t="n">
+        <v>5.94</v>
+      </c>
       <c r="OY8" s="5" t="n">
         <v>9.36</v>
       </c>
@@ -6326,7 +6345,9 @@
       <c r="OU9" s="5"/>
       <c r="OV9" s="5"/>
       <c r="OW9" s="5"/>
-      <c r="OX9" s="5"/>
+      <c r="OX9" s="5" t="n">
+        <v>2.89</v>
+      </c>
       <c r="OY9" s="5" t="n">
         <v>4.54</v>
       </c>
@@ -6774,7 +6795,9 @@
       <c r="OU10" s="5"/>
       <c r="OV10" s="5"/>
       <c r="OW10" s="5"/>
-      <c r="OX10" s="5"/>
+      <c r="OX10" s="5" t="n">
+        <v>5.08</v>
+      </c>
       <c r="OY10" s="5" t="n">
         <v>7.96</v>
       </c>
@@ -7222,7 +7245,9 @@
       <c r="OU11" s="5"/>
       <c r="OV11" s="5"/>
       <c r="OW11" s="5"/>
-      <c r="OX11" s="5"/>
+      <c r="OX11" s="5" t="n">
+        <v>5.52</v>
+      </c>
       <c r="OY11" s="5" t="n">
         <v>8.64</v>
       </c>
@@ -7670,7 +7695,9 @@
       <c r="OU12" s="5"/>
       <c r="OV12" s="5"/>
       <c r="OW12" s="5"/>
-      <c r="OX12" s="5"/>
+      <c r="OX12" s="5" t="n">
+        <v>5.06</v>
+      </c>
       <c r="OY12" s="5" t="n">
         <v>7.9</v>
       </c>
@@ -8118,7 +8145,9 @@
       <c r="OU13" s="5"/>
       <c r="OV13" s="5"/>
       <c r="OW13" s="5"/>
-      <c r="OX13" s="5"/>
+      <c r="OX13" s="5" t="n">
+        <v>5.99</v>
+      </c>
       <c r="OY13" s="5" t="n">
         <v>9.41</v>
       </c>
@@ -8566,7 +8595,9 @@
       <c r="OU14" s="5"/>
       <c r="OV14" s="5"/>
       <c r="OW14" s="5"/>
-      <c r="OX14" s="5"/>
+      <c r="OX14" s="5" t="n">
+        <v>35.47</v>
+      </c>
       <c r="OY14" s="5" t="n">
         <v>55.39</v>
       </c>
@@ -9014,7 +9045,9 @@
       <c r="OU15" s="5"/>
       <c r="OV15" s="5"/>
       <c r="OW15" s="5"/>
-      <c r="OX15" s="5"/>
+      <c r="OX15" s="5" t="n">
+        <v>17.76</v>
+      </c>
       <c r="OY15" s="5" t="n">
         <v>17.58</v>
       </c>
@@ -9462,7 +9495,9 @@
       <c r="OU16" s="5"/>
       <c r="OV16" s="5"/>
       <c r="OW16" s="5"/>
-      <c r="OX16" s="5"/>
+      <c r="OX16" s="5" t="n">
+        <v>11.52</v>
+      </c>
       <c r="OY16" s="5" t="n">
         <v>11.52</v>
       </c>
@@ -9910,7 +9945,9 @@
       <c r="OU17" s="5"/>
       <c r="OV17" s="5"/>
       <c r="OW17" s="5"/>
-      <c r="OX17" s="5"/>
+      <c r="OX17" s="5" t="n">
+        <v>64.85</v>
+      </c>
       <c r="OY17" s="5" t="n">
         <v>65.52</v>
       </c>
@@ -10358,7 +10395,9 @@
       <c r="OU18" s="5"/>
       <c r="OV18" s="5"/>
       <c r="OW18" s="5"/>
-      <c r="OX18" s="5"/>
+      <c r="OX18" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="OY18" s="5" t="n">
         <v>0</v>
       </c>
@@ -10806,7 +10845,9 @@
       <c r="OU19" s="5"/>
       <c r="OV19" s="5"/>
       <c r="OW19" s="5"/>
-      <c r="OX19" s="5"/>
+      <c r="OX19" s="5" t="n">
+        <v>4</v>
+      </c>
       <c r="OY19" s="5" t="n">
         <v>8</v>
       </c>
@@ -11254,7 +11295,9 @@
       <c r="OU20" s="5"/>
       <c r="OV20" s="5"/>
       <c r="OW20" s="5"/>
-      <c r="OX20" s="5"/>
+      <c r="OX20" s="5" t="n">
+        <v>116</v>
+      </c>
       <c r="OY20" s="5" t="n">
         <v>46</v>
       </c>
@@ -11702,7 +11745,9 @@
       <c r="OU21" s="5"/>
       <c r="OV21" s="5"/>
       <c r="OW21" s="5"/>
-      <c r="OX21" s="5"/>
+      <c r="OX21" s="5" t="n">
+        <v>0.003</v>
+      </c>
       <c r="OY21" s="5" t="n">
         <v>0.003</v>
       </c>
@@ -12150,7 +12195,9 @@
       <c r="OU22" s="5"/>
       <c r="OV22" s="5"/>
       <c r="OW22" s="5"/>
-      <c r="OX22" s="5"/>
+      <c r="OX22" s="5" t="n">
+        <v>2.1</v>
+      </c>
       <c r="OY22" s="5" t="n">
         <v>0.5</v>
       </c>
@@ -12598,7 +12645,9 @@
       <c r="OU23" s="5"/>
       <c r="OV23" s="5"/>
       <c r="OW23" s="5"/>
-      <c r="OX23" s="5"/>
+      <c r="OX23" s="5" t="n">
+        <v>12</v>
+      </c>
       <c r="OY23" s="5" t="n">
         <v>344</v>
       </c>
@@ -13046,7 +13095,9 @@
       <c r="OU24" s="5"/>
       <c r="OV24" s="5"/>
       <c r="OW24" s="5"/>
-      <c r="OX24" s="5"/>
+      <c r="OX24" s="5" t="n">
+        <v>53</v>
+      </c>
       <c r="OY24" s="5" t="n">
         <v>43</v>
       </c>
@@ -13494,7 +13545,9 @@
       <c r="OU25" s="5"/>
       <c r="OV25" s="5"/>
       <c r="OW25" s="5"/>
-      <c r="OX25" s="5"/>
+      <c r="OX25" s="5" t="n">
+        <v>5.6</v>
+      </c>
       <c r="OY25" s="5" t="n">
         <v>2.67</v>
       </c>
@@ -13942,7 +13995,9 @@
       <c r="OU26" s="5"/>
       <c r="OV26" s="5"/>
       <c r="OW26" s="5"/>
-      <c r="OX26" s="5"/>
+      <c r="OX26" s="5" t="n">
+        <v>7.15</v>
+      </c>
       <c r="OY26" s="5" t="n">
         <v>0.04</v>
       </c>
@@ -14390,7 +14445,9 @@
       <c r="OU27" s="5"/>
       <c r="OV27" s="5"/>
       <c r="OW27" s="5"/>
-      <c r="OX27" s="5"/>
+      <c r="OX27" s="5" t="n">
+        <v>16.84</v>
+      </c>
       <c r="OY27" s="5" t="n">
         <v>0.04</v>
       </c>
@@ -14838,7 +14895,9 @@
       <c r="OU28" s="5"/>
       <c r="OV28" s="5"/>
       <c r="OW28" s="5"/>
-      <c r="OX28" s="5"/>
+      <c r="OX28" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OY28" s="5" t="s">
         <v>430</v>
       </c>
@@ -15286,7 +15345,9 @@
       <c r="OU29" s="5"/>
       <c r="OV29" s="5"/>
       <c r="OW29" s="5"/>
-      <c r="OX29" s="5"/>
+      <c r="OX29" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OY29" s="5" t="s">
         <v>430</v>
       </c>
@@ -15734,7 +15795,9 @@
       <c r="OU30" s="5"/>
       <c r="OV30" s="5"/>
       <c r="OW30" s="5"/>
-      <c r="OX30" s="5"/>
+      <c r="OX30" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OY30" s="5" t="s">
         <v>430</v>
       </c>
@@ -16182,7 +16245,9 @@
       <c r="OU31" s="5"/>
       <c r="OV31" s="5"/>
       <c r="OW31" s="5"/>
-      <c r="OX31" s="5"/>
+      <c r="OX31" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OY31" s="5" t="s">
         <v>430</v>
       </c>
@@ -16630,7 +16695,9 @@
       <c r="OU32" s="5"/>
       <c r="OV32" s="5"/>
       <c r="OW32" s="5"/>
-      <c r="OX32" s="5"/>
+      <c r="OX32" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OY32" s="5" t="s">
         <v>430</v>
       </c>
@@ -17078,7 +17145,9 @@
       <c r="OU33" s="5"/>
       <c r="OV33" s="5"/>
       <c r="OW33" s="5"/>
-      <c r="OX33" s="5"/>
+      <c r="OX33" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OY33" s="5" t="s">
         <v>430</v>
       </c>
@@ -17526,7 +17595,9 @@
       <c r="OU34" s="5"/>
       <c r="OV34" s="5"/>
       <c r="OW34" s="5"/>
-      <c r="OX34" s="5"/>
+      <c r="OX34" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OY34" s="5" t="s">
         <v>430</v>
       </c>
@@ -17974,7 +18045,9 @@
       <c r="OU35" s="5"/>
       <c r="OV35" s="5"/>
       <c r="OW35" s="5"/>
-      <c r="OX35" s="5"/>
+      <c r="OX35" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OY35" s="5" t="s">
         <v>430</v>
       </c>
@@ -18422,7 +18495,9 @@
       <c r="OU36" s="5"/>
       <c r="OV36" s="5"/>
       <c r="OW36" s="5"/>
-      <c r="OX36" s="5"/>
+      <c r="OX36" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OY36" s="5" t="s">
         <v>430</v>
       </c>
@@ -18870,7 +18945,9 @@
       <c r="OU37" s="5"/>
       <c r="OV37" s="5"/>
       <c r="OW37" s="5"/>
-      <c r="OX37" s="5"/>
+      <c r="OX37" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OY37" s="5" t="s">
         <v>430</v>
       </c>
@@ -19318,7 +19395,9 @@
       <c r="OU38" s="5"/>
       <c r="OV38" s="5"/>
       <c r="OW38" s="5"/>
-      <c r="OX38" s="5"/>
+      <c r="OX38" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OY38" s="5" t="s">
         <v>430</v>
       </c>
@@ -19766,7 +19845,9 @@
       <c r="OU39" s="5"/>
       <c r="OV39" s="5"/>
       <c r="OW39" s="5"/>
-      <c r="OX39" s="5"/>
+      <c r="OX39" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OY39" s="5" t="s">
         <v>430</v>
       </c>
@@ -20214,7 +20295,9 @@
       <c r="OU40" s="5"/>
       <c r="OV40" s="5"/>
       <c r="OW40" s="5"/>
-      <c r="OX40" s="5"/>
+      <c r="OX40" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OY40" s="5" t="s">
         <v>430</v>
       </c>
@@ -20662,7 +20745,9 @@
       <c r="OU41" s="5"/>
       <c r="OV41" s="5"/>
       <c r="OW41" s="5"/>
-      <c r="OX41" s="5"/>
+      <c r="OX41" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OY41" s="5" t="s">
         <v>430</v>
       </c>
@@ -21110,7 +21195,9 @@
       <c r="OU42" s="5"/>
       <c r="OV42" s="5"/>
       <c r="OW42" s="5"/>
-      <c r="OX42" s="5"/>
+      <c r="OX42" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OY42" s="5" t="s">
         <v>430</v>
       </c>
@@ -21558,7 +21645,9 @@
       <c r="OU43" s="5"/>
       <c r="OV43" s="5"/>
       <c r="OW43" s="5"/>
-      <c r="OX43" s="5"/>
+      <c r="OX43" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OY43" s="5" t="s">
         <v>430</v>
       </c>
@@ -22006,7 +22095,9 @@
       <c r="OU44" s="5"/>
       <c r="OV44" s="5"/>
       <c r="OW44" s="5"/>
-      <c r="OX44" s="5"/>
+      <c r="OX44" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OY44" s="5" t="s">
         <v>430</v>
       </c>
@@ -22454,7 +22545,9 @@
       <c r="OU45" s="5"/>
       <c r="OV45" s="5"/>
       <c r="OW45" s="5"/>
-      <c r="OX45" s="5"/>
+      <c r="OX45" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OY45" s="5" t="s">
         <v>430</v>
       </c>
@@ -22902,7 +22995,9 @@
       <c r="OU46" s="5"/>
       <c r="OV46" s="5"/>
       <c r="OW46" s="5"/>
-      <c r="OX46" s="5"/>
+      <c r="OX46" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OY46" s="5" t="s">
         <v>430</v>
       </c>
@@ -23350,7 +23445,9 @@
       <c r="OU47" s="5"/>
       <c r="OV47" s="5"/>
       <c r="OW47" s="5"/>
-      <c r="OX47" s="5"/>
+      <c r="OX47" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OY47" s="5" t="s">
         <v>430</v>
       </c>
@@ -23798,7 +23895,9 @@
       <c r="OU48" s="5"/>
       <c r="OV48" s="5"/>
       <c r="OW48" s="5"/>
-      <c r="OX48" s="5"/>
+      <c r="OX48" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OY48" s="5" t="s">
         <v>430</v>
       </c>
@@ -24246,7 +24345,9 @@
       <c r="OU49" s="5"/>
       <c r="OV49" s="5"/>
       <c r="OW49" s="5"/>
-      <c r="OX49" s="5"/>
+      <c r="OX49" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OY49" s="5" t="s">
         <v>430</v>
       </c>
@@ -24694,7 +24795,9 @@
       <c r="OU50" s="5"/>
       <c r="OV50" s="5"/>
       <c r="OW50" s="5"/>
-      <c r="OX50" s="5"/>
+      <c r="OX50" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OY50" s="5" t="s">
         <v>430</v>
       </c>
@@ -25142,7 +25245,9 @@
       <c r="OU51" s="5"/>
       <c r="OV51" s="5"/>
       <c r="OW51" s="5"/>
-      <c r="OX51" s="5"/>
+      <c r="OX51" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OY51" s="5" t="s">
         <v>430</v>
       </c>
@@ -25590,7 +25695,9 @@
       <c r="OU52" s="5"/>
       <c r="OV52" s="5"/>
       <c r="OW52" s="5"/>
-      <c r="OX52" s="5"/>
+      <c r="OX52" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OY52" s="5" t="s">
         <v>430</v>
       </c>
@@ -26038,7 +26145,9 @@
       <c r="OU53" s="5"/>
       <c r="OV53" s="5"/>
       <c r="OW53" s="5"/>
-      <c r="OX53" s="5"/>
+      <c r="OX53" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OY53" s="5" t="s">
         <v>430</v>
       </c>
@@ -26486,7 +26595,9 @@
       <c r="OU54" s="5"/>
       <c r="OV54" s="5"/>
       <c r="OW54" s="5"/>
-      <c r="OX54" s="5"/>
+      <c r="OX54" s="5" t="n">
+        <v>910</v>
+      </c>
       <c r="OY54" s="5" t="s">
         <v>430</v>
       </c>
@@ -26934,7 +27045,9 @@
       <c r="OU55" s="5"/>
       <c r="OV55" s="5"/>
       <c r="OW55" s="5"/>
-      <c r="OX55" s="5"/>
+      <c r="OX55" s="5" t="n">
+        <v>1010</v>
+      </c>
       <c r="OY55" s="5" t="s">
         <v>430</v>
       </c>
@@ -27382,7 +27495,9 @@
       <c r="OU56" s="5"/>
       <c r="OV56" s="5"/>
       <c r="OW56" s="5"/>
-      <c r="OX56" s="5"/>
+      <c r="OX56" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OY56" s="5" t="s">
         <v>430</v>
       </c>
@@ -27830,7 +27945,9 @@
       <c r="OU57" s="5"/>
       <c r="OV57" s="5"/>
       <c r="OW57" s="5"/>
-      <c r="OX57" s="5"/>
+      <c r="OX57" s="5" t="n">
+        <v>2.86</v>
+      </c>
       <c r="OY57" s="5" t="s">
         <v>430</v>
       </c>
@@ -27850,10 +27967,10 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="B58" s="5" t="s">
         <v>496</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>497</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>430</v>
@@ -28278,7 +28395,9 @@
       <c r="OU58" s="5"/>
       <c r="OV58" s="5"/>
       <c r="OW58" s="5"/>
-      <c r="OX58" s="5"/>
+      <c r="OX58" s="5" t="n">
+        <v>2.16</v>
+      </c>
       <c r="OY58" s="5" t="s">
         <v>430</v>
       </c>
@@ -28298,10 +28417,10 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="B59" s="5" t="s">
         <v>498</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>499</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>430</v>
@@ -28726,7 +28845,9 @@
       <c r="OU59" s="5"/>
       <c r="OV59" s="5"/>
       <c r="OW59" s="5"/>
-      <c r="OX59" s="5"/>
+      <c r="OX59" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OY59" s="5" t="s">
         <v>430</v>
       </c>
@@ -28746,7 +28867,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="4" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>500</v>
@@ -29174,7 +29295,9 @@
       <c r="OU60" s="5"/>
       <c r="OV60" s="5"/>
       <c r="OW60" s="5"/>
-      <c r="OX60" s="5"/>
+      <c r="OX60" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OY60" s="5" t="s">
         <v>430</v>
       </c>
@@ -29622,7 +29745,9 @@
       <c r="OU61" s="5"/>
       <c r="OV61" s="5"/>
       <c r="OW61" s="5"/>
-      <c r="OX61" s="5"/>
+      <c r="OX61" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OY61" s="5" t="s">
         <v>430</v>
       </c>
@@ -29642,20 +29767,20 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="B62" s="5" t="s">
         <v>503</v>
       </c>
-      <c r="B62" s="5" t="s">
-        <v>504</v>
-      </c>
-      <c r="C62" s="5" t="n">
-        <v>56</v>
+      <c r="C62" s="5" t="s">
+        <v>430</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>430</v>
       </c>
       <c r="E62" s="5"/>
-      <c r="F62" s="5" t="n">
-        <v>520</v>
+      <c r="F62" s="5" t="s">
+        <v>430</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
@@ -29689,8 +29814,8 @@
       <c r="AH62" s="5"/>
       <c r="AI62" s="5"/>
       <c r="AJ62" s="5"/>
-      <c r="AK62" s="5" t="n">
-        <v>660</v>
+      <c r="AK62" s="5" t="s">
+        <v>430</v>
       </c>
       <c r="AL62" s="5"/>
       <c r="AM62" s="5"/>
@@ -30070,9 +30195,11 @@
       <c r="OU62" s="5"/>
       <c r="OV62" s="5"/>
       <c r="OW62" s="5"/>
-      <c r="OX62" s="5"/>
-      <c r="OY62" s="5" t="n">
-        <v>992</v>
+      <c r="OX62" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="OY62" s="5" t="s">
+        <v>430</v>
       </c>
       <c r="OZ62" s="5"/>
       <c r="PA62" s="5"/>
@@ -30081,8 +30208,8 @@
       <c r="PD62" s="5"/>
       <c r="PE62" s="5"/>
       <c r="PF62" s="5"/>
-      <c r="PG62" s="5" t="n">
-        <v>484</v>
+      <c r="PG62" s="5" t="s">
+        <v>430</v>
       </c>
       <c r="PH62" s="5"/>
       <c r="PI62" s="5"/>
@@ -30090,7 +30217,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="4" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>505</v>
@@ -30098,8 +30225,8 @@
       <c r="C63" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="D63" s="5" t="n">
-        <v>86</v>
+      <c r="D63" s="5" t="s">
+        <v>430</v>
       </c>
       <c r="E63" s="5"/>
       <c r="F63" s="5" t="s">
@@ -30518,7 +30645,9 @@
       <c r="OU63" s="5"/>
       <c r="OV63" s="5"/>
       <c r="OW63" s="5"/>
-      <c r="OX63" s="5"/>
+      <c r="OX63" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="OY63" s="5" t="s">
         <v>430</v>
       </c>
@@ -30543,15 +30672,15 @@
       <c r="B64" s="5" t="s">
         <v>507</v>
       </c>
-      <c r="C64" s="5" t="s">
-        <v>430</v>
+      <c r="C64" s="5" t="n">
+        <v>56</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>430</v>
       </c>
       <c r="E64" s="5"/>
-      <c r="F64" s="5" t="s">
-        <v>430</v>
+      <c r="F64" s="5" t="n">
+        <v>520</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
@@ -30585,8 +30714,8 @@
       <c r="AH64" s="5"/>
       <c r="AI64" s="5"/>
       <c r="AJ64" s="5"/>
-      <c r="AK64" s="5" t="s">
-        <v>430</v>
+      <c r="AK64" s="5" t="n">
+        <v>660</v>
       </c>
       <c r="AL64" s="5"/>
       <c r="AM64" s="5"/>
@@ -30966,9 +31095,11 @@
       <c r="OU64" s="5"/>
       <c r="OV64" s="5"/>
       <c r="OW64" s="5"/>
-      <c r="OX64" s="5"/>
-      <c r="OY64" s="5" t="s">
-        <v>430</v>
+      <c r="OX64" s="5" t="n">
+        <v>792</v>
+      </c>
+      <c r="OY64" s="5" t="n">
+        <v>992</v>
       </c>
       <c r="OZ64" s="5"/>
       <c r="PA64" s="5"/>
@@ -30977,12 +31108,912 @@
       <c r="PD64" s="5"/>
       <c r="PE64" s="5"/>
       <c r="PF64" s="5"/>
-      <c r="PG64" s="5" t="s">
-        <v>430</v>
+      <c r="PG64" s="5" t="n">
+        <v>484</v>
       </c>
       <c r="PH64" s="5"/>
       <c r="PI64" s="5"/>
       <c r="PJ64" s="5"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>508</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="D65" s="5" t="n">
+        <v>86</v>
+      </c>
+      <c r="E65" s="5"/>
+      <c r="F65" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="G65" s="5"/>
+      <c r="H65" s="5"/>
+      <c r="I65" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="J65" s="5"/>
+      <c r="K65" s="5"/>
+      <c r="L65" s="5"/>
+      <c r="M65" s="5"/>
+      <c r="N65" s="5"/>
+      <c r="O65" s="5"/>
+      <c r="P65" s="5"/>
+      <c r="Q65" s="5"/>
+      <c r="R65" s="5"/>
+      <c r="S65" s="5"/>
+      <c r="T65" s="5"/>
+      <c r="U65" s="5"/>
+      <c r="V65" s="5"/>
+      <c r="W65" s="5"/>
+      <c r="X65" s="5"/>
+      <c r="Y65" s="5"/>
+      <c r="Z65" s="5"/>
+      <c r="AA65" s="5"/>
+      <c r="AB65" s="5"/>
+      <c r="AC65" s="5"/>
+      <c r="AD65" s="5"/>
+      <c r="AE65" s="5"/>
+      <c r="AF65" s="5"/>
+      <c r="AG65" s="5"/>
+      <c r="AH65" s="5"/>
+      <c r="AI65" s="5"/>
+      <c r="AJ65" s="5"/>
+      <c r="AK65" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="AL65" s="5"/>
+      <c r="AM65" s="5"/>
+      <c r="AN65" s="5"/>
+      <c r="AO65" s="5"/>
+      <c r="AP65" s="5"/>
+      <c r="AQ65" s="5"/>
+      <c r="AR65" s="5"/>
+      <c r="AS65" s="5"/>
+      <c r="AT65" s="5"/>
+      <c r="AU65" s="5"/>
+      <c r="AV65" s="5"/>
+      <c r="AW65" s="5"/>
+      <c r="AX65" s="5"/>
+      <c r="AY65" s="5"/>
+      <c r="AZ65" s="5"/>
+      <c r="BA65" s="5"/>
+      <c r="BB65" s="5"/>
+      <c r="BC65" s="5"/>
+      <c r="BD65" s="5"/>
+      <c r="BE65" s="5"/>
+      <c r="BF65" s="5"/>
+      <c r="BG65" s="5"/>
+      <c r="BH65" s="5"/>
+      <c r="BI65" s="5"/>
+      <c r="BJ65" s="5"/>
+      <c r="BK65" s="5"/>
+      <c r="BL65" s="5"/>
+      <c r="BM65" s="5"/>
+      <c r="BN65" s="5"/>
+      <c r="BO65" s="5"/>
+      <c r="BP65" s="5"/>
+      <c r="BQ65" s="5"/>
+      <c r="BR65" s="5"/>
+      <c r="BS65" s="5"/>
+      <c r="BT65" s="5"/>
+      <c r="BU65" s="5"/>
+      <c r="BV65" s="5"/>
+      <c r="BW65" s="5"/>
+      <c r="BX65" s="5"/>
+      <c r="BY65" s="5"/>
+      <c r="BZ65" s="5"/>
+      <c r="CA65" s="5"/>
+      <c r="CB65" s="5"/>
+      <c r="CC65" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="CD65" s="5"/>
+      <c r="CE65" s="5"/>
+      <c r="CF65" s="5"/>
+      <c r="CG65" s="5"/>
+      <c r="CH65" s="5"/>
+      <c r="CI65" s="5"/>
+      <c r="CJ65" s="5"/>
+      <c r="CK65" s="5"/>
+      <c r="CL65" s="5"/>
+      <c r="CM65" s="5"/>
+      <c r="CN65" s="5"/>
+      <c r="CO65" s="5"/>
+      <c r="CP65" s="5"/>
+      <c r="CQ65" s="5"/>
+      <c r="CR65" s="5"/>
+      <c r="CS65" s="5"/>
+      <c r="CT65" s="5"/>
+      <c r="CU65" s="5"/>
+      <c r="CV65" s="5"/>
+      <c r="CW65" s="5"/>
+      <c r="CX65" s="5"/>
+      <c r="CY65" s="5"/>
+      <c r="CZ65" s="5"/>
+      <c r="DA65" s="5"/>
+      <c r="DB65" s="5"/>
+      <c r="DC65" s="5"/>
+      <c r="DD65" s="5"/>
+      <c r="DE65" s="5"/>
+      <c r="DF65" s="5"/>
+      <c r="DG65" s="5"/>
+      <c r="DH65" s="5"/>
+      <c r="DI65" s="5"/>
+      <c r="DJ65" s="5"/>
+      <c r="DK65" s="5"/>
+      <c r="DL65" s="5"/>
+      <c r="DM65" s="5"/>
+      <c r="DN65" s="5"/>
+      <c r="DO65" s="5"/>
+      <c r="DP65" s="5"/>
+      <c r="DQ65" s="5"/>
+      <c r="DR65" s="5"/>
+      <c r="DS65" s="5"/>
+      <c r="DT65" s="5"/>
+      <c r="DU65" s="5"/>
+      <c r="DV65" s="5"/>
+      <c r="DW65" s="5"/>
+      <c r="DX65" s="5"/>
+      <c r="DY65" s="5"/>
+      <c r="DZ65" s="5"/>
+      <c r="EA65" s="5"/>
+      <c r="EB65" s="5"/>
+      <c r="EC65" s="5"/>
+      <c r="ED65" s="5"/>
+      <c r="EE65" s="5"/>
+      <c r="EF65" s="5"/>
+      <c r="EG65" s="5"/>
+      <c r="EH65" s="5"/>
+      <c r="EI65" s="5"/>
+      <c r="EJ65" s="5"/>
+      <c r="EK65" s="5"/>
+      <c r="EL65" s="5"/>
+      <c r="EM65" s="5"/>
+      <c r="EN65" s="5"/>
+      <c r="EO65" s="5"/>
+      <c r="EP65" s="5"/>
+      <c r="EQ65" s="5"/>
+      <c r="ER65" s="5"/>
+      <c r="ES65" s="5"/>
+      <c r="ET65" s="5"/>
+      <c r="EU65" s="5"/>
+      <c r="EV65" s="5"/>
+      <c r="EW65" s="5"/>
+      <c r="EX65" s="5"/>
+      <c r="EY65" s="5"/>
+      <c r="EZ65" s="5"/>
+      <c r="FA65" s="5"/>
+      <c r="FB65" s="5"/>
+      <c r="FC65" s="5"/>
+      <c r="FD65" s="5"/>
+      <c r="FE65" s="5"/>
+      <c r="FF65" s="5"/>
+      <c r="FG65" s="5"/>
+      <c r="FH65" s="5"/>
+      <c r="FI65" s="5"/>
+      <c r="FJ65" s="5"/>
+      <c r="FK65" s="5"/>
+      <c r="FL65" s="5"/>
+      <c r="FM65" s="5"/>
+      <c r="FN65" s="5"/>
+      <c r="FO65" s="5"/>
+      <c r="FP65" s="5"/>
+      <c r="FQ65" s="5"/>
+      <c r="FR65" s="5"/>
+      <c r="FS65" s="5"/>
+      <c r="FT65" s="5"/>
+      <c r="FU65" s="5"/>
+      <c r="FV65" s="5"/>
+      <c r="FW65" s="5"/>
+      <c r="FX65" s="5"/>
+      <c r="FY65" s="5"/>
+      <c r="FZ65" s="5"/>
+      <c r="GA65" s="5"/>
+      <c r="GB65" s="5"/>
+      <c r="GC65" s="5"/>
+      <c r="GD65" s="5"/>
+      <c r="GE65" s="5"/>
+      <c r="GF65" s="5"/>
+      <c r="GG65" s="5"/>
+      <c r="GH65" s="5"/>
+      <c r="GI65" s="5"/>
+      <c r="GJ65" s="5"/>
+      <c r="GK65" s="5"/>
+      <c r="GL65" s="5"/>
+      <c r="GM65" s="5"/>
+      <c r="GN65" s="5"/>
+      <c r="GO65" s="5"/>
+      <c r="GP65" s="5"/>
+      <c r="GQ65" s="5"/>
+      <c r="GR65" s="5"/>
+      <c r="GS65" s="5"/>
+      <c r="GT65" s="5"/>
+      <c r="GU65" s="5"/>
+      <c r="GV65" s="5"/>
+      <c r="GW65" s="5"/>
+      <c r="GX65" s="5"/>
+      <c r="GY65" s="5"/>
+      <c r="GZ65" s="5"/>
+      <c r="HA65" s="5"/>
+      <c r="HB65" s="5"/>
+      <c r="HC65" s="5"/>
+      <c r="HD65" s="5"/>
+      <c r="HE65" s="5"/>
+      <c r="HF65" s="5"/>
+      <c r="HG65" s="5"/>
+      <c r="HH65" s="5"/>
+      <c r="HI65" s="5"/>
+      <c r="HJ65" s="5"/>
+      <c r="HK65" s="5"/>
+      <c r="HL65" s="5"/>
+      <c r="HM65" s="5"/>
+      <c r="HN65" s="5"/>
+      <c r="HO65" s="5"/>
+      <c r="HP65" s="5"/>
+      <c r="HQ65" s="5"/>
+      <c r="HR65" s="5"/>
+      <c r="HS65" s="5"/>
+      <c r="HT65" s="5"/>
+      <c r="HU65" s="5"/>
+      <c r="HV65" s="5"/>
+      <c r="HW65" s="5"/>
+      <c r="HX65" s="5"/>
+      <c r="HY65" s="5"/>
+      <c r="HZ65" s="5"/>
+      <c r="IA65" s="5"/>
+      <c r="IB65" s="5"/>
+      <c r="IC65" s="5"/>
+      <c r="ID65" s="5"/>
+      <c r="IE65" s="5"/>
+      <c r="IF65" s="5"/>
+      <c r="IG65" s="5"/>
+      <c r="IH65" s="5"/>
+      <c r="II65" s="5"/>
+      <c r="IJ65" s="5"/>
+      <c r="IK65" s="5"/>
+      <c r="IL65" s="5"/>
+      <c r="IM65" s="5"/>
+      <c r="IN65" s="5"/>
+      <c r="IO65" s="5"/>
+      <c r="IP65" s="5"/>
+      <c r="IQ65" s="5"/>
+      <c r="IR65" s="5"/>
+      <c r="IS65" s="5"/>
+      <c r="IT65" s="5"/>
+      <c r="IU65" s="5"/>
+      <c r="IV65" s="5"/>
+      <c r="IW65" s="5"/>
+      <c r="IX65" s="5"/>
+      <c r="IY65" s="5"/>
+      <c r="IZ65" s="5"/>
+      <c r="JA65" s="5"/>
+      <c r="JB65" s="5"/>
+      <c r="JC65" s="5"/>
+      <c r="JD65" s="5"/>
+      <c r="JE65" s="5"/>
+      <c r="JF65" s="5"/>
+      <c r="JG65" s="5"/>
+      <c r="JH65" s="5"/>
+      <c r="JI65" s="5"/>
+      <c r="JJ65" s="5"/>
+      <c r="JK65" s="5"/>
+      <c r="JL65" s="5"/>
+      <c r="JM65" s="5"/>
+      <c r="JN65" s="5"/>
+      <c r="JO65" s="5"/>
+      <c r="JP65" s="5"/>
+      <c r="JQ65" s="5"/>
+      <c r="JR65" s="5"/>
+      <c r="JS65" s="5"/>
+      <c r="JT65" s="5"/>
+      <c r="JU65" s="5"/>
+      <c r="JV65" s="5"/>
+      <c r="JW65" s="5"/>
+      <c r="JX65" s="5"/>
+      <c r="JY65" s="5"/>
+      <c r="JZ65" s="5"/>
+      <c r="KA65" s="5"/>
+      <c r="KB65" s="5"/>
+      <c r="KC65" s="5"/>
+      <c r="KD65" s="5"/>
+      <c r="KE65" s="5"/>
+      <c r="KF65" s="5"/>
+      <c r="KG65" s="5"/>
+      <c r="KH65" s="5"/>
+      <c r="KI65" s="5"/>
+      <c r="KJ65" s="5"/>
+      <c r="KK65" s="5"/>
+      <c r="KL65" s="5"/>
+      <c r="KM65" s="5"/>
+      <c r="KN65" s="5"/>
+      <c r="KO65" s="5"/>
+      <c r="KP65" s="5"/>
+      <c r="KQ65" s="5"/>
+      <c r="KR65" s="5"/>
+      <c r="KS65" s="5"/>
+      <c r="KT65" s="5"/>
+      <c r="KU65" s="5"/>
+      <c r="KV65" s="5"/>
+      <c r="KW65" s="5"/>
+      <c r="KX65" s="5"/>
+      <c r="KY65" s="5"/>
+      <c r="KZ65" s="5"/>
+      <c r="LA65" s="5"/>
+      <c r="LB65" s="5"/>
+      <c r="LC65" s="5"/>
+      <c r="LD65" s="5"/>
+      <c r="LE65" s="5"/>
+      <c r="LF65" s="5"/>
+      <c r="LG65" s="5"/>
+      <c r="LH65" s="5"/>
+      <c r="LI65" s="5"/>
+      <c r="LJ65" s="5"/>
+      <c r="LK65" s="5"/>
+      <c r="LL65" s="5"/>
+      <c r="LM65" s="5"/>
+      <c r="LN65" s="5"/>
+      <c r="LO65" s="5"/>
+      <c r="LP65" s="5"/>
+      <c r="LQ65" s="5"/>
+      <c r="LR65" s="5"/>
+      <c r="LS65" s="5"/>
+      <c r="LT65" s="5"/>
+      <c r="LU65" s="5"/>
+      <c r="LV65" s="5"/>
+      <c r="LW65" s="5"/>
+      <c r="LX65" s="5"/>
+      <c r="LY65" s="5"/>
+      <c r="LZ65" s="5"/>
+      <c r="MA65" s="5"/>
+      <c r="MB65" s="5"/>
+      <c r="MC65" s="5"/>
+      <c r="MD65" s="5"/>
+      <c r="ME65" s="5"/>
+      <c r="MF65" s="5"/>
+      <c r="MG65" s="5"/>
+      <c r="MH65" s="5"/>
+      <c r="MI65" s="5"/>
+      <c r="MJ65" s="5"/>
+      <c r="MK65" s="5"/>
+      <c r="ML65" s="5"/>
+      <c r="MM65" s="5"/>
+      <c r="MN65" s="5"/>
+      <c r="MO65" s="5"/>
+      <c r="MP65" s="5"/>
+      <c r="MQ65" s="5"/>
+      <c r="MR65" s="5"/>
+      <c r="MS65" s="5"/>
+      <c r="MT65" s="5"/>
+      <c r="MU65" s="5"/>
+      <c r="MV65" s="5"/>
+      <c r="MW65" s="5"/>
+      <c r="MX65" s="5"/>
+      <c r="MY65" s="5"/>
+      <c r="MZ65" s="5"/>
+      <c r="NA65" s="5"/>
+      <c r="NB65" s="5"/>
+      <c r="NC65" s="5"/>
+      <c r="ND65" s="5"/>
+      <c r="NE65" s="5"/>
+      <c r="NF65" s="5"/>
+      <c r="NG65" s="5"/>
+      <c r="NH65" s="5"/>
+      <c r="NI65" s="5"/>
+      <c r="NJ65" s="5"/>
+      <c r="NK65" s="5"/>
+      <c r="NL65" s="5"/>
+      <c r="NM65" s="5"/>
+      <c r="NN65" s="5"/>
+      <c r="NO65" s="5"/>
+      <c r="NP65" s="5"/>
+      <c r="NQ65" s="5"/>
+      <c r="NR65" s="5"/>
+      <c r="NS65" s="5"/>
+      <c r="NT65" s="5"/>
+      <c r="NU65" s="5"/>
+      <c r="NV65" s="5"/>
+      <c r="NW65" s="5"/>
+      <c r="NX65" s="5"/>
+      <c r="NY65" s="5"/>
+      <c r="NZ65" s="5"/>
+      <c r="OA65" s="5"/>
+      <c r="OB65" s="5"/>
+      <c r="OC65" s="5"/>
+      <c r="OD65" s="5"/>
+      <c r="OE65" s="5"/>
+      <c r="OF65" s="5"/>
+      <c r="OG65" s="5"/>
+      <c r="OH65" s="5"/>
+      <c r="OI65" s="5"/>
+      <c r="OJ65" s="5"/>
+      <c r="OK65" s="5"/>
+      <c r="OL65" s="5"/>
+      <c r="OM65" s="5"/>
+      <c r="ON65" s="5"/>
+      <c r="OO65" s="5"/>
+      <c r="OP65" s="5"/>
+      <c r="OQ65" s="5"/>
+      <c r="OR65" s="5"/>
+      <c r="OS65" s="5"/>
+      <c r="OT65" s="5"/>
+      <c r="OU65" s="5"/>
+      <c r="OV65" s="5"/>
+      <c r="OW65" s="5"/>
+      <c r="OX65" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="OY65" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="OZ65" s="5"/>
+      <c r="PA65" s="5"/>
+      <c r="PB65" s="5"/>
+      <c r="PC65" s="5"/>
+      <c r="PD65" s="5"/>
+      <c r="PE65" s="5"/>
+      <c r="PF65" s="5"/>
+      <c r="PG65" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="PH65" s="5"/>
+      <c r="PI65" s="5"/>
+      <c r="PJ65" s="5"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>510</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="E66" s="5"/>
+      <c r="F66" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="G66" s="5"/>
+      <c r="H66" s="5"/>
+      <c r="I66" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="J66" s="5"/>
+      <c r="K66" s="5"/>
+      <c r="L66" s="5"/>
+      <c r="M66" s="5"/>
+      <c r="N66" s="5"/>
+      <c r="O66" s="5"/>
+      <c r="P66" s="5"/>
+      <c r="Q66" s="5"/>
+      <c r="R66" s="5"/>
+      <c r="S66" s="5"/>
+      <c r="T66" s="5"/>
+      <c r="U66" s="5"/>
+      <c r="V66" s="5"/>
+      <c r="W66" s="5"/>
+      <c r="X66" s="5"/>
+      <c r="Y66" s="5"/>
+      <c r="Z66" s="5"/>
+      <c r="AA66" s="5"/>
+      <c r="AB66" s="5"/>
+      <c r="AC66" s="5"/>
+      <c r="AD66" s="5"/>
+      <c r="AE66" s="5"/>
+      <c r="AF66" s="5"/>
+      <c r="AG66" s="5"/>
+      <c r="AH66" s="5"/>
+      <c r="AI66" s="5"/>
+      <c r="AJ66" s="5"/>
+      <c r="AK66" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="AL66" s="5"/>
+      <c r="AM66" s="5"/>
+      <c r="AN66" s="5"/>
+      <c r="AO66" s="5"/>
+      <c r="AP66" s="5"/>
+      <c r="AQ66" s="5"/>
+      <c r="AR66" s="5"/>
+      <c r="AS66" s="5"/>
+      <c r="AT66" s="5"/>
+      <c r="AU66" s="5"/>
+      <c r="AV66" s="5"/>
+      <c r="AW66" s="5"/>
+      <c r="AX66" s="5"/>
+      <c r="AY66" s="5"/>
+      <c r="AZ66" s="5"/>
+      <c r="BA66" s="5"/>
+      <c r="BB66" s="5"/>
+      <c r="BC66" s="5"/>
+      <c r="BD66" s="5"/>
+      <c r="BE66" s="5"/>
+      <c r="BF66" s="5"/>
+      <c r="BG66" s="5"/>
+      <c r="BH66" s="5"/>
+      <c r="BI66" s="5"/>
+      <c r="BJ66" s="5"/>
+      <c r="BK66" s="5"/>
+      <c r="BL66" s="5"/>
+      <c r="BM66" s="5"/>
+      <c r="BN66" s="5"/>
+      <c r="BO66" s="5"/>
+      <c r="BP66" s="5"/>
+      <c r="BQ66" s="5"/>
+      <c r="BR66" s="5"/>
+      <c r="BS66" s="5"/>
+      <c r="BT66" s="5"/>
+      <c r="BU66" s="5"/>
+      <c r="BV66" s="5"/>
+      <c r="BW66" s="5"/>
+      <c r="BX66" s="5"/>
+      <c r="BY66" s="5"/>
+      <c r="BZ66" s="5"/>
+      <c r="CA66" s="5"/>
+      <c r="CB66" s="5"/>
+      <c r="CC66" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="CD66" s="5"/>
+      <c r="CE66" s="5"/>
+      <c r="CF66" s="5"/>
+      <c r="CG66" s="5"/>
+      <c r="CH66" s="5"/>
+      <c r="CI66" s="5"/>
+      <c r="CJ66" s="5"/>
+      <c r="CK66" s="5"/>
+      <c r="CL66" s="5"/>
+      <c r="CM66" s="5"/>
+      <c r="CN66" s="5"/>
+      <c r="CO66" s="5"/>
+      <c r="CP66" s="5"/>
+      <c r="CQ66" s="5"/>
+      <c r="CR66" s="5"/>
+      <c r="CS66" s="5"/>
+      <c r="CT66" s="5"/>
+      <c r="CU66" s="5"/>
+      <c r="CV66" s="5"/>
+      <c r="CW66" s="5"/>
+      <c r="CX66" s="5"/>
+      <c r="CY66" s="5"/>
+      <c r="CZ66" s="5"/>
+      <c r="DA66" s="5"/>
+      <c r="DB66" s="5"/>
+      <c r="DC66" s="5"/>
+      <c r="DD66" s="5"/>
+      <c r="DE66" s="5"/>
+      <c r="DF66" s="5"/>
+      <c r="DG66" s="5"/>
+      <c r="DH66" s="5"/>
+      <c r="DI66" s="5"/>
+      <c r="DJ66" s="5"/>
+      <c r="DK66" s="5"/>
+      <c r="DL66" s="5"/>
+      <c r="DM66" s="5"/>
+      <c r="DN66" s="5"/>
+      <c r="DO66" s="5"/>
+      <c r="DP66" s="5"/>
+      <c r="DQ66" s="5"/>
+      <c r="DR66" s="5"/>
+      <c r="DS66" s="5"/>
+      <c r="DT66" s="5"/>
+      <c r="DU66" s="5"/>
+      <c r="DV66" s="5"/>
+      <c r="DW66" s="5"/>
+      <c r="DX66" s="5"/>
+      <c r="DY66" s="5"/>
+      <c r="DZ66" s="5"/>
+      <c r="EA66" s="5"/>
+      <c r="EB66" s="5"/>
+      <c r="EC66" s="5"/>
+      <c r="ED66" s="5"/>
+      <c r="EE66" s="5"/>
+      <c r="EF66" s="5"/>
+      <c r="EG66" s="5"/>
+      <c r="EH66" s="5"/>
+      <c r="EI66" s="5"/>
+      <c r="EJ66" s="5"/>
+      <c r="EK66" s="5"/>
+      <c r="EL66" s="5"/>
+      <c r="EM66" s="5"/>
+      <c r="EN66" s="5"/>
+      <c r="EO66" s="5"/>
+      <c r="EP66" s="5"/>
+      <c r="EQ66" s="5"/>
+      <c r="ER66" s="5"/>
+      <c r="ES66" s="5"/>
+      <c r="ET66" s="5"/>
+      <c r="EU66" s="5"/>
+      <c r="EV66" s="5"/>
+      <c r="EW66" s="5"/>
+      <c r="EX66" s="5"/>
+      <c r="EY66" s="5"/>
+      <c r="EZ66" s="5"/>
+      <c r="FA66" s="5"/>
+      <c r="FB66" s="5"/>
+      <c r="FC66" s="5"/>
+      <c r="FD66" s="5"/>
+      <c r="FE66" s="5"/>
+      <c r="FF66" s="5"/>
+      <c r="FG66" s="5"/>
+      <c r="FH66" s="5"/>
+      <c r="FI66" s="5"/>
+      <c r="FJ66" s="5"/>
+      <c r="FK66" s="5"/>
+      <c r="FL66" s="5"/>
+      <c r="FM66" s="5"/>
+      <c r="FN66" s="5"/>
+      <c r="FO66" s="5"/>
+      <c r="FP66" s="5"/>
+      <c r="FQ66" s="5"/>
+      <c r="FR66" s="5"/>
+      <c r="FS66" s="5"/>
+      <c r="FT66" s="5"/>
+      <c r="FU66" s="5"/>
+      <c r="FV66" s="5"/>
+      <c r="FW66" s="5"/>
+      <c r="FX66" s="5"/>
+      <c r="FY66" s="5"/>
+      <c r="FZ66" s="5"/>
+      <c r="GA66" s="5"/>
+      <c r="GB66" s="5"/>
+      <c r="GC66" s="5"/>
+      <c r="GD66" s="5"/>
+      <c r="GE66" s="5"/>
+      <c r="GF66" s="5"/>
+      <c r="GG66" s="5"/>
+      <c r="GH66" s="5"/>
+      <c r="GI66" s="5"/>
+      <c r="GJ66" s="5"/>
+      <c r="GK66" s="5"/>
+      <c r="GL66" s="5"/>
+      <c r="GM66" s="5"/>
+      <c r="GN66" s="5"/>
+      <c r="GO66" s="5"/>
+      <c r="GP66" s="5"/>
+      <c r="GQ66" s="5"/>
+      <c r="GR66" s="5"/>
+      <c r="GS66" s="5"/>
+      <c r="GT66" s="5"/>
+      <c r="GU66" s="5"/>
+      <c r="GV66" s="5"/>
+      <c r="GW66" s="5"/>
+      <c r="GX66" s="5"/>
+      <c r="GY66" s="5"/>
+      <c r="GZ66" s="5"/>
+      <c r="HA66" s="5"/>
+      <c r="HB66" s="5"/>
+      <c r="HC66" s="5"/>
+      <c r="HD66" s="5"/>
+      <c r="HE66" s="5"/>
+      <c r="HF66" s="5"/>
+      <c r="HG66" s="5"/>
+      <c r="HH66" s="5"/>
+      <c r="HI66" s="5"/>
+      <c r="HJ66" s="5"/>
+      <c r="HK66" s="5"/>
+      <c r="HL66" s="5"/>
+      <c r="HM66" s="5"/>
+      <c r="HN66" s="5"/>
+      <c r="HO66" s="5"/>
+      <c r="HP66" s="5"/>
+      <c r="HQ66" s="5"/>
+      <c r="HR66" s="5"/>
+      <c r="HS66" s="5"/>
+      <c r="HT66" s="5"/>
+      <c r="HU66" s="5"/>
+      <c r="HV66" s="5"/>
+      <c r="HW66" s="5"/>
+      <c r="HX66" s="5"/>
+      <c r="HY66" s="5"/>
+      <c r="HZ66" s="5"/>
+      <c r="IA66" s="5"/>
+      <c r="IB66" s="5"/>
+      <c r="IC66" s="5"/>
+      <c r="ID66" s="5"/>
+      <c r="IE66" s="5"/>
+      <c r="IF66" s="5"/>
+      <c r="IG66" s="5"/>
+      <c r="IH66" s="5"/>
+      <c r="II66" s="5"/>
+      <c r="IJ66" s="5"/>
+      <c r="IK66" s="5"/>
+      <c r="IL66" s="5"/>
+      <c r="IM66" s="5"/>
+      <c r="IN66" s="5"/>
+      <c r="IO66" s="5"/>
+      <c r="IP66" s="5"/>
+      <c r="IQ66" s="5"/>
+      <c r="IR66" s="5"/>
+      <c r="IS66" s="5"/>
+      <c r="IT66" s="5"/>
+      <c r="IU66" s="5"/>
+      <c r="IV66" s="5"/>
+      <c r="IW66" s="5"/>
+      <c r="IX66" s="5"/>
+      <c r="IY66" s="5"/>
+      <c r="IZ66" s="5"/>
+      <c r="JA66" s="5"/>
+      <c r="JB66" s="5"/>
+      <c r="JC66" s="5"/>
+      <c r="JD66" s="5"/>
+      <c r="JE66" s="5"/>
+      <c r="JF66" s="5"/>
+      <c r="JG66" s="5"/>
+      <c r="JH66" s="5"/>
+      <c r="JI66" s="5"/>
+      <c r="JJ66" s="5"/>
+      <c r="JK66" s="5"/>
+      <c r="JL66" s="5"/>
+      <c r="JM66" s="5"/>
+      <c r="JN66" s="5"/>
+      <c r="JO66" s="5"/>
+      <c r="JP66" s="5"/>
+      <c r="JQ66" s="5"/>
+      <c r="JR66" s="5"/>
+      <c r="JS66" s="5"/>
+      <c r="JT66" s="5"/>
+      <c r="JU66" s="5"/>
+      <c r="JV66" s="5"/>
+      <c r="JW66" s="5"/>
+      <c r="JX66" s="5"/>
+      <c r="JY66" s="5"/>
+      <c r="JZ66" s="5"/>
+      <c r="KA66" s="5"/>
+      <c r="KB66" s="5"/>
+      <c r="KC66" s="5"/>
+      <c r="KD66" s="5"/>
+      <c r="KE66" s="5"/>
+      <c r="KF66" s="5"/>
+      <c r="KG66" s="5"/>
+      <c r="KH66" s="5"/>
+      <c r="KI66" s="5"/>
+      <c r="KJ66" s="5"/>
+      <c r="KK66" s="5"/>
+      <c r="KL66" s="5"/>
+      <c r="KM66" s="5"/>
+      <c r="KN66" s="5"/>
+      <c r="KO66" s="5"/>
+      <c r="KP66" s="5"/>
+      <c r="KQ66" s="5"/>
+      <c r="KR66" s="5"/>
+      <c r="KS66" s="5"/>
+      <c r="KT66" s="5"/>
+      <c r="KU66" s="5"/>
+      <c r="KV66" s="5"/>
+      <c r="KW66" s="5"/>
+      <c r="KX66" s="5"/>
+      <c r="KY66" s="5"/>
+      <c r="KZ66" s="5"/>
+      <c r="LA66" s="5"/>
+      <c r="LB66" s="5"/>
+      <c r="LC66" s="5"/>
+      <c r="LD66" s="5"/>
+      <c r="LE66" s="5"/>
+      <c r="LF66" s="5"/>
+      <c r="LG66" s="5"/>
+      <c r="LH66" s="5"/>
+      <c r="LI66" s="5"/>
+      <c r="LJ66" s="5"/>
+      <c r="LK66" s="5"/>
+      <c r="LL66" s="5"/>
+      <c r="LM66" s="5"/>
+      <c r="LN66" s="5"/>
+      <c r="LO66" s="5"/>
+      <c r="LP66" s="5"/>
+      <c r="LQ66" s="5"/>
+      <c r="LR66" s="5"/>
+      <c r="LS66" s="5"/>
+      <c r="LT66" s="5"/>
+      <c r="LU66" s="5"/>
+      <c r="LV66" s="5"/>
+      <c r="LW66" s="5"/>
+      <c r="LX66" s="5"/>
+      <c r="LY66" s="5"/>
+      <c r="LZ66" s="5"/>
+      <c r="MA66" s="5"/>
+      <c r="MB66" s="5"/>
+      <c r="MC66" s="5"/>
+      <c r="MD66" s="5"/>
+      <c r="ME66" s="5"/>
+      <c r="MF66" s="5"/>
+      <c r="MG66" s="5"/>
+      <c r="MH66" s="5"/>
+      <c r="MI66" s="5"/>
+      <c r="MJ66" s="5"/>
+      <c r="MK66" s="5"/>
+      <c r="ML66" s="5"/>
+      <c r="MM66" s="5"/>
+      <c r="MN66" s="5"/>
+      <c r="MO66" s="5"/>
+      <c r="MP66" s="5"/>
+      <c r="MQ66" s="5"/>
+      <c r="MR66" s="5"/>
+      <c r="MS66" s="5"/>
+      <c r="MT66" s="5"/>
+      <c r="MU66" s="5"/>
+      <c r="MV66" s="5"/>
+      <c r="MW66" s="5"/>
+      <c r="MX66" s="5"/>
+      <c r="MY66" s="5"/>
+      <c r="MZ66" s="5"/>
+      <c r="NA66" s="5"/>
+      <c r="NB66" s="5"/>
+      <c r="NC66" s="5"/>
+      <c r="ND66" s="5"/>
+      <c r="NE66" s="5"/>
+      <c r="NF66" s="5"/>
+      <c r="NG66" s="5"/>
+      <c r="NH66" s="5"/>
+      <c r="NI66" s="5"/>
+      <c r="NJ66" s="5"/>
+      <c r="NK66" s="5"/>
+      <c r="NL66" s="5"/>
+      <c r="NM66" s="5"/>
+      <c r="NN66" s="5"/>
+      <c r="NO66" s="5"/>
+      <c r="NP66" s="5"/>
+      <c r="NQ66" s="5"/>
+      <c r="NR66" s="5"/>
+      <c r="NS66" s="5"/>
+      <c r="NT66" s="5"/>
+      <c r="NU66" s="5"/>
+      <c r="NV66" s="5"/>
+      <c r="NW66" s="5"/>
+      <c r="NX66" s="5"/>
+      <c r="NY66" s="5"/>
+      <c r="NZ66" s="5"/>
+      <c r="OA66" s="5"/>
+      <c r="OB66" s="5"/>
+      <c r="OC66" s="5"/>
+      <c r="OD66" s="5"/>
+      <c r="OE66" s="5"/>
+      <c r="OF66" s="5"/>
+      <c r="OG66" s="5"/>
+      <c r="OH66" s="5"/>
+      <c r="OI66" s="5"/>
+      <c r="OJ66" s="5"/>
+      <c r="OK66" s="5"/>
+      <c r="OL66" s="5"/>
+      <c r="OM66" s="5"/>
+      <c r="ON66" s="5"/>
+      <c r="OO66" s="5"/>
+      <c r="OP66" s="5"/>
+      <c r="OQ66" s="5"/>
+      <c r="OR66" s="5"/>
+      <c r="OS66" s="5"/>
+      <c r="OT66" s="5"/>
+      <c r="OU66" s="5"/>
+      <c r="OV66" s="5"/>
+      <c r="OW66" s="5"/>
+      <c r="OX66" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="OY66" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="OZ66" s="5"/>
+      <c r="PA66" s="5"/>
+      <c r="PB66" s="5"/>
+      <c r="PC66" s="5"/>
+      <c r="PD66" s="5"/>
+      <c r="PE66" s="5"/>
+      <c r="PF66" s="5"/>
+      <c r="PG66" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="PH66" s="5"/>
+      <c r="PI66" s="5"/>
+      <c r="PJ66" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Part2_PlatformBenchmarks_Results_v1.0.0.xlsx
+++ b/Part2_PlatformBenchmarks_Results_v1.0.0.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="511">
   <si>
     <t xml:space="preserve">Arduino Benchmark Suite – Part 2: Platform Benchmarks</t>
   </si>
@@ -4107,7 +4107,9 @@
       <c r="PC4" s="5"/>
       <c r="PD4" s="5"/>
       <c r="PE4" s="5"/>
-      <c r="PF4" s="5"/>
+      <c r="PF4" s="5" t="n">
+        <v>3.45</v>
+      </c>
       <c r="PG4" s="5" t="n">
         <v>3.45</v>
       </c>
@@ -4557,7 +4559,9 @@
       <c r="PC5" s="5"/>
       <c r="PD5" s="5"/>
       <c r="PE5" s="5"/>
-      <c r="PF5" s="5"/>
+      <c r="PF5" s="5" t="n">
+        <v>0.2</v>
+      </c>
       <c r="PG5" s="5" t="n">
         <v>0</v>
       </c>
@@ -5007,7 +5011,9 @@
       <c r="PC6" s="5"/>
       <c r="PD6" s="5"/>
       <c r="PE6" s="5"/>
-      <c r="PF6" s="5"/>
+      <c r="PF6" s="5" t="n">
+        <v>4.48</v>
+      </c>
       <c r="PG6" s="5" t="n">
         <v>4.48</v>
       </c>
@@ -5457,7 +5463,9 @@
       <c r="PC7" s="5"/>
       <c r="PD7" s="5"/>
       <c r="PE7" s="5"/>
-      <c r="PF7" s="5"/>
+      <c r="PF7" s="5" t="n">
+        <v>6.24</v>
+      </c>
       <c r="PG7" s="5" t="n">
         <v>6.24</v>
       </c>
@@ -5907,7 +5915,9 @@
       <c r="PC8" s="5"/>
       <c r="PD8" s="5"/>
       <c r="PE8" s="5"/>
-      <c r="PF8" s="5"/>
+      <c r="PF8" s="5" t="n">
+        <v>5.94</v>
+      </c>
       <c r="PG8" s="5" t="n">
         <v>5.94</v>
       </c>
@@ -6357,7 +6367,9 @@
       <c r="PC9" s="5"/>
       <c r="PD9" s="5"/>
       <c r="PE9" s="5"/>
-      <c r="PF9" s="5"/>
+      <c r="PF9" s="5" t="n">
+        <v>2.89</v>
+      </c>
       <c r="PG9" s="5" t="n">
         <v>2.89</v>
       </c>
@@ -6807,7 +6819,9 @@
       <c r="PC10" s="5"/>
       <c r="PD10" s="5"/>
       <c r="PE10" s="5"/>
-      <c r="PF10" s="5"/>
+      <c r="PF10" s="5" t="n">
+        <v>5.08</v>
+      </c>
       <c r="PG10" s="5" t="n">
         <v>5.08</v>
       </c>
@@ -7257,7 +7271,9 @@
       <c r="PC11" s="5"/>
       <c r="PD11" s="5"/>
       <c r="PE11" s="5"/>
-      <c r="PF11" s="5"/>
+      <c r="PF11" s="5" t="n">
+        <v>5.52</v>
+      </c>
       <c r="PG11" s="5" t="n">
         <v>5.52</v>
       </c>
@@ -7707,7 +7723,9 @@
       <c r="PC12" s="5"/>
       <c r="PD12" s="5"/>
       <c r="PE12" s="5"/>
-      <c r="PF12" s="5"/>
+      <c r="PF12" s="5" t="n">
+        <v>5.05</v>
+      </c>
       <c r="PG12" s="5" t="n">
         <v>5.06</v>
       </c>
@@ -8157,7 +8175,9 @@
       <c r="PC13" s="5"/>
       <c r="PD13" s="5"/>
       <c r="PE13" s="5"/>
-      <c r="PF13" s="5"/>
+      <c r="PF13" s="5" t="n">
+        <v>5.99</v>
+      </c>
       <c r="PG13" s="5" t="n">
         <v>5.99</v>
       </c>
@@ -8607,7 +8627,9 @@
       <c r="PC14" s="5"/>
       <c r="PD14" s="5"/>
       <c r="PE14" s="5"/>
-      <c r="PF14" s="5"/>
+      <c r="PF14" s="5" t="n">
+        <v>35.47</v>
+      </c>
       <c r="PG14" s="5" t="n">
         <v>35.47</v>
       </c>
@@ -9057,7 +9079,9 @@
       <c r="PC15" s="5"/>
       <c r="PD15" s="5"/>
       <c r="PE15" s="5"/>
-      <c r="PF15" s="5"/>
+      <c r="PF15" s="5" t="n">
+        <v>17.76</v>
+      </c>
       <c r="PG15" s="5" t="n">
         <v>17.76</v>
       </c>
@@ -9507,7 +9531,9 @@
       <c r="PC16" s="5"/>
       <c r="PD16" s="5"/>
       <c r="PE16" s="5"/>
-      <c r="PF16" s="5"/>
+      <c r="PF16" s="5" t="n">
+        <v>11.52</v>
+      </c>
       <c r="PG16" s="5" t="n">
         <v>11.52</v>
       </c>
@@ -9957,7 +9983,9 @@
       <c r="PC17" s="5"/>
       <c r="PD17" s="5"/>
       <c r="PE17" s="5"/>
-      <c r="PF17" s="5"/>
+      <c r="PF17" s="5" t="n">
+        <v>64.85</v>
+      </c>
       <c r="PG17" s="5" t="n">
         <v>64.85</v>
       </c>
@@ -10407,7 +10435,9 @@
       <c r="PC18" s="5"/>
       <c r="PD18" s="5"/>
       <c r="PE18" s="5"/>
-      <c r="PF18" s="5"/>
+      <c r="PF18" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="PG18" s="5" t="n">
         <v>0</v>
       </c>
@@ -10857,7 +10887,9 @@
       <c r="PC19" s="5"/>
       <c r="PD19" s="5"/>
       <c r="PE19" s="5"/>
-      <c r="PF19" s="5"/>
+      <c r="PF19" s="5" t="n">
+        <v>4</v>
+      </c>
       <c r="PG19" s="5" t="n">
         <v>4</v>
       </c>
@@ -11307,7 +11339,9 @@
       <c r="PC20" s="5"/>
       <c r="PD20" s="5"/>
       <c r="PE20" s="5"/>
-      <c r="PF20" s="5"/>
+      <c r="PF20" s="5" t="n">
+        <v>108</v>
+      </c>
       <c r="PG20" s="5" t="n">
         <v>108</v>
       </c>
@@ -11757,7 +11791,9 @@
       <c r="PC21" s="5"/>
       <c r="PD21" s="5"/>
       <c r="PE21" s="5"/>
-      <c r="PF21" s="5"/>
+      <c r="PF21" s="5" t="n">
+        <v>0.003</v>
+      </c>
       <c r="PG21" s="5" t="n">
         <v>0.003</v>
       </c>
@@ -12207,7 +12243,9 @@
       <c r="PC22" s="5"/>
       <c r="PD22" s="5"/>
       <c r="PE22" s="5"/>
-      <c r="PF22" s="5"/>
+      <c r="PF22" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="PG22" s="5" t="n">
         <v>1.7</v>
       </c>
@@ -12657,7 +12695,9 @@
       <c r="PC23" s="5"/>
       <c r="PD23" s="5"/>
       <c r="PE23" s="5"/>
-      <c r="PF23" s="5"/>
+      <c r="PF23" s="5" t="n">
+        <v>14</v>
+      </c>
       <c r="PG23" s="5" t="n">
         <v>14</v>
       </c>
@@ -13107,7 +13147,9 @@
       <c r="PC24" s="5"/>
       <c r="PD24" s="5"/>
       <c r="PE24" s="5"/>
-      <c r="PF24" s="5"/>
+      <c r="PF24" s="5" t="n">
+        <v>45</v>
+      </c>
       <c r="PG24" s="5" t="n">
         <v>45</v>
       </c>
@@ -13557,7 +13599,9 @@
       <c r="PC25" s="5"/>
       <c r="PD25" s="5"/>
       <c r="PE25" s="5"/>
-      <c r="PF25" s="5"/>
+      <c r="PF25" s="5" t="n">
+        <v>5.67</v>
+      </c>
       <c r="PG25" s="5" t="n">
         <v>5.67</v>
       </c>
@@ -14007,7 +14051,9 @@
       <c r="PC26" s="5"/>
       <c r="PD26" s="5"/>
       <c r="PE26" s="5"/>
-      <c r="PF26" s="5"/>
+      <c r="PF26" s="5" t="n">
+        <v>7.41</v>
+      </c>
       <c r="PG26" s="5" t="n">
         <v>7.39</v>
       </c>
@@ -14457,7 +14503,9 @@
       <c r="PC27" s="5"/>
       <c r="PD27" s="5"/>
       <c r="PE27" s="5"/>
-      <c r="PF27" s="5"/>
+      <c r="PF27" s="5" t="n">
+        <v>18.23</v>
+      </c>
       <c r="PG27" s="5" t="n">
         <v>17.49</v>
       </c>
@@ -14907,7 +14955,9 @@
       <c r="PC28" s="5"/>
       <c r="PD28" s="5"/>
       <c r="PE28" s="5"/>
-      <c r="PF28" s="5"/>
+      <c r="PF28" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PG28" s="5" t="s">
         <v>430</v>
       </c>
@@ -15357,7 +15407,9 @@
       <c r="PC29" s="5"/>
       <c r="PD29" s="5"/>
       <c r="PE29" s="5"/>
-      <c r="PF29" s="5"/>
+      <c r="PF29" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PG29" s="5" t="s">
         <v>430</v>
       </c>
@@ -15807,7 +15859,9 @@
       <c r="PC30" s="5"/>
       <c r="PD30" s="5"/>
       <c r="PE30" s="5"/>
-      <c r="PF30" s="5"/>
+      <c r="PF30" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PG30" s="5" t="s">
         <v>430</v>
       </c>
@@ -16257,7 +16311,9 @@
       <c r="PC31" s="5"/>
       <c r="PD31" s="5"/>
       <c r="PE31" s="5"/>
-      <c r="PF31" s="5"/>
+      <c r="PF31" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PG31" s="5" t="s">
         <v>430</v>
       </c>
@@ -16707,7 +16763,9 @@
       <c r="PC32" s="5"/>
       <c r="PD32" s="5"/>
       <c r="PE32" s="5"/>
-      <c r="PF32" s="5"/>
+      <c r="PF32" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PG32" s="5" t="s">
         <v>430</v>
       </c>
@@ -17157,7 +17215,9 @@
       <c r="PC33" s="5"/>
       <c r="PD33" s="5"/>
       <c r="PE33" s="5"/>
-      <c r="PF33" s="5"/>
+      <c r="PF33" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PG33" s="5" t="s">
         <v>430</v>
       </c>
@@ -17607,7 +17667,9 @@
       <c r="PC34" s="5"/>
       <c r="PD34" s="5"/>
       <c r="PE34" s="5"/>
-      <c r="PF34" s="5"/>
+      <c r="PF34" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PG34" s="5" t="s">
         <v>430</v>
       </c>
@@ -18057,7 +18119,9 @@
       <c r="PC35" s="5"/>
       <c r="PD35" s="5"/>
       <c r="PE35" s="5"/>
-      <c r="PF35" s="5"/>
+      <c r="PF35" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PG35" s="5" t="s">
         <v>430</v>
       </c>
@@ -18507,7 +18571,9 @@
       <c r="PC36" s="5"/>
       <c r="PD36" s="5"/>
       <c r="PE36" s="5"/>
-      <c r="PF36" s="5"/>
+      <c r="PF36" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PG36" s="5" t="s">
         <v>430</v>
       </c>
@@ -18957,7 +19023,9 @@
       <c r="PC37" s="5"/>
       <c r="PD37" s="5"/>
       <c r="PE37" s="5"/>
-      <c r="PF37" s="5"/>
+      <c r="PF37" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PG37" s="5" t="s">
         <v>430</v>
       </c>
@@ -19407,7 +19475,9 @@
       <c r="PC38" s="5"/>
       <c r="PD38" s="5"/>
       <c r="PE38" s="5"/>
-      <c r="PF38" s="5"/>
+      <c r="PF38" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PG38" s="5" t="s">
         <v>430</v>
       </c>
@@ -19857,7 +19927,9 @@
       <c r="PC39" s="5"/>
       <c r="PD39" s="5"/>
       <c r="PE39" s="5"/>
-      <c r="PF39" s="5"/>
+      <c r="PF39" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PG39" s="5" t="s">
         <v>430</v>
       </c>
@@ -20307,7 +20379,9 @@
       <c r="PC40" s="5"/>
       <c r="PD40" s="5"/>
       <c r="PE40" s="5"/>
-      <c r="PF40" s="5"/>
+      <c r="PF40" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PG40" s="5" t="s">
         <v>430</v>
       </c>
@@ -20757,7 +20831,9 @@
       <c r="PC41" s="5"/>
       <c r="PD41" s="5"/>
       <c r="PE41" s="5"/>
-      <c r="PF41" s="5"/>
+      <c r="PF41" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PG41" s="5" t="s">
         <v>430</v>
       </c>
@@ -21207,7 +21283,9 @@
       <c r="PC42" s="5"/>
       <c r="PD42" s="5"/>
       <c r="PE42" s="5"/>
-      <c r="PF42" s="5"/>
+      <c r="PF42" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PG42" s="5" t="s">
         <v>430</v>
       </c>
@@ -21657,7 +21735,9 @@
       <c r="PC43" s="5"/>
       <c r="PD43" s="5"/>
       <c r="PE43" s="5"/>
-      <c r="PF43" s="5"/>
+      <c r="PF43" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PG43" s="5" t="s">
         <v>430</v>
       </c>
@@ -22107,7 +22187,9 @@
       <c r="PC44" s="5"/>
       <c r="PD44" s="5"/>
       <c r="PE44" s="5"/>
-      <c r="PF44" s="5"/>
+      <c r="PF44" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PG44" s="5" t="s">
         <v>430</v>
       </c>
@@ -22557,7 +22639,9 @@
       <c r="PC45" s="5"/>
       <c r="PD45" s="5"/>
       <c r="PE45" s="5"/>
-      <c r="PF45" s="5"/>
+      <c r="PF45" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PG45" s="5" t="s">
         <v>430</v>
       </c>
@@ -23007,7 +23091,9 @@
       <c r="PC46" s="5"/>
       <c r="PD46" s="5"/>
       <c r="PE46" s="5"/>
-      <c r="PF46" s="5"/>
+      <c r="PF46" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PG46" s="5" t="s">
         <v>430</v>
       </c>
@@ -23457,7 +23543,9 @@
       <c r="PC47" s="5"/>
       <c r="PD47" s="5"/>
       <c r="PE47" s="5"/>
-      <c r="PF47" s="5"/>
+      <c r="PF47" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PG47" s="5" t="s">
         <v>430</v>
       </c>
@@ -23907,7 +23995,9 @@
       <c r="PC48" s="5"/>
       <c r="PD48" s="5"/>
       <c r="PE48" s="5"/>
-      <c r="PF48" s="5"/>
+      <c r="PF48" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PG48" s="5" t="s">
         <v>430</v>
       </c>
@@ -24357,7 +24447,9 @@
       <c r="PC49" s="5"/>
       <c r="PD49" s="5"/>
       <c r="PE49" s="5"/>
-      <c r="PF49" s="5"/>
+      <c r="PF49" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PG49" s="5" t="s">
         <v>430</v>
       </c>
@@ -24807,7 +24899,9 @@
       <c r="PC50" s="5"/>
       <c r="PD50" s="5"/>
       <c r="PE50" s="5"/>
-      <c r="PF50" s="5"/>
+      <c r="PF50" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PG50" s="5" t="s">
         <v>430</v>
       </c>
@@ -25257,7 +25351,9 @@
       <c r="PC51" s="5"/>
       <c r="PD51" s="5"/>
       <c r="PE51" s="5"/>
-      <c r="PF51" s="5"/>
+      <c r="PF51" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PG51" s="5" t="s">
         <v>430</v>
       </c>
@@ -25707,7 +25803,9 @@
       <c r="PC52" s="5"/>
       <c r="PD52" s="5"/>
       <c r="PE52" s="5"/>
-      <c r="PF52" s="5"/>
+      <c r="PF52" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PG52" s="5" t="s">
         <v>430</v>
       </c>
@@ -26157,7 +26255,9 @@
       <c r="PC53" s="5"/>
       <c r="PD53" s="5"/>
       <c r="PE53" s="5"/>
-      <c r="PF53" s="5"/>
+      <c r="PF53" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PG53" s="5" t="s">
         <v>430</v>
       </c>
@@ -26607,7 +26707,9 @@
       <c r="PC54" s="5"/>
       <c r="PD54" s="5"/>
       <c r="PE54" s="5"/>
-      <c r="PF54" s="5"/>
+      <c r="PF54" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PG54" s="5" t="s">
         <v>430</v>
       </c>
@@ -27057,7 +27159,9 @@
       <c r="PC55" s="5"/>
       <c r="PD55" s="5"/>
       <c r="PE55" s="5"/>
-      <c r="PF55" s="5"/>
+      <c r="PF55" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PG55" s="5" t="s">
         <v>430</v>
       </c>
@@ -27507,7 +27611,9 @@
       <c r="PC56" s="5"/>
       <c r="PD56" s="5"/>
       <c r="PE56" s="5"/>
-      <c r="PF56" s="5"/>
+      <c r="PF56" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PG56" s="5" t="s">
         <v>430</v>
       </c>
@@ -27957,7 +28063,9 @@
       <c r="PC57" s="5"/>
       <c r="PD57" s="5"/>
       <c r="PE57" s="5"/>
-      <c r="PF57" s="5"/>
+      <c r="PF57" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PG57" s="5" t="s">
         <v>430</v>
       </c>
@@ -28407,7 +28515,9 @@
       <c r="PC58" s="5"/>
       <c r="PD58" s="5"/>
       <c r="PE58" s="5"/>
-      <c r="PF58" s="5"/>
+      <c r="PF58" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PG58" s="5" t="s">
         <v>430</v>
       </c>
@@ -28857,7 +28967,9 @@
       <c r="PC59" s="5"/>
       <c r="PD59" s="5"/>
       <c r="PE59" s="5"/>
-      <c r="PF59" s="5"/>
+      <c r="PF59" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PG59" s="5" t="s">
         <v>430</v>
       </c>
@@ -29307,7 +29419,9 @@
       <c r="PC60" s="5"/>
       <c r="PD60" s="5"/>
       <c r="PE60" s="5"/>
-      <c r="PF60" s="5"/>
+      <c r="PF60" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PG60" s="5" t="s">
         <v>430</v>
       </c>
@@ -29757,7 +29871,9 @@
       <c r="PC61" s="5"/>
       <c r="PD61" s="5"/>
       <c r="PE61" s="5"/>
-      <c r="PF61" s="5"/>
+      <c r="PF61" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PG61" s="5" t="s">
         <v>430</v>
       </c>
@@ -30207,7 +30323,9 @@
       <c r="PC62" s="5"/>
       <c r="PD62" s="5"/>
       <c r="PE62" s="5"/>
-      <c r="PF62" s="5"/>
+      <c r="PF62" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PG62" s="5" t="s">
         <v>430</v>
       </c>
@@ -30657,7 +30775,9 @@
       <c r="PC63" s="5"/>
       <c r="PD63" s="5"/>
       <c r="PE63" s="5"/>
-      <c r="PF63" s="5"/>
+      <c r="PF63" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PG63" s="5" t="s">
         <v>430</v>
       </c>
@@ -31107,7 +31227,9 @@
       <c r="PC64" s="5"/>
       <c r="PD64" s="5"/>
       <c r="PE64" s="5"/>
-      <c r="PF64" s="5"/>
+      <c r="PF64" s="5" t="n">
+        <v>732</v>
+      </c>
       <c r="PG64" s="5" t="n">
         <v>484</v>
       </c>
@@ -31557,7 +31679,9 @@
       <c r="PC65" s="5"/>
       <c r="PD65" s="5"/>
       <c r="PE65" s="5"/>
-      <c r="PF65" s="5"/>
+      <c r="PF65" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PG65" s="5" t="s">
         <v>430</v>
       </c>
@@ -32007,7 +32131,9 @@
       <c r="PC66" s="5"/>
       <c r="PD66" s="5"/>
       <c r="PE66" s="5"/>
-      <c r="PF66" s="5"/>
+      <c r="PF66" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="PG66" s="5" t="s">
         <v>430</v>
       </c>

--- a/Part2_PlatformBenchmarks_Results_v1.0.0.xlsx
+++ b/Part2_PlatformBenchmarks_Results_v1.0.0.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="512">
   <si>
     <t xml:space="preserve">Arduino Benchmark Suite – Part 2: Platform Benchmarks</t>
   </si>
@@ -1399,6 +1399,9 @@
     <t xml:space="preserve">400 kHz speed (txn/ms)</t>
   </si>
   <si>
+    <t xml:space="preserve">1 MHz speed (txn/ms)</t>
+  </si>
+  <si>
     <t xml:space="preserve">WiFi</t>
   </si>
   <si>
@@ -1444,10 +1447,10 @@
     <t xml:space="preserve">PBKDF2-HMAC-SHA256 (ops/ms)</t>
   </si>
   <si>
-    <t xml:space="preserve">Hardware AES Encrypt (ops/ms)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hardware AES Decrypt (ops/ms)</t>
+    <t xml:space="preserve">Hardware AES Encrypt (blocks/ms)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hardware AES Decrypt (blocks/ms)</t>
   </si>
   <si>
     <t xml:space="preserve">Hardware RNG (bytes/sec)</t>
@@ -1946,7 +1949,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:PJ66"/>
+  <dimension ref="A1:PJ67"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.31"/>
@@ -3693,7 +3696,9 @@
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
+      <c r="P4" s="5" t="n">
+        <v>397.77</v>
+      </c>
       <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
       <c r="S4" s="5"/>
@@ -4145,7 +4150,9 @@
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
+      <c r="P5" s="5" t="n">
+        <v>3</v>
+      </c>
       <c r="Q5" s="5"/>
       <c r="R5" s="5"/>
       <c r="S5" s="5"/>
@@ -4597,7 +4604,9 @@
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
+      <c r="P6" s="5" t="n">
+        <v>429.18</v>
+      </c>
       <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
       <c r="S6" s="5"/>
@@ -5049,7 +5058,9 @@
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
+      <c r="P7" s="5" t="n">
+        <v>854.7</v>
+      </c>
       <c r="Q7" s="5"/>
       <c r="R7" s="5"/>
       <c r="S7" s="5"/>
@@ -5501,7 +5512,9 @@
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
       <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
+      <c r="P8" s="5" t="n">
+        <v>781.25</v>
+      </c>
       <c r="Q8" s="5"/>
       <c r="R8" s="5"/>
       <c r="S8" s="5"/>
@@ -5953,7 +5966,9 @@
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
       <c r="O9" s="5"/>
-      <c r="P9" s="5"/>
+      <c r="P9" s="5" t="n">
+        <v>299.4</v>
+      </c>
       <c r="Q9" s="5"/>
       <c r="R9" s="5"/>
       <c r="S9" s="5"/>
@@ -6405,7 +6420,9 @@
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
       <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
+      <c r="P10" s="5" t="n">
+        <v>606.06</v>
+      </c>
       <c r="Q10" s="5"/>
       <c r="R10" s="5"/>
       <c r="S10" s="5"/>
@@ -6857,7 +6874,9 @@
       <c r="M11" s="5"/>
       <c r="N11" s="5"/>
       <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
+      <c r="P11" s="5" t="n">
+        <v>584.8</v>
+      </c>
       <c r="Q11" s="5"/>
       <c r="R11" s="5"/>
       <c r="S11" s="5"/>
@@ -7309,7 +7328,9 @@
       <c r="M12" s="5"/>
       <c r="N12" s="5"/>
       <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
+      <c r="P12" s="5" t="n">
+        <v>628.93</v>
+      </c>
       <c r="Q12" s="5"/>
       <c r="R12" s="5"/>
       <c r="S12" s="5"/>
@@ -7761,7 +7782,9 @@
       <c r="M13" s="5"/>
       <c r="N13" s="5"/>
       <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
+      <c r="P13" s="5" t="n">
+        <v>793.65</v>
+      </c>
       <c r="Q13" s="5"/>
       <c r="R13" s="5"/>
       <c r="S13" s="5"/>
@@ -8213,7 +8236,9 @@
       <c r="M14" s="5"/>
       <c r="N14" s="5"/>
       <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
+      <c r="P14" s="5" t="n">
+        <v>1261.03</v>
+      </c>
       <c r="Q14" s="5"/>
       <c r="R14" s="5"/>
       <c r="S14" s="5"/>
@@ -8665,7 +8690,9 @@
       <c r="M15" s="5"/>
       <c r="N15" s="5"/>
       <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
+      <c r="P15" s="5" t="n">
+        <v>55.87</v>
+      </c>
       <c r="Q15" s="5"/>
       <c r="R15" s="5"/>
       <c r="S15" s="5"/>
@@ -9117,7 +9144,9 @@
       <c r="M16" s="5"/>
       <c r="N16" s="5"/>
       <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
+      <c r="P16" s="5" t="n">
+        <v>11.52</v>
+      </c>
       <c r="Q16" s="5"/>
       <c r="R16" s="5"/>
       <c r="S16" s="5"/>
@@ -9569,7 +9598,9 @@
       <c r="M17" s="5"/>
       <c r="N17" s="5"/>
       <c r="O17" s="5"/>
-      <c r="P17" s="5"/>
+      <c r="P17" s="5" t="n">
+        <v>20.62</v>
+      </c>
       <c r="Q17" s="5"/>
       <c r="R17" s="5"/>
       <c r="S17" s="5"/>
@@ -10021,7 +10052,9 @@
       <c r="M18" s="5"/>
       <c r="N18" s="5"/>
       <c r="O18" s="5"/>
-      <c r="P18" s="5"/>
+      <c r="P18" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="Q18" s="5"/>
       <c r="R18" s="5"/>
       <c r="S18" s="5"/>
@@ -10473,7 +10506,9 @@
       <c r="M19" s="5"/>
       <c r="N19" s="5"/>
       <c r="O19" s="5"/>
-      <c r="P19" s="5"/>
+      <c r="P19" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="Q19" s="5"/>
       <c r="R19" s="5"/>
       <c r="S19" s="5"/>
@@ -10925,7 +10960,9 @@
       <c r="M20" s="5"/>
       <c r="N20" s="5"/>
       <c r="O20" s="5"/>
-      <c r="P20" s="5"/>
+      <c r="P20" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="Q20" s="5"/>
       <c r="R20" s="5"/>
       <c r="S20" s="5"/>
@@ -11377,7 +11414,9 @@
       <c r="M21" s="5"/>
       <c r="N21" s="5"/>
       <c r="O21" s="5"/>
-      <c r="P21" s="5"/>
+      <c r="P21" s="5" t="n">
+        <v>0.011</v>
+      </c>
       <c r="Q21" s="5"/>
       <c r="R21" s="5"/>
       <c r="S21" s="5"/>
@@ -11829,7 +11868,9 @@
       <c r="M22" s="5"/>
       <c r="N22" s="5"/>
       <c r="O22" s="5"/>
-      <c r="P22" s="5"/>
+      <c r="P22" s="5" t="n">
+        <v>0.2</v>
+      </c>
       <c r="Q22" s="5"/>
       <c r="R22" s="5"/>
       <c r="S22" s="5"/>
@@ -12281,7 +12322,9 @@
       <c r="M23" s="5"/>
       <c r="N23" s="5"/>
       <c r="O23" s="5"/>
-      <c r="P23" s="5"/>
+      <c r="P23" s="5" t="n">
+        <v>63</v>
+      </c>
       <c r="Q23" s="5"/>
       <c r="R23" s="5"/>
       <c r="S23" s="5"/>
@@ -12733,7 +12776,9 @@
       <c r="M24" s="5"/>
       <c r="N24" s="5"/>
       <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
+      <c r="P24" s="5" t="n">
+        <v>81</v>
+      </c>
       <c r="Q24" s="5"/>
       <c r="R24" s="5"/>
       <c r="S24" s="5"/>
@@ -13185,7 +13230,9 @@
       <c r="M25" s="5"/>
       <c r="N25" s="5"/>
       <c r="O25" s="5"/>
-      <c r="P25" s="5"/>
+      <c r="P25" s="5" t="n">
+        <v>0.36</v>
+      </c>
       <c r="Q25" s="5"/>
       <c r="R25" s="5"/>
       <c r="S25" s="5"/>
@@ -13637,7 +13684,9 @@
       <c r="M26" s="5"/>
       <c r="N26" s="5"/>
       <c r="O26" s="5"/>
-      <c r="P26" s="5"/>
+      <c r="P26" s="5" t="n">
+        <v>5.38</v>
+      </c>
       <c r="Q26" s="5"/>
       <c r="R26" s="5"/>
       <c r="S26" s="5"/>
@@ -14089,7 +14138,9 @@
       <c r="M27" s="5"/>
       <c r="N27" s="5"/>
       <c r="O27" s="5"/>
-      <c r="P27" s="5"/>
+      <c r="P27" s="5" t="n">
+        <v>10.45</v>
+      </c>
       <c r="Q27" s="5"/>
       <c r="R27" s="5"/>
       <c r="S27" s="5"/>
@@ -14515,16 +14566,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>459</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>460</v>
-      </c>
       <c r="C28" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="D28" s="5" t="n">
-        <v>2</v>
+      <c r="D28" s="5" t="s">
+        <v>430</v>
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="5" t="s">
@@ -14541,7 +14592,9 @@
       <c r="M28" s="5"/>
       <c r="N28" s="5"/>
       <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
+      <c r="P28" s="5" t="n">
+        <v>11.55</v>
+      </c>
       <c r="Q28" s="5"/>
       <c r="R28" s="5"/>
       <c r="S28" s="5"/>
@@ -14608,8 +14661,8 @@
       <c r="BZ28" s="5"/>
       <c r="CA28" s="5"/>
       <c r="CB28" s="5"/>
-      <c r="CC28" s="5" t="n">
-        <v>0</v>
+      <c r="CC28" s="5" t="s">
+        <v>430</v>
       </c>
       <c r="CD28" s="5"/>
       <c r="CE28" s="5"/>
@@ -14967,7 +15020,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>461</v>
@@ -14975,8 +15028,8 @@
       <c r="C29" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="D29" s="5" t="s">
-        <v>430</v>
+      <c r="D29" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="E29" s="5"/>
       <c r="F29" s="5" t="s">
@@ -14993,7 +15046,9 @@
       <c r="M29" s="5"/>
       <c r="N29" s="5"/>
       <c r="O29" s="5"/>
-      <c r="P29" s="5"/>
+      <c r="P29" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="Q29" s="5"/>
       <c r="R29" s="5"/>
       <c r="S29" s="5"/>
@@ -15060,8 +15115,8 @@
       <c r="BZ29" s="5"/>
       <c r="CA29" s="5"/>
       <c r="CB29" s="5"/>
-      <c r="CC29" s="5" t="s">
-        <v>430</v>
+      <c r="CC29" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="CD29" s="5"/>
       <c r="CE29" s="5"/>
@@ -15419,16 +15474,16 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>463</v>
-      </c>
       <c r="C30" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="D30" s="5" t="n">
-        <v>6</v>
+      <c r="D30" s="5" t="s">
+        <v>430</v>
       </c>
       <c r="E30" s="5"/>
       <c r="F30" s="5" t="s">
@@ -15445,7 +15500,9 @@
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
       <c r="O30" s="5"/>
-      <c r="P30" s="5"/>
+      <c r="P30" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="Q30" s="5"/>
       <c r="R30" s="5"/>
       <c r="S30" s="5"/>
@@ -15512,8 +15569,8 @@
       <c r="BZ30" s="5"/>
       <c r="CA30" s="5"/>
       <c r="CB30" s="5"/>
-      <c r="CC30" s="5" t="n">
-        <v>5</v>
+      <c r="CC30" s="5" t="s">
+        <v>430</v>
       </c>
       <c r="CD30" s="5"/>
       <c r="CE30" s="5"/>
@@ -15871,16 +15928,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>430</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>5068.28</v>
+        <v>6</v>
       </c>
       <c r="E31" s="5"/>
       <c r="F31" s="5" t="s">
@@ -15897,7 +15954,9 @@
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
       <c r="O31" s="5"/>
-      <c r="P31" s="5"/>
+      <c r="P31" s="5" t="n">
+        <v>4</v>
+      </c>
       <c r="Q31" s="5"/>
       <c r="R31" s="5"/>
       <c r="S31" s="5"/>
@@ -15964,8 +16023,8 @@
       <c r="BZ31" s="5"/>
       <c r="CA31" s="5"/>
       <c r="CB31" s="5"/>
-      <c r="CC31" s="5" t="s">
-        <v>430</v>
+      <c r="CC31" s="5" t="n">
+        <v>5</v>
       </c>
       <c r="CD31" s="5"/>
       <c r="CE31" s="5"/>
@@ -16323,16 +16382,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>430</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>5.155</v>
+        <v>5068.28</v>
       </c>
       <c r="E32" s="5"/>
       <c r="F32" s="5" t="s">
@@ -16349,7 +16408,9 @@
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
       <c r="O32" s="5"/>
-      <c r="P32" s="5"/>
+      <c r="P32" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="Q32" s="5"/>
       <c r="R32" s="5"/>
       <c r="S32" s="5"/>
@@ -16775,7 +16836,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>466</v>
@@ -16784,7 +16845,7 @@
         <v>430</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>128000000</v>
+        <v>5.155</v>
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="5" t="s">
@@ -16801,7 +16862,9 @@
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
       <c r="O33" s="5"/>
-      <c r="P33" s="5"/>
+      <c r="P33" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="Q33" s="5"/>
       <c r="R33" s="5"/>
       <c r="S33" s="5"/>
@@ -17227,7 +17290,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>467</v>
@@ -17236,7 +17299,7 @@
         <v>430</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>5.16</v>
+        <v>128000000</v>
       </c>
       <c r="E34" s="5"/>
       <c r="F34" s="5" t="s">
@@ -17253,7 +17316,9 @@
       <c r="M34" s="5"/>
       <c r="N34" s="5"/>
       <c r="O34" s="5"/>
-      <c r="P34" s="5"/>
+      <c r="P34" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="Q34" s="5"/>
       <c r="R34" s="5"/>
       <c r="S34" s="5"/>
@@ -17679,7 +17744,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>468</v>
@@ -17687,8 +17752,8 @@
       <c r="C35" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="D35" s="5" t="s">
-        <v>430</v>
+      <c r="D35" s="5" t="n">
+        <v>5.16</v>
       </c>
       <c r="E35" s="5"/>
       <c r="F35" s="5" t="s">
@@ -17705,7 +17770,9 @@
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
       <c r="O35" s="5"/>
-      <c r="P35" s="5"/>
+      <c r="P35" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="Q35" s="5"/>
       <c r="R35" s="5"/>
       <c r="S35" s="5"/>
@@ -17772,8 +17839,8 @@
       <c r="BZ35" s="5"/>
       <c r="CA35" s="5"/>
       <c r="CB35" s="5"/>
-      <c r="CC35" s="5" t="n">
-        <v>2.02</v>
+      <c r="CC35" s="5" t="s">
+        <v>430</v>
       </c>
       <c r="CD35" s="5"/>
       <c r="CE35" s="5"/>
@@ -18131,7 +18198,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>469</v>
@@ -18157,7 +18224,9 @@
       <c r="M36" s="5"/>
       <c r="N36" s="5"/>
       <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
+      <c r="P36" s="5" t="n">
+        <v>2.51</v>
+      </c>
       <c r="Q36" s="5"/>
       <c r="R36" s="5"/>
       <c r="S36" s="5"/>
@@ -18225,7 +18294,7 @@
       <c r="CA36" s="5"/>
       <c r="CB36" s="5"/>
       <c r="CC36" s="5" t="n">
-        <v>30.1</v>
+        <v>2.02</v>
       </c>
       <c r="CD36" s="5"/>
       <c r="CE36" s="5"/>
@@ -18583,7 +18652,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>470</v>
@@ -18609,7 +18678,9 @@
       <c r="M37" s="5"/>
       <c r="N37" s="5"/>
       <c r="O37" s="5"/>
-      <c r="P37" s="5"/>
+      <c r="P37" s="5" t="n">
+        <v>29.86</v>
+      </c>
       <c r="Q37" s="5"/>
       <c r="R37" s="5"/>
       <c r="S37" s="5"/>
@@ -18677,7 +18748,7 @@
       <c r="CA37" s="5"/>
       <c r="CB37" s="5"/>
       <c r="CC37" s="5" t="n">
-        <v>39.86</v>
+        <v>30.1</v>
       </c>
       <c r="CD37" s="5"/>
       <c r="CE37" s="5"/>
@@ -19035,7 +19106,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>471</v>
@@ -19061,7 +19132,9 @@
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
       <c r="O38" s="5"/>
-      <c r="P38" s="5"/>
+      <c r="P38" s="5" t="n">
+        <v>62.07</v>
+      </c>
       <c r="Q38" s="5"/>
       <c r="R38" s="5"/>
       <c r="S38" s="5"/>
@@ -19129,7 +19202,7 @@
       <c r="CA38" s="5"/>
       <c r="CB38" s="5"/>
       <c r="CC38" s="5" t="n">
-        <v>28.87</v>
+        <v>39.86</v>
       </c>
       <c r="CD38" s="5"/>
       <c r="CE38" s="5"/>
@@ -19487,7 +19560,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>472</v>
@@ -19513,7 +19586,9 @@
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
       <c r="O39" s="5"/>
-      <c r="P39" s="5"/>
+      <c r="P39" s="5" t="n">
+        <v>29.12</v>
+      </c>
       <c r="Q39" s="5"/>
       <c r="R39" s="5"/>
       <c r="S39" s="5"/>
@@ -19581,7 +19656,7 @@
       <c r="CA39" s="5"/>
       <c r="CB39" s="5"/>
       <c r="CC39" s="5" t="n">
-        <v>5.57</v>
+        <v>28.87</v>
       </c>
       <c r="CD39" s="5"/>
       <c r="CE39" s="5"/>
@@ -19939,7 +20014,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>473</v>
@@ -19965,7 +20040,9 @@
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
       <c r="O40" s="5"/>
-      <c r="P40" s="5"/>
+      <c r="P40" s="5" t="n">
+        <v>21.96</v>
+      </c>
       <c r="Q40" s="5"/>
       <c r="R40" s="5"/>
       <c r="S40" s="5"/>
@@ -20033,7 +20110,7 @@
       <c r="CA40" s="5"/>
       <c r="CB40" s="5"/>
       <c r="CC40" s="5" t="n">
-        <v>0.04</v>
+        <v>5.57</v>
       </c>
       <c r="CD40" s="5"/>
       <c r="CE40" s="5"/>
@@ -20391,7 +20468,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>474</v>
@@ -20417,7 +20494,9 @@
       <c r="M41" s="5"/>
       <c r="N41" s="5"/>
       <c r="O41" s="5"/>
-      <c r="P41" s="5"/>
+      <c r="P41" s="5" t="n">
+        <v>0.03</v>
+      </c>
       <c r="Q41" s="5"/>
       <c r="R41" s="5"/>
       <c r="S41" s="5"/>
@@ -20484,8 +20563,8 @@
       <c r="BZ41" s="5"/>
       <c r="CA41" s="5"/>
       <c r="CB41" s="5"/>
-      <c r="CC41" s="5" t="s">
-        <v>430</v>
+      <c r="CC41" s="5" t="n">
+        <v>0.04</v>
       </c>
       <c r="CD41" s="5"/>
       <c r="CE41" s="5"/>
@@ -20843,7 +20922,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>475</v>
@@ -20869,7 +20948,9 @@
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
       <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
+      <c r="P42" s="5" t="n">
+        <v>33.67</v>
+      </c>
       <c r="Q42" s="5"/>
       <c r="R42" s="5"/>
       <c r="S42" s="5"/>
@@ -21295,7 +21376,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>476</v>
@@ -21303,8 +21384,8 @@
       <c r="C43" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="D43" s="5" t="n">
-        <v>9142.04</v>
+      <c r="D43" s="5" t="s">
+        <v>430</v>
       </c>
       <c r="E43" s="5"/>
       <c r="F43" s="5" t="s">
@@ -21321,7 +21402,9 @@
       <c r="M43" s="5"/>
       <c r="N43" s="5"/>
       <c r="O43" s="5"/>
-      <c r="P43" s="5"/>
+      <c r="P43" s="5" t="n">
+        <v>33.91</v>
+      </c>
       <c r="Q43" s="5"/>
       <c r="R43" s="5"/>
       <c r="S43" s="5"/>
@@ -21747,7 +21830,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>477</v>
@@ -21755,8 +21838,8 @@
       <c r="C44" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="D44" s="5" t="s">
-        <v>430</v>
+      <c r="D44" s="5" t="n">
+        <v>9142.04</v>
       </c>
       <c r="E44" s="5"/>
       <c r="F44" s="5" t="s">
@@ -21764,8 +21847,8 @@
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
-      <c r="I44" s="5" t="n">
-        <v>8.21</v>
+      <c r="I44" s="5" t="s">
+        <v>430</v>
       </c>
       <c r="J44" s="5"/>
       <c r="K44" s="5"/>
@@ -21773,7 +21856,9 @@
       <c r="M44" s="5"/>
       <c r="N44" s="5"/>
       <c r="O44" s="5"/>
-      <c r="P44" s="5"/>
+      <c r="P44" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="Q44" s="5"/>
       <c r="R44" s="5"/>
       <c r="S44" s="5"/>
@@ -21840,8 +21925,8 @@
       <c r="BZ44" s="5"/>
       <c r="CA44" s="5"/>
       <c r="CB44" s="5"/>
-      <c r="CC44" s="5" t="n">
-        <v>1303.78</v>
+      <c r="CC44" s="5" t="s">
+        <v>430</v>
       </c>
       <c r="CD44" s="5"/>
       <c r="CE44" s="5"/>
@@ -22199,10 +22284,10 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="B45" s="5" t="s">
         <v>478</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>479</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>430</v>
@@ -22216,8 +22301,8 @@
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
-      <c r="I45" s="5" t="s">
-        <v>430</v>
+      <c r="I45" s="5" t="n">
+        <v>8.21</v>
       </c>
       <c r="J45" s="5"/>
       <c r="K45" s="5"/>
@@ -22225,7 +22310,9 @@
       <c r="M45" s="5"/>
       <c r="N45" s="5"/>
       <c r="O45" s="5"/>
-      <c r="P45" s="5"/>
+      <c r="P45" s="5" t="n">
+        <v>44.8</v>
+      </c>
       <c r="Q45" s="5"/>
       <c r="R45" s="5"/>
       <c r="S45" s="5"/>
@@ -22293,7 +22380,7 @@
       <c r="CA45" s="5"/>
       <c r="CB45" s="5"/>
       <c r="CC45" s="5" t="n">
-        <v>555845</v>
+        <v>1303.78</v>
       </c>
       <c r="CD45" s="5"/>
       <c r="CE45" s="5"/>
@@ -22651,7 +22738,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>480</v>
@@ -22677,7 +22764,9 @@
       <c r="M46" s="5"/>
       <c r="N46" s="5"/>
       <c r="O46" s="5"/>
-      <c r="P46" s="5"/>
+      <c r="P46" s="5" t="n">
+        <v>6294565</v>
+      </c>
       <c r="Q46" s="5"/>
       <c r="R46" s="5"/>
       <c r="S46" s="5"/>
@@ -22744,8 +22833,8 @@
       <c r="BZ46" s="5"/>
       <c r="CA46" s="5"/>
       <c r="CB46" s="5"/>
-      <c r="CC46" s="5" t="s">
-        <v>430</v>
+      <c r="CC46" s="5" t="n">
+        <v>555845</v>
       </c>
       <c r="CD46" s="5"/>
       <c r="CE46" s="5"/>
@@ -23103,7 +23192,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>481</v>
@@ -23129,7 +23218,9 @@
       <c r="M47" s="5"/>
       <c r="N47" s="5"/>
       <c r="O47" s="5"/>
-      <c r="P47" s="5"/>
+      <c r="P47" s="5" t="n">
+        <v>6305655</v>
+      </c>
       <c r="Q47" s="5"/>
       <c r="R47" s="5"/>
       <c r="S47" s="5"/>
@@ -23555,10 +23646,10 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="B48" s="5" t="s">
         <v>482</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>483</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>430</v>
@@ -23581,7 +23672,9 @@
       <c r="M48" s="5"/>
       <c r="N48" s="5"/>
       <c r="O48" s="5"/>
-      <c r="P48" s="5"/>
+      <c r="P48" s="5" t="n">
+        <v>99.82</v>
+      </c>
       <c r="Q48" s="5"/>
       <c r="R48" s="5"/>
       <c r="S48" s="5"/>
@@ -23602,8 +23695,8 @@
       <c r="AH48" s="5"/>
       <c r="AI48" s="5"/>
       <c r="AJ48" s="5"/>
-      <c r="AK48" s="5" t="n">
-        <v>22324</v>
+      <c r="AK48" s="5" t="s">
+        <v>430</v>
       </c>
       <c r="AL48" s="5"/>
       <c r="AM48" s="5"/>
@@ -24007,10 +24100,10 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>443</v>
+        <v>484</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>430</v>
@@ -24033,7 +24126,9 @@
       <c r="M49" s="5"/>
       <c r="N49" s="5"/>
       <c r="O49" s="5"/>
-      <c r="P49" s="5"/>
+      <c r="P49" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="Q49" s="5"/>
       <c r="R49" s="5"/>
       <c r="S49" s="5"/>
@@ -24055,7 +24150,7 @@
       <c r="AI49" s="5"/>
       <c r="AJ49" s="5"/>
       <c r="AK49" s="5" t="n">
-        <v>1892.4</v>
+        <v>22324</v>
       </c>
       <c r="AL49" s="5"/>
       <c r="AM49" s="5"/>
@@ -24459,16 +24554,16 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>485</v>
+        <v>443</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="D50" s="5" t="n">
-        <v>161.03</v>
+      <c r="D50" s="5" t="s">
+        <v>430</v>
       </c>
       <c r="E50" s="5"/>
       <c r="F50" s="5" t="s">
@@ -24485,7 +24580,9 @@
       <c r="M50" s="5"/>
       <c r="N50" s="5"/>
       <c r="O50" s="5"/>
-      <c r="P50" s="5"/>
+      <c r="P50" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="Q50" s="5"/>
       <c r="R50" s="5"/>
       <c r="S50" s="5"/>
@@ -24506,8 +24603,8 @@
       <c r="AH50" s="5"/>
       <c r="AI50" s="5"/>
       <c r="AJ50" s="5"/>
-      <c r="AK50" s="5" t="s">
-        <v>430</v>
+      <c r="AK50" s="5" t="n">
+        <v>1892.4</v>
       </c>
       <c r="AL50" s="5"/>
       <c r="AM50" s="5"/>
@@ -24911,7 +25008,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>486</v>
@@ -24920,7 +25017,7 @@
         <v>430</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>26.5</v>
+        <v>161.03</v>
       </c>
       <c r="E51" s="5"/>
       <c r="F51" s="5" t="s">
@@ -24937,7 +25034,9 @@
       <c r="M51" s="5"/>
       <c r="N51" s="5"/>
       <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
+      <c r="P51" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="Q51" s="5"/>
       <c r="R51" s="5"/>
       <c r="S51" s="5"/>
@@ -25363,16 +25462,16 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="B52" s="5" t="s">
         <v>487</v>
       </c>
-      <c r="B52" s="5" t="s">
-        <v>488</v>
-      </c>
       <c r="C52" s="5" t="s">
         <v>430</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>101.85</v>
+        <v>26.5</v>
       </c>
       <c r="E52" s="5"/>
       <c r="F52" s="5" t="s">
@@ -25389,7 +25488,9 @@
       <c r="M52" s="5"/>
       <c r="N52" s="5"/>
       <c r="O52" s="5"/>
-      <c r="P52" s="5"/>
+      <c r="P52" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="Q52" s="5"/>
       <c r="R52" s="5"/>
       <c r="S52" s="5"/>
@@ -25815,7 +25916,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>489</v>
@@ -25824,7 +25925,7 @@
         <v>430</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>103.1</v>
+        <v>101.85</v>
       </c>
       <c r="E53" s="5"/>
       <c r="F53" s="5" t="s">
@@ -25841,7 +25942,9 @@
       <c r="M53" s="5"/>
       <c r="N53" s="5"/>
       <c r="O53" s="5"/>
-      <c r="P53" s="5"/>
+      <c r="P53" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="Q53" s="5"/>
       <c r="R53" s="5"/>
       <c r="S53" s="5"/>
@@ -26267,16 +26370,16 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="B54" s="5" t="s">
         <v>490</v>
       </c>
-      <c r="B54" s="5" t="s">
-        <v>491</v>
-      </c>
       <c r="C54" s="5" t="s">
         <v>430</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>60.29</v>
+        <v>103.1</v>
       </c>
       <c r="E54" s="5"/>
       <c r="F54" s="5" t="s">
@@ -26293,7 +26396,9 @@
       <c r="M54" s="5"/>
       <c r="N54" s="5"/>
       <c r="O54" s="5"/>
-      <c r="P54" s="5"/>
+      <c r="P54" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="Q54" s="5"/>
       <c r="R54" s="5"/>
       <c r="S54" s="5"/>
@@ -26695,8 +26800,8 @@
       <c r="OU54" s="5"/>
       <c r="OV54" s="5"/>
       <c r="OW54" s="5"/>
-      <c r="OX54" s="5" t="n">
-        <v>910</v>
+      <c r="OX54" s="5" t="s">
+        <v>430</v>
       </c>
       <c r="OY54" s="5" t="s">
         <v>430</v>
@@ -26719,7 +26824,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>492</v>
@@ -26728,7 +26833,7 @@
         <v>430</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>5.49</v>
+        <v>60.29</v>
       </c>
       <c r="E55" s="5"/>
       <c r="F55" s="5" t="s">
@@ -26745,7 +26850,9 @@
       <c r="M55" s="5"/>
       <c r="N55" s="5"/>
       <c r="O55" s="5"/>
-      <c r="P55" s="5"/>
+      <c r="P55" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="Q55" s="5"/>
       <c r="R55" s="5"/>
       <c r="S55" s="5"/>
@@ -27148,7 +27255,7 @@
       <c r="OV55" s="5"/>
       <c r="OW55" s="5"/>
       <c r="OX55" s="5" t="n">
-        <v>1010</v>
+        <v>910</v>
       </c>
       <c r="OY55" s="5" t="s">
         <v>430</v>
@@ -27171,7 +27278,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>493</v>
@@ -27180,7 +27287,7 @@
         <v>430</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>-0.431</v>
+        <v>5.49</v>
       </c>
       <c r="E56" s="5"/>
       <c r="F56" s="5" t="s">
@@ -27197,7 +27304,9 @@
       <c r="M56" s="5"/>
       <c r="N56" s="5"/>
       <c r="O56" s="5"/>
-      <c r="P56" s="5"/>
+      <c r="P56" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="Q56" s="5"/>
       <c r="R56" s="5"/>
       <c r="S56" s="5"/>
@@ -27599,8 +27708,8 @@
       <c r="OU56" s="5"/>
       <c r="OV56" s="5"/>
       <c r="OW56" s="5"/>
-      <c r="OX56" s="5" t="s">
-        <v>430</v>
+      <c r="OX56" s="5" t="n">
+        <v>1010</v>
       </c>
       <c r="OY56" s="5" t="s">
         <v>430</v>
@@ -27623,16 +27732,16 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="B57" s="5" t="s">
         <v>494</v>
       </c>
-      <c r="B57" s="5" t="s">
-        <v>495</v>
-      </c>
       <c r="C57" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="D57" s="5" t="s">
-        <v>430</v>
+      <c r="D57" s="5" t="n">
+        <v>-0.431</v>
       </c>
       <c r="E57" s="5"/>
       <c r="F57" s="5" t="s">
@@ -27649,7 +27758,9 @@
       <c r="M57" s="5"/>
       <c r="N57" s="5"/>
       <c r="O57" s="5"/>
-      <c r="P57" s="5"/>
+      <c r="P57" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="Q57" s="5"/>
       <c r="R57" s="5"/>
       <c r="S57" s="5"/>
@@ -28051,8 +28162,8 @@
       <c r="OU57" s="5"/>
       <c r="OV57" s="5"/>
       <c r="OW57" s="5"/>
-      <c r="OX57" s="5" t="n">
-        <v>2.86</v>
+      <c r="OX57" s="5" t="s">
+        <v>430</v>
       </c>
       <c r="OY57" s="5" t="s">
         <v>430</v>
@@ -28075,7 +28186,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>496</v>
@@ -28101,7 +28212,9 @@
       <c r="M58" s="5"/>
       <c r="N58" s="5"/>
       <c r="O58" s="5"/>
-      <c r="P58" s="5"/>
+      <c r="P58" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="Q58" s="5"/>
       <c r="R58" s="5"/>
       <c r="S58" s="5"/>
@@ -28504,7 +28617,7 @@
       <c r="OV58" s="5"/>
       <c r="OW58" s="5"/>
       <c r="OX58" s="5" t="n">
-        <v>2.16</v>
+        <v>2.86</v>
       </c>
       <c r="OY58" s="5" t="s">
         <v>430</v>
@@ -28527,10 +28640,10 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="B59" s="5" t="s">
         <v>497</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>498</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>430</v>
@@ -28553,7 +28666,9 @@
       <c r="M59" s="5"/>
       <c r="N59" s="5"/>
       <c r="O59" s="5"/>
-      <c r="P59" s="5"/>
+      <c r="P59" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="Q59" s="5"/>
       <c r="R59" s="5"/>
       <c r="S59" s="5"/>
@@ -28955,8 +29070,8 @@
       <c r="OU59" s="5"/>
       <c r="OV59" s="5"/>
       <c r="OW59" s="5"/>
-      <c r="OX59" s="5" t="s">
-        <v>430</v>
+      <c r="OX59" s="5" t="n">
+        <v>2.16</v>
       </c>
       <c r="OY59" s="5" t="s">
         <v>430</v>
@@ -28979,10 +29094,10 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="B60" s="5" t="s">
         <v>499</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>500</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>430</v>
@@ -29005,7 +29120,9 @@
       <c r="M60" s="5"/>
       <c r="N60" s="5"/>
       <c r="O60" s="5"/>
-      <c r="P60" s="5"/>
+      <c r="P60" s="5" t="n">
+        <v>1461.99</v>
+      </c>
       <c r="Q60" s="5"/>
       <c r="R60" s="5"/>
       <c r="S60" s="5"/>
@@ -29431,10 +29548,10 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="B61" s="5" t="s">
         <v>501</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>502</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>430</v>
@@ -29457,7 +29574,9 @@
       <c r="M61" s="5"/>
       <c r="N61" s="5"/>
       <c r="O61" s="5"/>
-      <c r="P61" s="5"/>
+      <c r="P61" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="Q61" s="5"/>
       <c r="R61" s="5"/>
       <c r="S61" s="5"/>
@@ -29883,7 +30002,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>503</v>
@@ -29909,7 +30028,9 @@
       <c r="M62" s="5"/>
       <c r="N62" s="5"/>
       <c r="O62" s="5"/>
-      <c r="P62" s="5"/>
+      <c r="P62" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="Q62" s="5"/>
       <c r="R62" s="5"/>
       <c r="S62" s="5"/>
@@ -30335,10 +30456,10 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="B63" s="5" t="s">
         <v>504</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>505</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>430</v>
@@ -30361,7 +30482,9 @@
       <c r="M63" s="5"/>
       <c r="N63" s="5"/>
       <c r="O63" s="5"/>
-      <c r="P63" s="5"/>
+      <c r="P63" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="Q63" s="5"/>
       <c r="R63" s="5"/>
       <c r="S63" s="5"/>
@@ -30787,20 +30910,20 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="B64" s="5" t="s">
         <v>506</v>
       </c>
-      <c r="B64" s="5" t="s">
-        <v>507</v>
-      </c>
-      <c r="C64" s="5" t="n">
-        <v>56</v>
+      <c r="C64" s="5" t="s">
+        <v>430</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>430</v>
       </c>
       <c r="E64" s="5"/>
-      <c r="F64" s="5" t="n">
-        <v>520</v>
+      <c r="F64" s="5" t="s">
+        <v>430</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
@@ -30813,7 +30936,9 @@
       <c r="M64" s="5"/>
       <c r="N64" s="5"/>
       <c r="O64" s="5"/>
-      <c r="P64" s="5"/>
+      <c r="P64" s="5" t="n">
+        <v>5000000</v>
+      </c>
       <c r="Q64" s="5"/>
       <c r="R64" s="5"/>
       <c r="S64" s="5"/>
@@ -30834,8 +30959,8 @@
       <c r="AH64" s="5"/>
       <c r="AI64" s="5"/>
       <c r="AJ64" s="5"/>
-      <c r="AK64" s="5" t="n">
-        <v>660</v>
+      <c r="AK64" s="5" t="s">
+        <v>430</v>
       </c>
       <c r="AL64" s="5"/>
       <c r="AM64" s="5"/>
@@ -31215,11 +31340,11 @@
       <c r="OU64" s="5"/>
       <c r="OV64" s="5"/>
       <c r="OW64" s="5"/>
-      <c r="OX64" s="5" t="n">
-        <v>792</v>
-      </c>
-      <c r="OY64" s="5" t="n">
-        <v>992</v>
+      <c r="OX64" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="OY64" s="5" t="s">
+        <v>430</v>
       </c>
       <c r="OZ64" s="5"/>
       <c r="PA64" s="5"/>
@@ -31227,11 +31352,11 @@
       <c r="PC64" s="5"/>
       <c r="PD64" s="5"/>
       <c r="PE64" s="5"/>
-      <c r="PF64" s="5" t="n">
-        <v>732</v>
-      </c>
-      <c r="PG64" s="5" t="n">
-        <v>484</v>
+      <c r="PF64" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="PG64" s="5" t="s">
+        <v>430</v>
       </c>
       <c r="PH64" s="5"/>
       <c r="PI64" s="5"/>
@@ -31239,20 +31364,20 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="4" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>508</v>
       </c>
-      <c r="C65" s="5" t="s">
-        <v>430</v>
-      </c>
-      <c r="D65" s="5" t="n">
-        <v>86</v>
+      <c r="C65" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>430</v>
       </c>
       <c r="E65" s="5"/>
-      <c r="F65" s="5" t="s">
-        <v>430</v>
+      <c r="F65" s="5" t="n">
+        <v>520</v>
       </c>
       <c r="G65" s="5"/>
       <c r="H65" s="5"/>
@@ -31265,7 +31390,9 @@
       <c r="M65" s="5"/>
       <c r="N65" s="5"/>
       <c r="O65" s="5"/>
-      <c r="P65" s="5"/>
+      <c r="P65" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="Q65" s="5"/>
       <c r="R65" s="5"/>
       <c r="S65" s="5"/>
@@ -31286,8 +31413,8 @@
       <c r="AH65" s="5"/>
       <c r="AI65" s="5"/>
       <c r="AJ65" s="5"/>
-      <c r="AK65" s="5" t="s">
-        <v>430</v>
+      <c r="AK65" s="5" t="n">
+        <v>660</v>
       </c>
       <c r="AL65" s="5"/>
       <c r="AM65" s="5"/>
@@ -31667,11 +31794,11 @@
       <c r="OU65" s="5"/>
       <c r="OV65" s="5"/>
       <c r="OW65" s="5"/>
-      <c r="OX65" s="5" t="s">
-        <v>430</v>
-      </c>
-      <c r="OY65" s="5" t="s">
-        <v>430</v>
+      <c r="OX65" s="5" t="n">
+        <v>792</v>
+      </c>
+      <c r="OY65" s="5" t="n">
+        <v>992</v>
       </c>
       <c r="OZ65" s="5"/>
       <c r="PA65" s="5"/>
@@ -31679,11 +31806,11 @@
       <c r="PC65" s="5"/>
       <c r="PD65" s="5"/>
       <c r="PE65" s="5"/>
-      <c r="PF65" s="5" t="s">
-        <v>430</v>
-      </c>
-      <c r="PG65" s="5" t="s">
-        <v>430</v>
+      <c r="PF65" s="5" t="n">
+        <v>732</v>
+      </c>
+      <c r="PG65" s="5" t="n">
+        <v>484</v>
       </c>
       <c r="PH65" s="5"/>
       <c r="PI65" s="5"/>
@@ -31691,16 +31818,16 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="B66" s="5" t="s">
         <v>509</v>
       </c>
-      <c r="B66" s="5" t="s">
-        <v>510</v>
-      </c>
       <c r="C66" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="D66" s="5" t="s">
-        <v>430</v>
+      <c r="D66" s="5" t="n">
+        <v>86</v>
       </c>
       <c r="E66" s="5"/>
       <c r="F66" s="5" t="s">
@@ -31717,7 +31844,9 @@
       <c r="M66" s="5"/>
       <c r="N66" s="5"/>
       <c r="O66" s="5"/>
-      <c r="P66" s="5"/>
+      <c r="P66" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="Q66" s="5"/>
       <c r="R66" s="5"/>
       <c r="S66" s="5"/>
@@ -32141,6 +32270,460 @@
       <c r="PI66" s="5"/>
       <c r="PJ66" s="5"/>
     </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>511</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="E67" s="5"/>
+      <c r="F67" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="G67" s="5"/>
+      <c r="H67" s="5"/>
+      <c r="I67" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="J67" s="5"/>
+      <c r="K67" s="5"/>
+      <c r="L67" s="5"/>
+      <c r="M67" s="5"/>
+      <c r="N67" s="5"/>
+      <c r="O67" s="5"/>
+      <c r="P67" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="Q67" s="5"/>
+      <c r="R67" s="5"/>
+      <c r="S67" s="5"/>
+      <c r="T67" s="5"/>
+      <c r="U67" s="5"/>
+      <c r="V67" s="5"/>
+      <c r="W67" s="5"/>
+      <c r="X67" s="5"/>
+      <c r="Y67" s="5"/>
+      <c r="Z67" s="5"/>
+      <c r="AA67" s="5"/>
+      <c r="AB67" s="5"/>
+      <c r="AC67" s="5"/>
+      <c r="AD67" s="5"/>
+      <c r="AE67" s="5"/>
+      <c r="AF67" s="5"/>
+      <c r="AG67" s="5"/>
+      <c r="AH67" s="5"/>
+      <c r="AI67" s="5"/>
+      <c r="AJ67" s="5"/>
+      <c r="AK67" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="AL67" s="5"/>
+      <c r="AM67" s="5"/>
+      <c r="AN67" s="5"/>
+      <c r="AO67" s="5"/>
+      <c r="AP67" s="5"/>
+      <c r="AQ67" s="5"/>
+      <c r="AR67" s="5"/>
+      <c r="AS67" s="5"/>
+      <c r="AT67" s="5"/>
+      <c r="AU67" s="5"/>
+      <c r="AV67" s="5"/>
+      <c r="AW67" s="5"/>
+      <c r="AX67" s="5"/>
+      <c r="AY67" s="5"/>
+      <c r="AZ67" s="5"/>
+      <c r="BA67" s="5"/>
+      <c r="BB67" s="5"/>
+      <c r="BC67" s="5"/>
+      <c r="BD67" s="5"/>
+      <c r="BE67" s="5"/>
+      <c r="BF67" s="5"/>
+      <c r="BG67" s="5"/>
+      <c r="BH67" s="5"/>
+      <c r="BI67" s="5"/>
+      <c r="BJ67" s="5"/>
+      <c r="BK67" s="5"/>
+      <c r="BL67" s="5"/>
+      <c r="BM67" s="5"/>
+      <c r="BN67" s="5"/>
+      <c r="BO67" s="5"/>
+      <c r="BP67" s="5"/>
+      <c r="BQ67" s="5"/>
+      <c r="BR67" s="5"/>
+      <c r="BS67" s="5"/>
+      <c r="BT67" s="5"/>
+      <c r="BU67" s="5"/>
+      <c r="BV67" s="5"/>
+      <c r="BW67" s="5"/>
+      <c r="BX67" s="5"/>
+      <c r="BY67" s="5"/>
+      <c r="BZ67" s="5"/>
+      <c r="CA67" s="5"/>
+      <c r="CB67" s="5"/>
+      <c r="CC67" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="CD67" s="5"/>
+      <c r="CE67" s="5"/>
+      <c r="CF67" s="5"/>
+      <c r="CG67" s="5"/>
+      <c r="CH67" s="5"/>
+      <c r="CI67" s="5"/>
+      <c r="CJ67" s="5"/>
+      <c r="CK67" s="5"/>
+      <c r="CL67" s="5"/>
+      <c r="CM67" s="5"/>
+      <c r="CN67" s="5"/>
+      <c r="CO67" s="5"/>
+      <c r="CP67" s="5"/>
+      <c r="CQ67" s="5"/>
+      <c r="CR67" s="5"/>
+      <c r="CS67" s="5"/>
+      <c r="CT67" s="5"/>
+      <c r="CU67" s="5"/>
+      <c r="CV67" s="5"/>
+      <c r="CW67" s="5"/>
+      <c r="CX67" s="5"/>
+      <c r="CY67" s="5"/>
+      <c r="CZ67" s="5"/>
+      <c r="DA67" s="5"/>
+      <c r="DB67" s="5"/>
+      <c r="DC67" s="5"/>
+      <c r="DD67" s="5"/>
+      <c r="DE67" s="5"/>
+      <c r="DF67" s="5"/>
+      <c r="DG67" s="5"/>
+      <c r="DH67" s="5"/>
+      <c r="DI67" s="5"/>
+      <c r="DJ67" s="5"/>
+      <c r="DK67" s="5"/>
+      <c r="DL67" s="5"/>
+      <c r="DM67" s="5"/>
+      <c r="DN67" s="5"/>
+      <c r="DO67" s="5"/>
+      <c r="DP67" s="5"/>
+      <c r="DQ67" s="5"/>
+      <c r="DR67" s="5"/>
+      <c r="DS67" s="5"/>
+      <c r="DT67" s="5"/>
+      <c r="DU67" s="5"/>
+      <c r="DV67" s="5"/>
+      <c r="DW67" s="5"/>
+      <c r="DX67" s="5"/>
+      <c r="DY67" s="5"/>
+      <c r="DZ67" s="5"/>
+      <c r="EA67" s="5"/>
+      <c r="EB67" s="5"/>
+      <c r="EC67" s="5"/>
+      <c r="ED67" s="5"/>
+      <c r="EE67" s="5"/>
+      <c r="EF67" s="5"/>
+      <c r="EG67" s="5"/>
+      <c r="EH67" s="5"/>
+      <c r="EI67" s="5"/>
+      <c r="EJ67" s="5"/>
+      <c r="EK67" s="5"/>
+      <c r="EL67" s="5"/>
+      <c r="EM67" s="5"/>
+      <c r="EN67" s="5"/>
+      <c r="EO67" s="5"/>
+      <c r="EP67" s="5"/>
+      <c r="EQ67" s="5"/>
+      <c r="ER67" s="5"/>
+      <c r="ES67" s="5"/>
+      <c r="ET67" s="5"/>
+      <c r="EU67" s="5"/>
+      <c r="EV67" s="5"/>
+      <c r="EW67" s="5"/>
+      <c r="EX67" s="5"/>
+      <c r="EY67" s="5"/>
+      <c r="EZ67" s="5"/>
+      <c r="FA67" s="5"/>
+      <c r="FB67" s="5"/>
+      <c r="FC67" s="5"/>
+      <c r="FD67" s="5"/>
+      <c r="FE67" s="5"/>
+      <c r="FF67" s="5"/>
+      <c r="FG67" s="5"/>
+      <c r="FH67" s="5"/>
+      <c r="FI67" s="5"/>
+      <c r="FJ67" s="5"/>
+      <c r="FK67" s="5"/>
+      <c r="FL67" s="5"/>
+      <c r="FM67" s="5"/>
+      <c r="FN67" s="5"/>
+      <c r="FO67" s="5"/>
+      <c r="FP67" s="5"/>
+      <c r="FQ67" s="5"/>
+      <c r="FR67" s="5"/>
+      <c r="FS67" s="5"/>
+      <c r="FT67" s="5"/>
+      <c r="FU67" s="5"/>
+      <c r="FV67" s="5"/>
+      <c r="FW67" s="5"/>
+      <c r="FX67" s="5"/>
+      <c r="FY67" s="5"/>
+      <c r="FZ67" s="5"/>
+      <c r="GA67" s="5"/>
+      <c r="GB67" s="5"/>
+      <c r="GC67" s="5"/>
+      <c r="GD67" s="5"/>
+      <c r="GE67" s="5"/>
+      <c r="GF67" s="5"/>
+      <c r="GG67" s="5"/>
+      <c r="GH67" s="5"/>
+      <c r="GI67" s="5"/>
+      <c r="GJ67" s="5"/>
+      <c r="GK67" s="5"/>
+      <c r="GL67" s="5"/>
+      <c r="GM67" s="5"/>
+      <c r="GN67" s="5"/>
+      <c r="GO67" s="5"/>
+      <c r="GP67" s="5"/>
+      <c r="GQ67" s="5"/>
+      <c r="GR67" s="5"/>
+      <c r="GS67" s="5"/>
+      <c r="GT67" s="5"/>
+      <c r="GU67" s="5"/>
+      <c r="GV67" s="5"/>
+      <c r="GW67" s="5"/>
+      <c r="GX67" s="5"/>
+      <c r="GY67" s="5"/>
+      <c r="GZ67" s="5"/>
+      <c r="HA67" s="5"/>
+      <c r="HB67" s="5"/>
+      <c r="HC67" s="5"/>
+      <c r="HD67" s="5"/>
+      <c r="HE67" s="5"/>
+      <c r="HF67" s="5"/>
+      <c r="HG67" s="5"/>
+      <c r="HH67" s="5"/>
+      <c r="HI67" s="5"/>
+      <c r="HJ67" s="5"/>
+      <c r="HK67" s="5"/>
+      <c r="HL67" s="5"/>
+      <c r="HM67" s="5"/>
+      <c r="HN67" s="5"/>
+      <c r="HO67" s="5"/>
+      <c r="HP67" s="5"/>
+      <c r="HQ67" s="5"/>
+      <c r="HR67" s="5"/>
+      <c r="HS67" s="5"/>
+      <c r="HT67" s="5"/>
+      <c r="HU67" s="5"/>
+      <c r="HV67" s="5"/>
+      <c r="HW67" s="5"/>
+      <c r="HX67" s="5"/>
+      <c r="HY67" s="5"/>
+      <c r="HZ67" s="5"/>
+      <c r="IA67" s="5"/>
+      <c r="IB67" s="5"/>
+      <c r="IC67" s="5"/>
+      <c r="ID67" s="5"/>
+      <c r="IE67" s="5"/>
+      <c r="IF67" s="5"/>
+      <c r="IG67" s="5"/>
+      <c r="IH67" s="5"/>
+      <c r="II67" s="5"/>
+      <c r="IJ67" s="5"/>
+      <c r="IK67" s="5"/>
+      <c r="IL67" s="5"/>
+      <c r="IM67" s="5"/>
+      <c r="IN67" s="5"/>
+      <c r="IO67" s="5"/>
+      <c r="IP67" s="5"/>
+      <c r="IQ67" s="5"/>
+      <c r="IR67" s="5"/>
+      <c r="IS67" s="5"/>
+      <c r="IT67" s="5"/>
+      <c r="IU67" s="5"/>
+      <c r="IV67" s="5"/>
+      <c r="IW67" s="5"/>
+      <c r="IX67" s="5"/>
+      <c r="IY67" s="5"/>
+      <c r="IZ67" s="5"/>
+      <c r="JA67" s="5"/>
+      <c r="JB67" s="5"/>
+      <c r="JC67" s="5"/>
+      <c r="JD67" s="5"/>
+      <c r="JE67" s="5"/>
+      <c r="JF67" s="5"/>
+      <c r="JG67" s="5"/>
+      <c r="JH67" s="5"/>
+      <c r="JI67" s="5"/>
+      <c r="JJ67" s="5"/>
+      <c r="JK67" s="5"/>
+      <c r="JL67" s="5"/>
+      <c r="JM67" s="5"/>
+      <c r="JN67" s="5"/>
+      <c r="JO67" s="5"/>
+      <c r="JP67" s="5"/>
+      <c r="JQ67" s="5"/>
+      <c r="JR67" s="5"/>
+      <c r="JS67" s="5"/>
+      <c r="JT67" s="5"/>
+      <c r="JU67" s="5"/>
+      <c r="JV67" s="5"/>
+      <c r="JW67" s="5"/>
+      <c r="JX67" s="5"/>
+      <c r="JY67" s="5"/>
+      <c r="JZ67" s="5"/>
+      <c r="KA67" s="5"/>
+      <c r="KB67" s="5"/>
+      <c r="KC67" s="5"/>
+      <c r="KD67" s="5"/>
+      <c r="KE67" s="5"/>
+      <c r="KF67" s="5"/>
+      <c r="KG67" s="5"/>
+      <c r="KH67" s="5"/>
+      <c r="KI67" s="5"/>
+      <c r="KJ67" s="5"/>
+      <c r="KK67" s="5"/>
+      <c r="KL67" s="5"/>
+      <c r="KM67" s="5"/>
+      <c r="KN67" s="5"/>
+      <c r="KO67" s="5"/>
+      <c r="KP67" s="5"/>
+      <c r="KQ67" s="5"/>
+      <c r="KR67" s="5"/>
+      <c r="KS67" s="5"/>
+      <c r="KT67" s="5"/>
+      <c r="KU67" s="5"/>
+      <c r="KV67" s="5"/>
+      <c r="KW67" s="5"/>
+      <c r="KX67" s="5"/>
+      <c r="KY67" s="5"/>
+      <c r="KZ67" s="5"/>
+      <c r="LA67" s="5"/>
+      <c r="LB67" s="5"/>
+      <c r="LC67" s="5"/>
+      <c r="LD67" s="5"/>
+      <c r="LE67" s="5"/>
+      <c r="LF67" s="5"/>
+      <c r="LG67" s="5"/>
+      <c r="LH67" s="5"/>
+      <c r="LI67" s="5"/>
+      <c r="LJ67" s="5"/>
+      <c r="LK67" s="5"/>
+      <c r="LL67" s="5"/>
+      <c r="LM67" s="5"/>
+      <c r="LN67" s="5"/>
+      <c r="LO67" s="5"/>
+      <c r="LP67" s="5"/>
+      <c r="LQ67" s="5"/>
+      <c r="LR67" s="5"/>
+      <c r="LS67" s="5"/>
+      <c r="LT67" s="5"/>
+      <c r="LU67" s="5"/>
+      <c r="LV67" s="5"/>
+      <c r="LW67" s="5"/>
+      <c r="LX67" s="5"/>
+      <c r="LY67" s="5"/>
+      <c r="LZ67" s="5"/>
+      <c r="MA67" s="5"/>
+      <c r="MB67" s="5"/>
+      <c r="MC67" s="5"/>
+      <c r="MD67" s="5"/>
+      <c r="ME67" s="5"/>
+      <c r="MF67" s="5"/>
+      <c r="MG67" s="5"/>
+      <c r="MH67" s="5"/>
+      <c r="MI67" s="5"/>
+      <c r="MJ67" s="5"/>
+      <c r="MK67" s="5"/>
+      <c r="ML67" s="5"/>
+      <c r="MM67" s="5"/>
+      <c r="MN67" s="5"/>
+      <c r="MO67" s="5"/>
+      <c r="MP67" s="5"/>
+      <c r="MQ67" s="5"/>
+      <c r="MR67" s="5"/>
+      <c r="MS67" s="5"/>
+      <c r="MT67" s="5"/>
+      <c r="MU67" s="5"/>
+      <c r="MV67" s="5"/>
+      <c r="MW67" s="5"/>
+      <c r="MX67" s="5"/>
+      <c r="MY67" s="5"/>
+      <c r="MZ67" s="5"/>
+      <c r="NA67" s="5"/>
+      <c r="NB67" s="5"/>
+      <c r="NC67" s="5"/>
+      <c r="ND67" s="5"/>
+      <c r="NE67" s="5"/>
+      <c r="NF67" s="5"/>
+      <c r="NG67" s="5"/>
+      <c r="NH67" s="5"/>
+      <c r="NI67" s="5"/>
+      <c r="NJ67" s="5"/>
+      <c r="NK67" s="5"/>
+      <c r="NL67" s="5"/>
+      <c r="NM67" s="5"/>
+      <c r="NN67" s="5"/>
+      <c r="NO67" s="5"/>
+      <c r="NP67" s="5"/>
+      <c r="NQ67" s="5"/>
+      <c r="NR67" s="5"/>
+      <c r="NS67" s="5"/>
+      <c r="NT67" s="5"/>
+      <c r="NU67" s="5"/>
+      <c r="NV67" s="5"/>
+      <c r="NW67" s="5"/>
+      <c r="NX67" s="5"/>
+      <c r="NY67" s="5"/>
+      <c r="NZ67" s="5"/>
+      <c r="OA67" s="5"/>
+      <c r="OB67" s="5"/>
+      <c r="OC67" s="5"/>
+      <c r="OD67" s="5"/>
+      <c r="OE67" s="5"/>
+      <c r="OF67" s="5"/>
+      <c r="OG67" s="5"/>
+      <c r="OH67" s="5"/>
+      <c r="OI67" s="5"/>
+      <c r="OJ67" s="5"/>
+      <c r="OK67" s="5"/>
+      <c r="OL67" s="5"/>
+      <c r="OM67" s="5"/>
+      <c r="ON67" s="5"/>
+      <c r="OO67" s="5"/>
+      <c r="OP67" s="5"/>
+      <c r="OQ67" s="5"/>
+      <c r="OR67" s="5"/>
+      <c r="OS67" s="5"/>
+      <c r="OT67" s="5"/>
+      <c r="OU67" s="5"/>
+      <c r="OV67" s="5"/>
+      <c r="OW67" s="5"/>
+      <c r="OX67" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="OY67" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="OZ67" s="5"/>
+      <c r="PA67" s="5"/>
+      <c r="PB67" s="5"/>
+      <c r="PC67" s="5"/>
+      <c r="PD67" s="5"/>
+      <c r="PE67" s="5"/>
+      <c r="PF67" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="PG67" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="PH67" s="5"/>
+      <c r="PI67" s="5"/>
+      <c r="PJ67" s="5"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:PJ1"/>

--- a/Part2_PlatformBenchmarks_Results_v1.0.0.xlsx
+++ b/Part2_PlatformBenchmarks_Results_v1.0.0.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="512">
   <si>
     <t xml:space="preserve">Arduino Benchmark Suite – Part 2: Platform Benchmarks</t>
   </si>
@@ -1949,7 +1949,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:PJ67"/>
+  <dimension ref="A1:PJ68"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.31"/>
@@ -3681,7 +3681,9 @@
       <c r="D4" s="5" t="n">
         <v>75.81</v>
       </c>
-      <c r="E4" s="5"/>
+      <c r="E4" s="5" t="n">
+        <v>76.4</v>
+      </c>
       <c r="F4" s="5" t="n">
         <v>3.45</v>
       </c>
@@ -4135,7 +4137,9 @@
       <c r="D5" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="E5" s="5"/>
+      <c r="E5" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="F5" s="5" t="n">
         <v>0.41</v>
       </c>
@@ -4589,7 +4593,9 @@
       <c r="D6" s="5" t="n">
         <v>36.86</v>
       </c>
-      <c r="E6" s="5"/>
+      <c r="E6" s="5" t="n">
+        <v>36.42</v>
+      </c>
       <c r="F6" s="5" t="n">
         <v>4.48</v>
       </c>
@@ -5043,7 +5049,9 @@
       <c r="D7" s="5" t="n">
         <v>37.79</v>
       </c>
-      <c r="E7" s="5"/>
+      <c r="E7" s="5" t="n">
+        <v>37.34</v>
+      </c>
       <c r="F7" s="5" t="n">
         <v>6.24</v>
       </c>
@@ -5497,7 +5505,9 @@
       <c r="D8" s="5" t="n">
         <v>37.71</v>
       </c>
-      <c r="E8" s="5"/>
+      <c r="E8" s="5" t="n">
+        <v>37.23</v>
+      </c>
       <c r="F8" s="5" t="n">
         <v>5.94</v>
       </c>
@@ -5951,7 +5961,9 @@
       <c r="D9" s="5" t="n">
         <v>17.41</v>
       </c>
-      <c r="E9" s="5"/>
+      <c r="E9" s="5" t="n">
+        <v>17.24</v>
+      </c>
       <c r="F9" s="5" t="n">
         <v>2.89</v>
       </c>
@@ -6405,7 +6417,9 @@
       <c r="D10" s="5" t="n">
         <v>173.91</v>
       </c>
-      <c r="E10" s="5"/>
+      <c r="E10" s="5" t="n">
+        <v>173.91</v>
+      </c>
       <c r="F10" s="5" t="n">
         <v>5.08</v>
       </c>
@@ -6859,7 +6873,9 @@
       <c r="D11" s="5" t="n">
         <v>199.2</v>
       </c>
-      <c r="E11" s="5"/>
+      <c r="E11" s="5" t="n">
+        <v>199.2</v>
+      </c>
       <c r="F11" s="5" t="n">
         <v>5.52</v>
       </c>
@@ -7313,7 +7329,9 @@
       <c r="D12" s="5" t="n">
         <v>205.76</v>
       </c>
-      <c r="E12" s="5"/>
+      <c r="E12" s="5" t="n">
+        <v>205.34</v>
+      </c>
       <c r="F12" s="5" t="n">
         <v>5.05</v>
       </c>
@@ -7767,7 +7785,9 @@
       <c r="D13" s="5" t="n">
         <v>214.59</v>
       </c>
-      <c r="E13" s="5"/>
+      <c r="E13" s="5" t="n">
+        <v>215.05</v>
+      </c>
       <c r="F13" s="5" t="n">
         <v>5.99</v>
       </c>
@@ -8221,7 +8241,9 @@
       <c r="D14" s="5" t="n">
         <v>210.97</v>
       </c>
-      <c r="E14" s="5"/>
+      <c r="E14" s="5" t="n">
+        <v>211.01</v>
+      </c>
       <c r="F14" s="5" t="n">
         <v>35.47</v>
       </c>
@@ -8675,7 +8697,9 @@
       <c r="D15" s="5" t="n">
         <v>11.56</v>
       </c>
-      <c r="E15" s="5"/>
+      <c r="E15" s="5" t="n">
+        <v>27.14</v>
+      </c>
       <c r="F15" s="5" t="n">
         <v>17.77</v>
       </c>
@@ -9129,7 +9153,9 @@
       <c r="D16" s="5" t="n">
         <v>11.52</v>
       </c>
-      <c r="E16" s="5"/>
+      <c r="E16" s="5" t="n">
+        <v>11.52</v>
+      </c>
       <c r="F16" s="5" t="n">
         <v>11.52</v>
       </c>
@@ -9583,7 +9609,9 @@
       <c r="D17" s="5" t="n">
         <v>99.63</v>
       </c>
-      <c r="E17" s="5"/>
+      <c r="E17" s="5" t="n">
+        <v>42.45</v>
+      </c>
       <c r="F17" s="5" t="n">
         <v>64.83</v>
       </c>
@@ -10037,7 +10065,9 @@
       <c r="D18" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="5"/>
+      <c r="E18" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="F18" s="5" t="n">
         <v>1</v>
       </c>
@@ -10491,7 +10521,9 @@
       <c r="D19" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E19" s="5"/>
+      <c r="E19" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="F19" s="5" t="n">
         <v>4</v>
       </c>
@@ -10945,7 +10977,9 @@
       <c r="D20" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="E20" s="5"/>
+      <c r="E20" s="5" t="n">
+        <v>48</v>
+      </c>
       <c r="F20" s="5" t="n">
         <v>108</v>
       </c>
@@ -11399,7 +11433,9 @@
       <c r="D21" s="5" t="n">
         <v>0.006</v>
       </c>
-      <c r="E21" s="5"/>
+      <c r="E21" s="5" t="n">
+        <v>0.005</v>
+      </c>
       <c r="F21" s="5" t="n">
         <v>0.003</v>
       </c>
@@ -11853,7 +11889,9 @@
       <c r="D22" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="E22" s="5"/>
+      <c r="E22" s="5" t="n">
+        <v>1.2</v>
+      </c>
       <c r="F22" s="5" t="n">
         <v>1.9</v>
       </c>
@@ -12307,7 +12345,9 @@
       <c r="D23" s="5" t="n">
         <v>325</v>
       </c>
-      <c r="E23" s="5"/>
+      <c r="E23" s="5" t="n">
+        <v>466</v>
+      </c>
       <c r="F23" s="5" t="n">
         <v>14</v>
       </c>
@@ -12761,7 +12801,9 @@
       <c r="D24" s="5" t="n">
         <v>56</v>
       </c>
-      <c r="E24" s="5"/>
+      <c r="E24" s="5" t="n">
+        <v>56</v>
+      </c>
       <c r="F24" s="5" t="n">
         <v>45</v>
       </c>
@@ -13215,7 +13257,9 @@
       <c r="D25" s="5" t="n">
         <v>0.61</v>
       </c>
-      <c r="E25" s="5"/>
+      <c r="E25" s="5" t="n">
+        <v>0.61</v>
+      </c>
       <c r="F25" s="5" t="n">
         <v>5.67</v>
       </c>
@@ -13669,7 +13713,9 @@
       <c r="D26" s="5" t="n">
         <v>0.99</v>
       </c>
-      <c r="E26" s="5"/>
+      <c r="E26" s="5" t="n">
+        <v>7.43</v>
+      </c>
       <c r="F26" s="5" t="n">
         <v>7.38</v>
       </c>
@@ -14123,7 +14169,9 @@
       <c r="D27" s="5" t="n">
         <v>0.99</v>
       </c>
-      <c r="E27" s="5"/>
+      <c r="E27" s="5" t="n">
+        <v>0.99</v>
+      </c>
       <c r="F27" s="5" t="n">
         <v>16.85</v>
       </c>
@@ -14577,7 +14625,9 @@
       <c r="D28" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="E28" s="5"/>
+      <c r="E28" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="F28" s="5" t="s">
         <v>430</v>
       </c>
@@ -15031,7 +15081,9 @@
       <c r="D29" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E29" s="5"/>
+      <c r="E29" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="F29" s="5" t="s">
         <v>430</v>
       </c>
@@ -15485,7 +15537,9 @@
       <c r="D30" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="E30" s="5"/>
+      <c r="E30" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="F30" s="5" t="s">
         <v>430</v>
       </c>
@@ -15939,7 +15993,9 @@
       <c r="D31" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E31" s="5"/>
+      <c r="E31" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="F31" s="5" t="s">
         <v>430</v>
       </c>
@@ -16393,7 +16449,9 @@
       <c r="D32" s="5" t="n">
         <v>5068.28</v>
       </c>
-      <c r="E32" s="5"/>
+      <c r="E32" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="F32" s="5" t="s">
         <v>430</v>
       </c>
@@ -16847,7 +16905,9 @@
       <c r="D33" s="5" t="n">
         <v>5.155</v>
       </c>
-      <c r="E33" s="5"/>
+      <c r="E33" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="F33" s="5" t="s">
         <v>430</v>
       </c>
@@ -17301,7 +17361,9 @@
       <c r="D34" s="5" t="n">
         <v>128000000</v>
       </c>
-      <c r="E34" s="5"/>
+      <c r="E34" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="F34" s="5" t="s">
         <v>430</v>
       </c>
@@ -17755,7 +17817,9 @@
       <c r="D35" s="5" t="n">
         <v>5.16</v>
       </c>
-      <c r="E35" s="5"/>
+      <c r="E35" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="F35" s="5" t="s">
         <v>430</v>
       </c>
@@ -18209,7 +18273,9 @@
       <c r="D36" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="E36" s="5"/>
+      <c r="E36" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="F36" s="5" t="s">
         <v>430</v>
       </c>
@@ -18663,7 +18729,9 @@
       <c r="D37" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="E37" s="5"/>
+      <c r="E37" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="F37" s="5" t="s">
         <v>430</v>
       </c>
@@ -19117,7 +19185,9 @@
       <c r="D38" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="E38" s="5"/>
+      <c r="E38" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="F38" s="5" t="s">
         <v>430</v>
       </c>
@@ -19571,7 +19641,9 @@
       <c r="D39" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="E39" s="5"/>
+      <c r="E39" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="F39" s="5" t="s">
         <v>430</v>
       </c>
@@ -20025,7 +20097,9 @@
       <c r="D40" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="E40" s="5"/>
+      <c r="E40" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="F40" s="5" t="s">
         <v>430</v>
       </c>
@@ -20479,7 +20553,9 @@
       <c r="D41" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="E41" s="5"/>
+      <c r="E41" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="F41" s="5" t="s">
         <v>430</v>
       </c>
@@ -20933,7 +21009,9 @@
       <c r="D42" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="E42" s="5"/>
+      <c r="E42" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="F42" s="5" t="s">
         <v>430</v>
       </c>
@@ -21387,7 +21465,9 @@
       <c r="D43" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="E43" s="5"/>
+      <c r="E43" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="F43" s="5" t="s">
         <v>430</v>
       </c>
@@ -21841,7 +21921,9 @@
       <c r="D44" s="5" t="n">
         <v>9142.04</v>
       </c>
-      <c r="E44" s="5"/>
+      <c r="E44" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="F44" s="5" t="s">
         <v>430</v>
       </c>
@@ -22295,7 +22377,9 @@
       <c r="D45" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="E45" s="5"/>
+      <c r="E45" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="F45" s="5" t="s">
         <v>430</v>
       </c>
@@ -22749,7 +22833,9 @@
       <c r="D46" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="E46" s="5"/>
+      <c r="E46" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="F46" s="5" t="s">
         <v>430</v>
       </c>
@@ -23203,7 +23289,9 @@
       <c r="D47" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="E47" s="5"/>
+      <c r="E47" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="F47" s="5" t="s">
         <v>430</v>
       </c>
@@ -23657,7 +23745,9 @@
       <c r="D48" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="E48" s="5"/>
+      <c r="E48" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="F48" s="5" t="s">
         <v>430</v>
       </c>
@@ -24111,7 +24201,9 @@
       <c r="D49" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="E49" s="5"/>
+      <c r="E49" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="F49" s="5" t="s">
         <v>430</v>
       </c>
@@ -24565,7 +24657,9 @@
       <c r="D50" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="E50" s="5"/>
+      <c r="E50" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="F50" s="5" t="s">
         <v>430</v>
       </c>
@@ -25019,7 +25113,9 @@
       <c r="D51" s="5" t="n">
         <v>161.03</v>
       </c>
-      <c r="E51" s="5"/>
+      <c r="E51" s="5" t="n">
+        <v>168.63</v>
+      </c>
       <c r="F51" s="5" t="s">
         <v>430</v>
       </c>
@@ -25473,7 +25569,9 @@
       <c r="D52" s="5" t="n">
         <v>26.5</v>
       </c>
-      <c r="E52" s="5"/>
+      <c r="E52" s="5" t="n">
+        <v>26.68</v>
+      </c>
       <c r="F52" s="5" t="s">
         <v>430</v>
       </c>
@@ -25927,7 +26025,9 @@
       <c r="D53" s="5" t="n">
         <v>101.85</v>
       </c>
-      <c r="E53" s="5"/>
+      <c r="E53" s="5" t="n">
+        <v>101.41</v>
+      </c>
       <c r="F53" s="5" t="s">
         <v>430</v>
       </c>
@@ -26381,7 +26481,9 @@
       <c r="D54" s="5" t="n">
         <v>103.1</v>
       </c>
-      <c r="E54" s="5"/>
+      <c r="E54" s="5" t="n">
+        <v>102.72</v>
+      </c>
       <c r="F54" s="5" t="s">
         <v>430</v>
       </c>
@@ -26835,7 +26937,9 @@
       <c r="D55" s="5" t="n">
         <v>60.29</v>
       </c>
-      <c r="E55" s="5"/>
+      <c r="E55" s="5" t="n">
+        <v>63.31</v>
+      </c>
       <c r="F55" s="5" t="s">
         <v>430</v>
       </c>
@@ -27289,7 +27393,9 @@
       <c r="D56" s="5" t="n">
         <v>5.49</v>
       </c>
-      <c r="E56" s="5"/>
+      <c r="E56" s="5" t="n">
+        <v>5.65</v>
+      </c>
       <c r="F56" s="5" t="s">
         <v>430</v>
       </c>
@@ -27743,7 +27849,9 @@
       <c r="D57" s="5" t="n">
         <v>-0.431</v>
       </c>
-      <c r="E57" s="5"/>
+      <c r="E57" s="5" t="n">
+        <v>-3.4</v>
+      </c>
       <c r="F57" s="5" t="s">
         <v>430</v>
       </c>
@@ -28197,7 +28305,9 @@
       <c r="D58" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="E58" s="5"/>
+      <c r="E58" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="F58" s="5" t="s">
         <v>430</v>
       </c>
@@ -28651,7 +28761,9 @@
       <c r="D59" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="E59" s="5"/>
+      <c r="E59" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="F59" s="5" t="s">
         <v>430</v>
       </c>
@@ -29105,7 +29217,9 @@
       <c r="D60" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="E60" s="5"/>
+      <c r="E60" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="F60" s="5" t="s">
         <v>430</v>
       </c>
@@ -29559,7 +29673,9 @@
       <c r="D61" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="E61" s="5"/>
+      <c r="E61" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="F61" s="5" t="s">
         <v>430</v>
       </c>
@@ -30013,7 +30129,9 @@
       <c r="D62" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="E62" s="5"/>
+      <c r="E62" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="F62" s="5" t="s">
         <v>430</v>
       </c>
@@ -30467,7 +30585,9 @@
       <c r="D63" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="E63" s="5"/>
+      <c r="E63" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="F63" s="5" t="s">
         <v>430</v>
       </c>
@@ -30921,7 +31041,9 @@
       <c r="D64" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="E64" s="5"/>
+      <c r="E64" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="F64" s="5" t="s">
         <v>430</v>
       </c>
@@ -31375,7 +31497,9 @@
       <c r="D65" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="E65" s="5"/>
+      <c r="E65" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="F65" s="5" t="n">
         <v>520</v>
       </c>
@@ -31829,7 +31953,9 @@
       <c r="D66" s="5" t="n">
         <v>86</v>
       </c>
-      <c r="E66" s="5"/>
+      <c r="E66" s="5" t="n">
+        <v>93</v>
+      </c>
       <c r="F66" s="5" t="s">
         <v>430</v>
       </c>
@@ -32272,10 +32398,10 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>430</v>
@@ -32283,7 +32409,9 @@
       <c r="D67" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="E67" s="5"/>
+      <c r="E67" s="5" t="n">
+        <v>631</v>
+      </c>
       <c r="F67" s="5" t="s">
         <v>430</v>
       </c>
@@ -32724,6 +32852,462 @@
       <c r="PI67" s="5"/>
       <c r="PJ67" s="5"/>
     </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>511</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="F68" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="G68" s="5"/>
+      <c r="H68" s="5"/>
+      <c r="I68" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="J68" s="5"/>
+      <c r="K68" s="5"/>
+      <c r="L68" s="5"/>
+      <c r="M68" s="5"/>
+      <c r="N68" s="5"/>
+      <c r="O68" s="5"/>
+      <c r="P68" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="Q68" s="5"/>
+      <c r="R68" s="5"/>
+      <c r="S68" s="5"/>
+      <c r="T68" s="5"/>
+      <c r="U68" s="5"/>
+      <c r="V68" s="5"/>
+      <c r="W68" s="5"/>
+      <c r="X68" s="5"/>
+      <c r="Y68" s="5"/>
+      <c r="Z68" s="5"/>
+      <c r="AA68" s="5"/>
+      <c r="AB68" s="5"/>
+      <c r="AC68" s="5"/>
+      <c r="AD68" s="5"/>
+      <c r="AE68" s="5"/>
+      <c r="AF68" s="5"/>
+      <c r="AG68" s="5"/>
+      <c r="AH68" s="5"/>
+      <c r="AI68" s="5"/>
+      <c r="AJ68" s="5"/>
+      <c r="AK68" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="AL68" s="5"/>
+      <c r="AM68" s="5"/>
+      <c r="AN68" s="5"/>
+      <c r="AO68" s="5"/>
+      <c r="AP68" s="5"/>
+      <c r="AQ68" s="5"/>
+      <c r="AR68" s="5"/>
+      <c r="AS68" s="5"/>
+      <c r="AT68" s="5"/>
+      <c r="AU68" s="5"/>
+      <c r="AV68" s="5"/>
+      <c r="AW68" s="5"/>
+      <c r="AX68" s="5"/>
+      <c r="AY68" s="5"/>
+      <c r="AZ68" s="5"/>
+      <c r="BA68" s="5"/>
+      <c r="BB68" s="5"/>
+      <c r="BC68" s="5"/>
+      <c r="BD68" s="5"/>
+      <c r="BE68" s="5"/>
+      <c r="BF68" s="5"/>
+      <c r="BG68" s="5"/>
+      <c r="BH68" s="5"/>
+      <c r="BI68" s="5"/>
+      <c r="BJ68" s="5"/>
+      <c r="BK68" s="5"/>
+      <c r="BL68" s="5"/>
+      <c r="BM68" s="5"/>
+      <c r="BN68" s="5"/>
+      <c r="BO68" s="5"/>
+      <c r="BP68" s="5"/>
+      <c r="BQ68" s="5"/>
+      <c r="BR68" s="5"/>
+      <c r="BS68" s="5"/>
+      <c r="BT68" s="5"/>
+      <c r="BU68" s="5"/>
+      <c r="BV68" s="5"/>
+      <c r="BW68" s="5"/>
+      <c r="BX68" s="5"/>
+      <c r="BY68" s="5"/>
+      <c r="BZ68" s="5"/>
+      <c r="CA68" s="5"/>
+      <c r="CB68" s="5"/>
+      <c r="CC68" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="CD68" s="5"/>
+      <c r="CE68" s="5"/>
+      <c r="CF68" s="5"/>
+      <c r="CG68" s="5"/>
+      <c r="CH68" s="5"/>
+      <c r="CI68" s="5"/>
+      <c r="CJ68" s="5"/>
+      <c r="CK68" s="5"/>
+      <c r="CL68" s="5"/>
+      <c r="CM68" s="5"/>
+      <c r="CN68" s="5"/>
+      <c r="CO68" s="5"/>
+      <c r="CP68" s="5"/>
+      <c r="CQ68" s="5"/>
+      <c r="CR68" s="5"/>
+      <c r="CS68" s="5"/>
+      <c r="CT68" s="5"/>
+      <c r="CU68" s="5"/>
+      <c r="CV68" s="5"/>
+      <c r="CW68" s="5"/>
+      <c r="CX68" s="5"/>
+      <c r="CY68" s="5"/>
+      <c r="CZ68" s="5"/>
+      <c r="DA68" s="5"/>
+      <c r="DB68" s="5"/>
+      <c r="DC68" s="5"/>
+      <c r="DD68" s="5"/>
+      <c r="DE68" s="5"/>
+      <c r="DF68" s="5"/>
+      <c r="DG68" s="5"/>
+      <c r="DH68" s="5"/>
+      <c r="DI68" s="5"/>
+      <c r="DJ68" s="5"/>
+      <c r="DK68" s="5"/>
+      <c r="DL68" s="5"/>
+      <c r="DM68" s="5"/>
+      <c r="DN68" s="5"/>
+      <c r="DO68" s="5"/>
+      <c r="DP68" s="5"/>
+      <c r="DQ68" s="5"/>
+      <c r="DR68" s="5"/>
+      <c r="DS68" s="5"/>
+      <c r="DT68" s="5"/>
+      <c r="DU68" s="5"/>
+      <c r="DV68" s="5"/>
+      <c r="DW68" s="5"/>
+      <c r="DX68" s="5"/>
+      <c r="DY68" s="5"/>
+      <c r="DZ68" s="5"/>
+      <c r="EA68" s="5"/>
+      <c r="EB68" s="5"/>
+      <c r="EC68" s="5"/>
+      <c r="ED68" s="5"/>
+      <c r="EE68" s="5"/>
+      <c r="EF68" s="5"/>
+      <c r="EG68" s="5"/>
+      <c r="EH68" s="5"/>
+      <c r="EI68" s="5"/>
+      <c r="EJ68" s="5"/>
+      <c r="EK68" s="5"/>
+      <c r="EL68" s="5"/>
+      <c r="EM68" s="5"/>
+      <c r="EN68" s="5"/>
+      <c r="EO68" s="5"/>
+      <c r="EP68" s="5"/>
+      <c r="EQ68" s="5"/>
+      <c r="ER68" s="5"/>
+      <c r="ES68" s="5"/>
+      <c r="ET68" s="5"/>
+      <c r="EU68" s="5"/>
+      <c r="EV68" s="5"/>
+      <c r="EW68" s="5"/>
+      <c r="EX68" s="5"/>
+      <c r="EY68" s="5"/>
+      <c r="EZ68" s="5"/>
+      <c r="FA68" s="5"/>
+      <c r="FB68" s="5"/>
+      <c r="FC68" s="5"/>
+      <c r="FD68" s="5"/>
+      <c r="FE68" s="5"/>
+      <c r="FF68" s="5"/>
+      <c r="FG68" s="5"/>
+      <c r="FH68" s="5"/>
+      <c r="FI68" s="5"/>
+      <c r="FJ68" s="5"/>
+      <c r="FK68" s="5"/>
+      <c r="FL68" s="5"/>
+      <c r="FM68" s="5"/>
+      <c r="FN68" s="5"/>
+      <c r="FO68" s="5"/>
+      <c r="FP68" s="5"/>
+      <c r="FQ68" s="5"/>
+      <c r="FR68" s="5"/>
+      <c r="FS68" s="5"/>
+      <c r="FT68" s="5"/>
+      <c r="FU68" s="5"/>
+      <c r="FV68" s="5"/>
+      <c r="FW68" s="5"/>
+      <c r="FX68" s="5"/>
+      <c r="FY68" s="5"/>
+      <c r="FZ68" s="5"/>
+      <c r="GA68" s="5"/>
+      <c r="GB68" s="5"/>
+      <c r="GC68" s="5"/>
+      <c r="GD68" s="5"/>
+      <c r="GE68" s="5"/>
+      <c r="GF68" s="5"/>
+      <c r="GG68" s="5"/>
+      <c r="GH68" s="5"/>
+      <c r="GI68" s="5"/>
+      <c r="GJ68" s="5"/>
+      <c r="GK68" s="5"/>
+      <c r="GL68" s="5"/>
+      <c r="GM68" s="5"/>
+      <c r="GN68" s="5"/>
+      <c r="GO68" s="5"/>
+      <c r="GP68" s="5"/>
+      <c r="GQ68" s="5"/>
+      <c r="GR68" s="5"/>
+      <c r="GS68" s="5"/>
+      <c r="GT68" s="5"/>
+      <c r="GU68" s="5"/>
+      <c r="GV68" s="5"/>
+      <c r="GW68" s="5"/>
+      <c r="GX68" s="5"/>
+      <c r="GY68" s="5"/>
+      <c r="GZ68" s="5"/>
+      <c r="HA68" s="5"/>
+      <c r="HB68" s="5"/>
+      <c r="HC68" s="5"/>
+      <c r="HD68" s="5"/>
+      <c r="HE68" s="5"/>
+      <c r="HF68" s="5"/>
+      <c r="HG68" s="5"/>
+      <c r="HH68" s="5"/>
+      <c r="HI68" s="5"/>
+      <c r="HJ68" s="5"/>
+      <c r="HK68" s="5"/>
+      <c r="HL68" s="5"/>
+      <c r="HM68" s="5"/>
+      <c r="HN68" s="5"/>
+      <c r="HO68" s="5"/>
+      <c r="HP68" s="5"/>
+      <c r="HQ68" s="5"/>
+      <c r="HR68" s="5"/>
+      <c r="HS68" s="5"/>
+      <c r="HT68" s="5"/>
+      <c r="HU68" s="5"/>
+      <c r="HV68" s="5"/>
+      <c r="HW68" s="5"/>
+      <c r="HX68" s="5"/>
+      <c r="HY68" s="5"/>
+      <c r="HZ68" s="5"/>
+      <c r="IA68" s="5"/>
+      <c r="IB68" s="5"/>
+      <c r="IC68" s="5"/>
+      <c r="ID68" s="5"/>
+      <c r="IE68" s="5"/>
+      <c r="IF68" s="5"/>
+      <c r="IG68" s="5"/>
+      <c r="IH68" s="5"/>
+      <c r="II68" s="5"/>
+      <c r="IJ68" s="5"/>
+      <c r="IK68" s="5"/>
+      <c r="IL68" s="5"/>
+      <c r="IM68" s="5"/>
+      <c r="IN68" s="5"/>
+      <c r="IO68" s="5"/>
+      <c r="IP68" s="5"/>
+      <c r="IQ68" s="5"/>
+      <c r="IR68" s="5"/>
+      <c r="IS68" s="5"/>
+      <c r="IT68" s="5"/>
+      <c r="IU68" s="5"/>
+      <c r="IV68" s="5"/>
+      <c r="IW68" s="5"/>
+      <c r="IX68" s="5"/>
+      <c r="IY68" s="5"/>
+      <c r="IZ68" s="5"/>
+      <c r="JA68" s="5"/>
+      <c r="JB68" s="5"/>
+      <c r="JC68" s="5"/>
+      <c r="JD68" s="5"/>
+      <c r="JE68" s="5"/>
+      <c r="JF68" s="5"/>
+      <c r="JG68" s="5"/>
+      <c r="JH68" s="5"/>
+      <c r="JI68" s="5"/>
+      <c r="JJ68" s="5"/>
+      <c r="JK68" s="5"/>
+      <c r="JL68" s="5"/>
+      <c r="JM68" s="5"/>
+      <c r="JN68" s="5"/>
+      <c r="JO68" s="5"/>
+      <c r="JP68" s="5"/>
+      <c r="JQ68" s="5"/>
+      <c r="JR68" s="5"/>
+      <c r="JS68" s="5"/>
+      <c r="JT68" s="5"/>
+      <c r="JU68" s="5"/>
+      <c r="JV68" s="5"/>
+      <c r="JW68" s="5"/>
+      <c r="JX68" s="5"/>
+      <c r="JY68" s="5"/>
+      <c r="JZ68" s="5"/>
+      <c r="KA68" s="5"/>
+      <c r="KB68" s="5"/>
+      <c r="KC68" s="5"/>
+      <c r="KD68" s="5"/>
+      <c r="KE68" s="5"/>
+      <c r="KF68" s="5"/>
+      <c r="KG68" s="5"/>
+      <c r="KH68" s="5"/>
+      <c r="KI68" s="5"/>
+      <c r="KJ68" s="5"/>
+      <c r="KK68" s="5"/>
+      <c r="KL68" s="5"/>
+      <c r="KM68" s="5"/>
+      <c r="KN68" s="5"/>
+      <c r="KO68" s="5"/>
+      <c r="KP68" s="5"/>
+      <c r="KQ68" s="5"/>
+      <c r="KR68" s="5"/>
+      <c r="KS68" s="5"/>
+      <c r="KT68" s="5"/>
+      <c r="KU68" s="5"/>
+      <c r="KV68" s="5"/>
+      <c r="KW68" s="5"/>
+      <c r="KX68" s="5"/>
+      <c r="KY68" s="5"/>
+      <c r="KZ68" s="5"/>
+      <c r="LA68" s="5"/>
+      <c r="LB68" s="5"/>
+      <c r="LC68" s="5"/>
+      <c r="LD68" s="5"/>
+      <c r="LE68" s="5"/>
+      <c r="LF68" s="5"/>
+      <c r="LG68" s="5"/>
+      <c r="LH68" s="5"/>
+      <c r="LI68" s="5"/>
+      <c r="LJ68" s="5"/>
+      <c r="LK68" s="5"/>
+      <c r="LL68" s="5"/>
+      <c r="LM68" s="5"/>
+      <c r="LN68" s="5"/>
+      <c r="LO68" s="5"/>
+      <c r="LP68" s="5"/>
+      <c r="LQ68" s="5"/>
+      <c r="LR68" s="5"/>
+      <c r="LS68" s="5"/>
+      <c r="LT68" s="5"/>
+      <c r="LU68" s="5"/>
+      <c r="LV68" s="5"/>
+      <c r="LW68" s="5"/>
+      <c r="LX68" s="5"/>
+      <c r="LY68" s="5"/>
+      <c r="LZ68" s="5"/>
+      <c r="MA68" s="5"/>
+      <c r="MB68" s="5"/>
+      <c r="MC68" s="5"/>
+      <c r="MD68" s="5"/>
+      <c r="ME68" s="5"/>
+      <c r="MF68" s="5"/>
+      <c r="MG68" s="5"/>
+      <c r="MH68" s="5"/>
+      <c r="MI68" s="5"/>
+      <c r="MJ68" s="5"/>
+      <c r="MK68" s="5"/>
+      <c r="ML68" s="5"/>
+      <c r="MM68" s="5"/>
+      <c r="MN68" s="5"/>
+      <c r="MO68" s="5"/>
+      <c r="MP68" s="5"/>
+      <c r="MQ68" s="5"/>
+      <c r="MR68" s="5"/>
+      <c r="MS68" s="5"/>
+      <c r="MT68" s="5"/>
+      <c r="MU68" s="5"/>
+      <c r="MV68" s="5"/>
+      <c r="MW68" s="5"/>
+      <c r="MX68" s="5"/>
+      <c r="MY68" s="5"/>
+      <c r="MZ68" s="5"/>
+      <c r="NA68" s="5"/>
+      <c r="NB68" s="5"/>
+      <c r="NC68" s="5"/>
+      <c r="ND68" s="5"/>
+      <c r="NE68" s="5"/>
+      <c r="NF68" s="5"/>
+      <c r="NG68" s="5"/>
+      <c r="NH68" s="5"/>
+      <c r="NI68" s="5"/>
+      <c r="NJ68" s="5"/>
+      <c r="NK68" s="5"/>
+      <c r="NL68" s="5"/>
+      <c r="NM68" s="5"/>
+      <c r="NN68" s="5"/>
+      <c r="NO68" s="5"/>
+      <c r="NP68" s="5"/>
+      <c r="NQ68" s="5"/>
+      <c r="NR68" s="5"/>
+      <c r="NS68" s="5"/>
+      <c r="NT68" s="5"/>
+      <c r="NU68" s="5"/>
+      <c r="NV68" s="5"/>
+      <c r="NW68" s="5"/>
+      <c r="NX68" s="5"/>
+      <c r="NY68" s="5"/>
+      <c r="NZ68" s="5"/>
+      <c r="OA68" s="5"/>
+      <c r="OB68" s="5"/>
+      <c r="OC68" s="5"/>
+      <c r="OD68" s="5"/>
+      <c r="OE68" s="5"/>
+      <c r="OF68" s="5"/>
+      <c r="OG68" s="5"/>
+      <c r="OH68" s="5"/>
+      <c r="OI68" s="5"/>
+      <c r="OJ68" s="5"/>
+      <c r="OK68" s="5"/>
+      <c r="OL68" s="5"/>
+      <c r="OM68" s="5"/>
+      <c r="ON68" s="5"/>
+      <c r="OO68" s="5"/>
+      <c r="OP68" s="5"/>
+      <c r="OQ68" s="5"/>
+      <c r="OR68" s="5"/>
+      <c r="OS68" s="5"/>
+      <c r="OT68" s="5"/>
+      <c r="OU68" s="5"/>
+      <c r="OV68" s="5"/>
+      <c r="OW68" s="5"/>
+      <c r="OX68" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="OY68" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="OZ68" s="5"/>
+      <c r="PA68" s="5"/>
+      <c r="PB68" s="5"/>
+      <c r="PC68" s="5"/>
+      <c r="PD68" s="5"/>
+      <c r="PE68" s="5"/>
+      <c r="PF68" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="PG68" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="PH68" s="5"/>
+      <c r="PI68" s="5"/>
+      <c r="PJ68" s="5"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:PJ1"/>

--- a/Part2_PlatformBenchmarks_Results_v1.0.0.xlsx
+++ b/Part2_PlatformBenchmarks_Results_v1.0.0.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1042" uniqueCount="512">
   <si>
     <t xml:space="preserve">Arduino Benchmark Suite – Part 2: Platform Benchmarks</t>
   </si>
@@ -3704,7 +3704,9 @@
       <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
       <c r="S4" s="5"/>
-      <c r="T4" s="5"/>
+      <c r="T4" s="5" t="n">
+        <v>3.34</v>
+      </c>
       <c r="U4" s="5"/>
       <c r="V4" s="5"/>
       <c r="W4" s="5"/>
@@ -4160,7 +4162,9 @@
       <c r="Q5" s="5"/>
       <c r="R5" s="5"/>
       <c r="S5" s="5"/>
-      <c r="T5" s="5"/>
+      <c r="T5" s="5" t="n">
+        <v>-0.2</v>
+      </c>
       <c r="U5" s="5"/>
       <c r="V5" s="5"/>
       <c r="W5" s="5"/>
@@ -4616,7 +4620,9 @@
       <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
       <c r="S6" s="5"/>
-      <c r="T6" s="5"/>
+      <c r="T6" s="5" t="n">
+        <v>4.34</v>
+      </c>
       <c r="U6" s="5"/>
       <c r="V6" s="5"/>
       <c r="W6" s="5"/>
@@ -5072,7 +5078,9 @@
       <c r="Q7" s="5"/>
       <c r="R7" s="5"/>
       <c r="S7" s="5"/>
-      <c r="T7" s="5"/>
+      <c r="T7" s="5" t="n">
+        <v>6.01</v>
+      </c>
       <c r="U7" s="5"/>
       <c r="V7" s="5"/>
       <c r="W7" s="5"/>
@@ -5528,7 +5536,9 @@
       <c r="Q8" s="5"/>
       <c r="R8" s="5"/>
       <c r="S8" s="5"/>
-      <c r="T8" s="5"/>
+      <c r="T8" s="5" t="n">
+        <v>5.72</v>
+      </c>
       <c r="U8" s="5"/>
       <c r="V8" s="5"/>
       <c r="W8" s="5"/>
@@ -5984,7 +5994,9 @@
       <c r="Q9" s="5"/>
       <c r="R9" s="5"/>
       <c r="S9" s="5"/>
-      <c r="T9" s="5"/>
+      <c r="T9" s="5" t="n">
+        <v>2.8</v>
+      </c>
       <c r="U9" s="5"/>
       <c r="V9" s="5"/>
       <c r="W9" s="5"/>
@@ -6440,7 +6452,9 @@
       <c r="Q10" s="5"/>
       <c r="R10" s="5"/>
       <c r="S10" s="5"/>
-      <c r="T10" s="5"/>
+      <c r="T10" s="5" t="n">
+        <v>4.91</v>
+      </c>
       <c r="U10" s="5"/>
       <c r="V10" s="5"/>
       <c r="W10" s="5"/>
@@ -6896,7 +6910,9 @@
       <c r="Q11" s="5"/>
       <c r="R11" s="5"/>
       <c r="S11" s="5"/>
-      <c r="T11" s="5"/>
+      <c r="T11" s="5" t="n">
+        <v>5.35</v>
+      </c>
       <c r="U11" s="5"/>
       <c r="V11" s="5"/>
       <c r="W11" s="5"/>
@@ -7352,7 +7368,9 @@
       <c r="Q12" s="5"/>
       <c r="R12" s="5"/>
       <c r="S12" s="5"/>
-      <c r="T12" s="5"/>
+      <c r="T12" s="5" t="n">
+        <v>4.9</v>
+      </c>
       <c r="U12" s="5"/>
       <c r="V12" s="5"/>
       <c r="W12" s="5"/>
@@ -7808,7 +7826,9 @@
       <c r="Q13" s="5"/>
       <c r="R13" s="5"/>
       <c r="S13" s="5"/>
-      <c r="T13" s="5"/>
+      <c r="T13" s="5" t="n">
+        <v>5.79</v>
+      </c>
       <c r="U13" s="5"/>
       <c r="V13" s="5"/>
       <c r="W13" s="5"/>
@@ -8264,7 +8284,9 @@
       <c r="Q14" s="5"/>
       <c r="R14" s="5"/>
       <c r="S14" s="5"/>
-      <c r="T14" s="5"/>
+      <c r="T14" s="5" t="n">
+        <v>34.54</v>
+      </c>
       <c r="U14" s="5"/>
       <c r="V14" s="5"/>
       <c r="W14" s="5"/>
@@ -8720,7 +8742,9 @@
       <c r="Q15" s="5"/>
       <c r="R15" s="5"/>
       <c r="S15" s="5"/>
-      <c r="T15" s="5"/>
+      <c r="T15" s="5" t="n">
+        <v>17.63</v>
+      </c>
       <c r="U15" s="5"/>
       <c r="V15" s="5"/>
       <c r="W15" s="5"/>
@@ -9176,7 +9200,9 @@
       <c r="Q16" s="5"/>
       <c r="R16" s="5"/>
       <c r="S16" s="5"/>
-      <c r="T16" s="5"/>
+      <c r="T16" s="5" t="n">
+        <v>11.52</v>
+      </c>
       <c r="U16" s="5"/>
       <c r="V16" s="5"/>
       <c r="W16" s="5"/>
@@ -9632,7 +9658,9 @@
       <c r="Q17" s="5"/>
       <c r="R17" s="5"/>
       <c r="S17" s="5"/>
-      <c r="T17" s="5"/>
+      <c r="T17" s="5" t="n">
+        <v>65.34</v>
+      </c>
       <c r="U17" s="5"/>
       <c r="V17" s="5"/>
       <c r="W17" s="5"/>
@@ -10088,7 +10116,9 @@
       <c r="Q18" s="5"/>
       <c r="R18" s="5"/>
       <c r="S18" s="5"/>
-      <c r="T18" s="5"/>
+      <c r="T18" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="U18" s="5"/>
       <c r="V18" s="5"/>
       <c r="W18" s="5"/>
@@ -10544,7 +10574,9 @@
       <c r="Q19" s="5"/>
       <c r="R19" s="5"/>
       <c r="S19" s="5"/>
-      <c r="T19" s="5"/>
+      <c r="T19" s="5" t="n">
+        <v>4</v>
+      </c>
       <c r="U19" s="5"/>
       <c r="V19" s="5"/>
       <c r="W19" s="5"/>
@@ -11000,7 +11032,9 @@
       <c r="Q20" s="5"/>
       <c r="R20" s="5"/>
       <c r="S20" s="5"/>
-      <c r="T20" s="5"/>
+      <c r="T20" s="5" t="n">
+        <v>120</v>
+      </c>
       <c r="U20" s="5"/>
       <c r="V20" s="5"/>
       <c r="W20" s="5"/>
@@ -11456,7 +11490,9 @@
       <c r="Q21" s="5"/>
       <c r="R21" s="5"/>
       <c r="S21" s="5"/>
-      <c r="T21" s="5"/>
+      <c r="T21" s="5" t="n">
+        <v>0.003</v>
+      </c>
       <c r="U21" s="5"/>
       <c r="V21" s="5"/>
       <c r="W21" s="5"/>
@@ -11912,7 +11948,9 @@
       <c r="Q22" s="5"/>
       <c r="R22" s="5"/>
       <c r="S22" s="5"/>
-      <c r="T22" s="5"/>
+      <c r="T22" s="5" t="n">
+        <v>1.6</v>
+      </c>
       <c r="U22" s="5"/>
       <c r="V22" s="5"/>
       <c r="W22" s="5"/>
@@ -12368,7 +12406,9 @@
       <c r="Q23" s="5"/>
       <c r="R23" s="5"/>
       <c r="S23" s="5"/>
-      <c r="T23" s="5"/>
+      <c r="T23" s="5" t="n">
+        <v>153</v>
+      </c>
       <c r="U23" s="5"/>
       <c r="V23" s="5"/>
       <c r="W23" s="5"/>
@@ -12824,7 +12864,9 @@
       <c r="Q24" s="5"/>
       <c r="R24" s="5"/>
       <c r="S24" s="5"/>
-      <c r="T24" s="5"/>
+      <c r="T24" s="5" t="n">
+        <v>44</v>
+      </c>
       <c r="U24" s="5"/>
       <c r="V24" s="5"/>
       <c r="W24" s="5"/>
@@ -13280,7 +13322,9 @@
       <c r="Q25" s="5"/>
       <c r="R25" s="5"/>
       <c r="S25" s="5"/>
-      <c r="T25" s="5"/>
+      <c r="T25" s="5" t="n">
+        <v>5.02</v>
+      </c>
       <c r="U25" s="5"/>
       <c r="V25" s="5"/>
       <c r="W25" s="5"/>
@@ -13736,7 +13780,9 @@
       <c r="Q26" s="5"/>
       <c r="R26" s="5"/>
       <c r="S26" s="5"/>
-      <c r="T26" s="5"/>
+      <c r="T26" s="5" t="n">
+        <v>7.37</v>
+      </c>
       <c r="U26" s="5"/>
       <c r="V26" s="5"/>
       <c r="W26" s="5"/>
@@ -14192,7 +14238,9 @@
       <c r="Q27" s="5"/>
       <c r="R27" s="5"/>
       <c r="S27" s="5"/>
-      <c r="T27" s="5"/>
+      <c r="T27" s="5" t="n">
+        <v>17.83</v>
+      </c>
       <c r="U27" s="5"/>
       <c r="V27" s="5"/>
       <c r="W27" s="5"/>
@@ -14648,7 +14696,9 @@
       <c r="Q28" s="5"/>
       <c r="R28" s="5"/>
       <c r="S28" s="5"/>
-      <c r="T28" s="5"/>
+      <c r="T28" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U28" s="5"/>
       <c r="V28" s="5"/>
       <c r="W28" s="5"/>
@@ -15104,7 +15154,9 @@
       <c r="Q29" s="5"/>
       <c r="R29" s="5"/>
       <c r="S29" s="5"/>
-      <c r="T29" s="5"/>
+      <c r="T29" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U29" s="5"/>
       <c r="V29" s="5"/>
       <c r="W29" s="5"/>
@@ -15560,7 +15612,9 @@
       <c r="Q30" s="5"/>
       <c r="R30" s="5"/>
       <c r="S30" s="5"/>
-      <c r="T30" s="5"/>
+      <c r="T30" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U30" s="5"/>
       <c r="V30" s="5"/>
       <c r="W30" s="5"/>
@@ -16016,7 +16070,9 @@
       <c r="Q31" s="5"/>
       <c r="R31" s="5"/>
       <c r="S31" s="5"/>
-      <c r="T31" s="5"/>
+      <c r="T31" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U31" s="5"/>
       <c r="V31" s="5"/>
       <c r="W31" s="5"/>
@@ -16472,7 +16528,9 @@
       <c r="Q32" s="5"/>
       <c r="R32" s="5"/>
       <c r="S32" s="5"/>
-      <c r="T32" s="5"/>
+      <c r="T32" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U32" s="5"/>
       <c r="V32" s="5"/>
       <c r="W32" s="5"/>
@@ -16928,7 +16986,9 @@
       <c r="Q33" s="5"/>
       <c r="R33" s="5"/>
       <c r="S33" s="5"/>
-      <c r="T33" s="5"/>
+      <c r="T33" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U33" s="5"/>
       <c r="V33" s="5"/>
       <c r="W33" s="5"/>
@@ -17384,7 +17444,9 @@
       <c r="Q34" s="5"/>
       <c r="R34" s="5"/>
       <c r="S34" s="5"/>
-      <c r="T34" s="5"/>
+      <c r="T34" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U34" s="5"/>
       <c r="V34" s="5"/>
       <c r="W34" s="5"/>
@@ -17840,7 +17902,9 @@
       <c r="Q35" s="5"/>
       <c r="R35" s="5"/>
       <c r="S35" s="5"/>
-      <c r="T35" s="5"/>
+      <c r="T35" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U35" s="5"/>
       <c r="V35" s="5"/>
       <c r="W35" s="5"/>
@@ -18296,7 +18360,9 @@
       <c r="Q36" s="5"/>
       <c r="R36" s="5"/>
       <c r="S36" s="5"/>
-      <c r="T36" s="5"/>
+      <c r="T36" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U36" s="5"/>
       <c r="V36" s="5"/>
       <c r="W36" s="5"/>
@@ -18752,7 +18818,9 @@
       <c r="Q37" s="5"/>
       <c r="R37" s="5"/>
       <c r="S37" s="5"/>
-      <c r="T37" s="5"/>
+      <c r="T37" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U37" s="5"/>
       <c r="V37" s="5"/>
       <c r="W37" s="5"/>
@@ -19208,7 +19276,9 @@
       <c r="Q38" s="5"/>
       <c r="R38" s="5"/>
       <c r="S38" s="5"/>
-      <c r="T38" s="5"/>
+      <c r="T38" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U38" s="5"/>
       <c r="V38" s="5"/>
       <c r="W38" s="5"/>
@@ -19664,7 +19734,9 @@
       <c r="Q39" s="5"/>
       <c r="R39" s="5"/>
       <c r="S39" s="5"/>
-      <c r="T39" s="5"/>
+      <c r="T39" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U39" s="5"/>
       <c r="V39" s="5"/>
       <c r="W39" s="5"/>
@@ -20120,7 +20192,9 @@
       <c r="Q40" s="5"/>
       <c r="R40" s="5"/>
       <c r="S40" s="5"/>
-      <c r="T40" s="5"/>
+      <c r="T40" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U40" s="5"/>
       <c r="V40" s="5"/>
       <c r="W40" s="5"/>
@@ -20576,7 +20650,9 @@
       <c r="Q41" s="5"/>
       <c r="R41" s="5"/>
       <c r="S41" s="5"/>
-      <c r="T41" s="5"/>
+      <c r="T41" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U41" s="5"/>
       <c r="V41" s="5"/>
       <c r="W41" s="5"/>
@@ -21032,7 +21108,9 @@
       <c r="Q42" s="5"/>
       <c r="R42" s="5"/>
       <c r="S42" s="5"/>
-      <c r="T42" s="5"/>
+      <c r="T42" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U42" s="5"/>
       <c r="V42" s="5"/>
       <c r="W42" s="5"/>
@@ -21488,7 +21566,9 @@
       <c r="Q43" s="5"/>
       <c r="R43" s="5"/>
       <c r="S43" s="5"/>
-      <c r="T43" s="5"/>
+      <c r="T43" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U43" s="5"/>
       <c r="V43" s="5"/>
       <c r="W43" s="5"/>
@@ -21944,7 +22024,9 @@
       <c r="Q44" s="5"/>
       <c r="R44" s="5"/>
       <c r="S44" s="5"/>
-      <c r="T44" s="5"/>
+      <c r="T44" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U44" s="5"/>
       <c r="V44" s="5"/>
       <c r="W44" s="5"/>
@@ -22400,7 +22482,9 @@
       <c r="Q45" s="5"/>
       <c r="R45" s="5"/>
       <c r="S45" s="5"/>
-      <c r="T45" s="5"/>
+      <c r="T45" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U45" s="5"/>
       <c r="V45" s="5"/>
       <c r="W45" s="5"/>
@@ -22856,7 +22940,9 @@
       <c r="Q46" s="5"/>
       <c r="R46" s="5"/>
       <c r="S46" s="5"/>
-      <c r="T46" s="5"/>
+      <c r="T46" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U46" s="5"/>
       <c r="V46" s="5"/>
       <c r="W46" s="5"/>
@@ -23312,7 +23398,9 @@
       <c r="Q47" s="5"/>
       <c r="R47" s="5"/>
       <c r="S47" s="5"/>
-      <c r="T47" s="5"/>
+      <c r="T47" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U47" s="5"/>
       <c r="V47" s="5"/>
       <c r="W47" s="5"/>
@@ -23768,7 +23856,9 @@
       <c r="Q48" s="5"/>
       <c r="R48" s="5"/>
       <c r="S48" s="5"/>
-      <c r="T48" s="5"/>
+      <c r="T48" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U48" s="5"/>
       <c r="V48" s="5"/>
       <c r="W48" s="5"/>
@@ -24224,7 +24314,9 @@
       <c r="Q49" s="5"/>
       <c r="R49" s="5"/>
       <c r="S49" s="5"/>
-      <c r="T49" s="5"/>
+      <c r="T49" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U49" s="5"/>
       <c r="V49" s="5"/>
       <c r="W49" s="5"/>
@@ -24680,7 +24772,9 @@
       <c r="Q50" s="5"/>
       <c r="R50" s="5"/>
       <c r="S50" s="5"/>
-      <c r="T50" s="5"/>
+      <c r="T50" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U50" s="5"/>
       <c r="V50" s="5"/>
       <c r="W50" s="5"/>
@@ -25136,7 +25230,9 @@
       <c r="Q51" s="5"/>
       <c r="R51" s="5"/>
       <c r="S51" s="5"/>
-      <c r="T51" s="5"/>
+      <c r="T51" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U51" s="5"/>
       <c r="V51" s="5"/>
       <c r="W51" s="5"/>
@@ -25592,7 +25688,9 @@
       <c r="Q52" s="5"/>
       <c r="R52" s="5"/>
       <c r="S52" s="5"/>
-      <c r="T52" s="5"/>
+      <c r="T52" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U52" s="5"/>
       <c r="V52" s="5"/>
       <c r="W52" s="5"/>
@@ -26048,7 +26146,9 @@
       <c r="Q53" s="5"/>
       <c r="R53" s="5"/>
       <c r="S53" s="5"/>
-      <c r="T53" s="5"/>
+      <c r="T53" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U53" s="5"/>
       <c r="V53" s="5"/>
       <c r="W53" s="5"/>
@@ -26504,7 +26604,9 @@
       <c r="Q54" s="5"/>
       <c r="R54" s="5"/>
       <c r="S54" s="5"/>
-      <c r="T54" s="5"/>
+      <c r="T54" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U54" s="5"/>
       <c r="V54" s="5"/>
       <c r="W54" s="5"/>
@@ -26960,7 +27062,9 @@
       <c r="Q55" s="5"/>
       <c r="R55" s="5"/>
       <c r="S55" s="5"/>
-      <c r="T55" s="5"/>
+      <c r="T55" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U55" s="5"/>
       <c r="V55" s="5"/>
       <c r="W55" s="5"/>
@@ -27416,7 +27520,9 @@
       <c r="Q56" s="5"/>
       <c r="R56" s="5"/>
       <c r="S56" s="5"/>
-      <c r="T56" s="5"/>
+      <c r="T56" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U56" s="5"/>
       <c r="V56" s="5"/>
       <c r="W56" s="5"/>
@@ -27872,7 +27978,9 @@
       <c r="Q57" s="5"/>
       <c r="R57" s="5"/>
       <c r="S57" s="5"/>
-      <c r="T57" s="5"/>
+      <c r="T57" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U57" s="5"/>
       <c r="V57" s="5"/>
       <c r="W57" s="5"/>
@@ -28328,7 +28436,9 @@
       <c r="Q58" s="5"/>
       <c r="R58" s="5"/>
       <c r="S58" s="5"/>
-      <c r="T58" s="5"/>
+      <c r="T58" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U58" s="5"/>
       <c r="V58" s="5"/>
       <c r="W58" s="5"/>
@@ -28784,7 +28894,9 @@
       <c r="Q59" s="5"/>
       <c r="R59" s="5"/>
       <c r="S59" s="5"/>
-      <c r="T59" s="5"/>
+      <c r="T59" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U59" s="5"/>
       <c r="V59" s="5"/>
       <c r="W59" s="5"/>
@@ -29240,7 +29352,9 @@
       <c r="Q60" s="5"/>
       <c r="R60" s="5"/>
       <c r="S60" s="5"/>
-      <c r="T60" s="5"/>
+      <c r="T60" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U60" s="5"/>
       <c r="V60" s="5"/>
       <c r="W60" s="5"/>
@@ -29696,7 +29810,9 @@
       <c r="Q61" s="5"/>
       <c r="R61" s="5"/>
       <c r="S61" s="5"/>
-      <c r="T61" s="5"/>
+      <c r="T61" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U61" s="5"/>
       <c r="V61" s="5"/>
       <c r="W61" s="5"/>
@@ -30152,7 +30268,9 @@
       <c r="Q62" s="5"/>
       <c r="R62" s="5"/>
       <c r="S62" s="5"/>
-      <c r="T62" s="5"/>
+      <c r="T62" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U62" s="5"/>
       <c r="V62" s="5"/>
       <c r="W62" s="5"/>
@@ -30608,7 +30726,9 @@
       <c r="Q63" s="5"/>
       <c r="R63" s="5"/>
       <c r="S63" s="5"/>
-      <c r="T63" s="5"/>
+      <c r="T63" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U63" s="5"/>
       <c r="V63" s="5"/>
       <c r="W63" s="5"/>
@@ -31064,7 +31184,9 @@
       <c r="Q64" s="5"/>
       <c r="R64" s="5"/>
       <c r="S64" s="5"/>
-      <c r="T64" s="5"/>
+      <c r="T64" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U64" s="5"/>
       <c r="V64" s="5"/>
       <c r="W64" s="5"/>
@@ -31520,7 +31642,9 @@
       <c r="Q65" s="5"/>
       <c r="R65" s="5"/>
       <c r="S65" s="5"/>
-      <c r="T65" s="5"/>
+      <c r="T65" s="5" t="n">
+        <v>620</v>
+      </c>
       <c r="U65" s="5"/>
       <c r="V65" s="5"/>
       <c r="W65" s="5"/>
@@ -31976,7 +32100,9 @@
       <c r="Q66" s="5"/>
       <c r="R66" s="5"/>
       <c r="S66" s="5"/>
-      <c r="T66" s="5"/>
+      <c r="T66" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U66" s="5"/>
       <c r="V66" s="5"/>
       <c r="W66" s="5"/>
@@ -32432,7 +32558,9 @@
       <c r="Q67" s="5"/>
       <c r="R67" s="5"/>
       <c r="S67" s="5"/>
-      <c r="T67" s="5"/>
+      <c r="T67" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U67" s="5"/>
       <c r="V67" s="5"/>
       <c r="W67" s="5"/>
@@ -32888,7 +33016,9 @@
       <c r="Q68" s="5"/>
       <c r="R68" s="5"/>
       <c r="S68" s="5"/>
-      <c r="T68" s="5"/>
+      <c r="T68" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="U68" s="5"/>
       <c r="V68" s="5"/>
       <c r="W68" s="5"/>

--- a/Part2_PlatformBenchmarks_Results_v1.0.0.xlsx
+++ b/Part2_PlatformBenchmarks_Results_v1.0.0.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1042" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="512">
   <si>
     <t xml:space="preserve">Arduino Benchmark Suite – Part 2: Platform Benchmarks</t>
   </si>
@@ -3729,7 +3729,9 @@
       <c r="AL4" s="5"/>
       <c r="AM4" s="5"/>
       <c r="AN4" s="5"/>
-      <c r="AO4" s="5"/>
+      <c r="AO4" s="5" t="n">
+        <v>12.38</v>
+      </c>
       <c r="AP4" s="5"/>
       <c r="AQ4" s="5"/>
       <c r="AR4" s="5"/>
@@ -4187,7 +4189,9 @@
       <c r="AL5" s="5"/>
       <c r="AM5" s="5"/>
       <c r="AN5" s="5"/>
-      <c r="AO5" s="5"/>
+      <c r="AO5" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP5" s="5"/>
       <c r="AQ5" s="5"/>
       <c r="AR5" s="5"/>
@@ -4645,7 +4649,9 @@
       <c r="AL6" s="5"/>
       <c r="AM6" s="5"/>
       <c r="AN6" s="5"/>
-      <c r="AO6" s="5"/>
+      <c r="AO6" s="5" t="n">
+        <v>73.86</v>
+      </c>
       <c r="AP6" s="5"/>
       <c r="AQ6" s="5"/>
       <c r="AR6" s="5"/>
@@ -5103,7 +5109,9 @@
       <c r="AL7" s="5"/>
       <c r="AM7" s="5"/>
       <c r="AN7" s="5"/>
-      <c r="AO7" s="5"/>
+      <c r="AO7" s="5" t="n">
+        <v>69.74</v>
+      </c>
       <c r="AP7" s="5"/>
       <c r="AQ7" s="5"/>
       <c r="AR7" s="5"/>
@@ -5561,7 +5569,9 @@
       <c r="AL8" s="5"/>
       <c r="AM8" s="5"/>
       <c r="AN8" s="5"/>
-      <c r="AO8" s="5"/>
+      <c r="AO8" s="5" t="n">
+        <v>53.59</v>
+      </c>
       <c r="AP8" s="5"/>
       <c r="AQ8" s="5"/>
       <c r="AR8" s="5"/>
@@ -6019,7 +6029,9 @@
       <c r="AL9" s="5"/>
       <c r="AM9" s="5"/>
       <c r="AN9" s="5"/>
-      <c r="AO9" s="5"/>
+      <c r="AO9" s="5" t="n">
+        <v>20.04</v>
+      </c>
       <c r="AP9" s="5"/>
       <c r="AQ9" s="5"/>
       <c r="AR9" s="5"/>
@@ -6477,7 +6489,9 @@
       <c r="AL10" s="5"/>
       <c r="AM10" s="5"/>
       <c r="AN10" s="5"/>
-      <c r="AO10" s="5"/>
+      <c r="AO10" s="5" t="n">
+        <v>55.07</v>
+      </c>
       <c r="AP10" s="5"/>
       <c r="AQ10" s="5"/>
       <c r="AR10" s="5"/>
@@ -6935,7 +6949,9 @@
       <c r="AL11" s="5"/>
       <c r="AM11" s="5"/>
       <c r="AN11" s="5"/>
-      <c r="AO11" s="5"/>
+      <c r="AO11" s="5" t="n">
+        <v>25.07</v>
+      </c>
       <c r="AP11" s="5"/>
       <c r="AQ11" s="5"/>
       <c r="AR11" s="5"/>
@@ -7393,7 +7409,9 @@
       <c r="AL12" s="5"/>
       <c r="AM12" s="5"/>
       <c r="AN12" s="5"/>
-      <c r="AO12" s="5"/>
+      <c r="AO12" s="5" t="n">
+        <v>26</v>
+      </c>
       <c r="AP12" s="5"/>
       <c r="AQ12" s="5"/>
       <c r="AR12" s="5"/>
@@ -7851,7 +7869,9 @@
       <c r="AL13" s="5"/>
       <c r="AM13" s="5"/>
       <c r="AN13" s="5"/>
-      <c r="AO13" s="5"/>
+      <c r="AO13" s="5" t="n">
+        <v>68.4</v>
+      </c>
       <c r="AP13" s="5"/>
       <c r="AQ13" s="5"/>
       <c r="AR13" s="5"/>
@@ -8309,7 +8329,9 @@
       <c r="AL14" s="5"/>
       <c r="AM14" s="5"/>
       <c r="AN14" s="5"/>
-      <c r="AO14" s="5"/>
+      <c r="AO14" s="5" t="n">
+        <v>1328.02</v>
+      </c>
       <c r="AP14" s="5"/>
       <c r="AQ14" s="5"/>
       <c r="AR14" s="5"/>
@@ -8767,7 +8789,9 @@
       <c r="AL15" s="5"/>
       <c r="AM15" s="5"/>
       <c r="AN15" s="5"/>
-      <c r="AO15" s="5"/>
+      <c r="AO15" s="5" t="n">
+        <v>13.93</v>
+      </c>
       <c r="AP15" s="5"/>
       <c r="AQ15" s="5"/>
       <c r="AR15" s="5"/>
@@ -9225,7 +9249,9 @@
       <c r="AL16" s="5"/>
       <c r="AM16" s="5"/>
       <c r="AN16" s="5"/>
-      <c r="AO16" s="5"/>
+      <c r="AO16" s="5" t="n">
+        <v>11.52</v>
+      </c>
       <c r="AP16" s="5"/>
       <c r="AQ16" s="5"/>
       <c r="AR16" s="5"/>
@@ -9683,7 +9709,9 @@
       <c r="AL17" s="5"/>
       <c r="AM17" s="5"/>
       <c r="AN17" s="5"/>
-      <c r="AO17" s="5"/>
+      <c r="AO17" s="5" t="n">
+        <v>82.72</v>
+      </c>
       <c r="AP17" s="5"/>
       <c r="AQ17" s="5"/>
       <c r="AR17" s="5"/>
@@ -10141,7 +10169,9 @@
       <c r="AL18" s="5"/>
       <c r="AM18" s="5"/>
       <c r="AN18" s="5"/>
-      <c r="AO18" s="5"/>
+      <c r="AO18" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="AP18" s="5"/>
       <c r="AQ18" s="5"/>
       <c r="AR18" s="5"/>
@@ -10599,7 +10629,9 @@
       <c r="AL19" s="5"/>
       <c r="AM19" s="5"/>
       <c r="AN19" s="5"/>
-      <c r="AO19" s="5"/>
+      <c r="AO19" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="AP19" s="5"/>
       <c r="AQ19" s="5"/>
       <c r="AR19" s="5"/>
@@ -11057,7 +11089,9 @@
       <c r="AL20" s="5"/>
       <c r="AM20" s="5"/>
       <c r="AN20" s="5"/>
-      <c r="AO20" s="5"/>
+      <c r="AO20" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="AP20" s="5"/>
       <c r="AQ20" s="5"/>
       <c r="AR20" s="5"/>
@@ -11515,7 +11549,9 @@
       <c r="AL21" s="5"/>
       <c r="AM21" s="5"/>
       <c r="AN21" s="5"/>
-      <c r="AO21" s="5"/>
+      <c r="AO21" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="AP21" s="5"/>
       <c r="AQ21" s="5"/>
       <c r="AR21" s="5"/>
@@ -11973,7 +12009,9 @@
       <c r="AL22" s="5"/>
       <c r="AM22" s="5"/>
       <c r="AN22" s="5"/>
-      <c r="AO22" s="5"/>
+      <c r="AO22" s="5" t="n">
+        <v>0.1</v>
+      </c>
       <c r="AP22" s="5"/>
       <c r="AQ22" s="5"/>
       <c r="AR22" s="5"/>
@@ -12431,7 +12469,9 @@
       <c r="AL23" s="5"/>
       <c r="AM23" s="5"/>
       <c r="AN23" s="5"/>
-      <c r="AO23" s="5"/>
+      <c r="AO23" s="5" t="n">
+        <v>161</v>
+      </c>
       <c r="AP23" s="5"/>
       <c r="AQ23" s="5"/>
       <c r="AR23" s="5"/>
@@ -12889,7 +12929,9 @@
       <c r="AL24" s="5"/>
       <c r="AM24" s="5"/>
       <c r="AN24" s="5"/>
-      <c r="AO24" s="5"/>
+      <c r="AO24" s="5" t="n">
+        <v>44</v>
+      </c>
       <c r="AP24" s="5"/>
       <c r="AQ24" s="5"/>
       <c r="AR24" s="5"/>
@@ -13347,7 +13389,9 @@
       <c r="AL25" s="5"/>
       <c r="AM25" s="5"/>
       <c r="AN25" s="5"/>
-      <c r="AO25" s="5"/>
+      <c r="AO25" s="5" t="n">
+        <v>1.17</v>
+      </c>
       <c r="AP25" s="5"/>
       <c r="AQ25" s="5"/>
       <c r="AR25" s="5"/>
@@ -13805,7 +13849,9 @@
       <c r="AL26" s="5"/>
       <c r="AM26" s="5"/>
       <c r="AN26" s="5"/>
-      <c r="AO26" s="5"/>
+      <c r="AO26" s="5" t="n">
+        <v>11.12</v>
+      </c>
       <c r="AP26" s="5"/>
       <c r="AQ26" s="5"/>
       <c r="AR26" s="5"/>
@@ -14263,7 +14309,9 @@
       <c r="AL27" s="5"/>
       <c r="AM27" s="5"/>
       <c r="AN27" s="5"/>
-      <c r="AO27" s="5"/>
+      <c r="AO27" s="5" t="n">
+        <v>25.11</v>
+      </c>
       <c r="AP27" s="5"/>
       <c r="AQ27" s="5"/>
       <c r="AR27" s="5"/>
@@ -14721,7 +14769,9 @@
       <c r="AL28" s="5"/>
       <c r="AM28" s="5"/>
       <c r="AN28" s="5"/>
-      <c r="AO28" s="5"/>
+      <c r="AO28" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP28" s="5"/>
       <c r="AQ28" s="5"/>
       <c r="AR28" s="5"/>
@@ -15179,7 +15229,9 @@
       <c r="AL29" s="5"/>
       <c r="AM29" s="5"/>
       <c r="AN29" s="5"/>
-      <c r="AO29" s="5"/>
+      <c r="AO29" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP29" s="5"/>
       <c r="AQ29" s="5"/>
       <c r="AR29" s="5"/>
@@ -15637,7 +15689,9 @@
       <c r="AL30" s="5"/>
       <c r="AM30" s="5"/>
       <c r="AN30" s="5"/>
-      <c r="AO30" s="5"/>
+      <c r="AO30" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP30" s="5"/>
       <c r="AQ30" s="5"/>
       <c r="AR30" s="5"/>
@@ -16095,7 +16149,9 @@
       <c r="AL31" s="5"/>
       <c r="AM31" s="5"/>
       <c r="AN31" s="5"/>
-      <c r="AO31" s="5"/>
+      <c r="AO31" s="5" t="n">
+        <v>8</v>
+      </c>
       <c r="AP31" s="5"/>
       <c r="AQ31" s="5"/>
       <c r="AR31" s="5"/>
@@ -16553,7 +16609,9 @@
       <c r="AL32" s="5"/>
       <c r="AM32" s="5"/>
       <c r="AN32" s="5"/>
-      <c r="AO32" s="5"/>
+      <c r="AO32" s="5" t="n">
+        <v>2000</v>
+      </c>
       <c r="AP32" s="5"/>
       <c r="AQ32" s="5"/>
       <c r="AR32" s="5"/>
@@ -17011,7 +17069,9 @@
       <c r="AL33" s="5"/>
       <c r="AM33" s="5"/>
       <c r="AN33" s="5"/>
-      <c r="AO33" s="5"/>
+      <c r="AO33" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP33" s="5"/>
       <c r="AQ33" s="5"/>
       <c r="AR33" s="5"/>
@@ -17469,7 +17529,9 @@
       <c r="AL34" s="5"/>
       <c r="AM34" s="5"/>
       <c r="AN34" s="5"/>
-      <c r="AO34" s="5"/>
+      <c r="AO34" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP34" s="5"/>
       <c r="AQ34" s="5"/>
       <c r="AR34" s="5"/>
@@ -17927,7 +17989,9 @@
       <c r="AL35" s="5"/>
       <c r="AM35" s="5"/>
       <c r="AN35" s="5"/>
-      <c r="AO35" s="5"/>
+      <c r="AO35" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP35" s="5"/>
       <c r="AQ35" s="5"/>
       <c r="AR35" s="5"/>
@@ -18385,7 +18449,9 @@
       <c r="AL36" s="5"/>
       <c r="AM36" s="5"/>
       <c r="AN36" s="5"/>
-      <c r="AO36" s="5"/>
+      <c r="AO36" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP36" s="5"/>
       <c r="AQ36" s="5"/>
       <c r="AR36" s="5"/>
@@ -18843,7 +18909,9 @@
       <c r="AL37" s="5"/>
       <c r="AM37" s="5"/>
       <c r="AN37" s="5"/>
-      <c r="AO37" s="5"/>
+      <c r="AO37" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP37" s="5"/>
       <c r="AQ37" s="5"/>
       <c r="AR37" s="5"/>
@@ -19301,7 +19369,9 @@
       <c r="AL38" s="5"/>
       <c r="AM38" s="5"/>
       <c r="AN38" s="5"/>
-      <c r="AO38" s="5"/>
+      <c r="AO38" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP38" s="5"/>
       <c r="AQ38" s="5"/>
       <c r="AR38" s="5"/>
@@ -19759,7 +19829,9 @@
       <c r="AL39" s="5"/>
       <c r="AM39" s="5"/>
       <c r="AN39" s="5"/>
-      <c r="AO39" s="5"/>
+      <c r="AO39" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP39" s="5"/>
       <c r="AQ39" s="5"/>
       <c r="AR39" s="5"/>
@@ -20217,7 +20289,9 @@
       <c r="AL40" s="5"/>
       <c r="AM40" s="5"/>
       <c r="AN40" s="5"/>
-      <c r="AO40" s="5"/>
+      <c r="AO40" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP40" s="5"/>
       <c r="AQ40" s="5"/>
       <c r="AR40" s="5"/>
@@ -20675,7 +20749,9 @@
       <c r="AL41" s="5"/>
       <c r="AM41" s="5"/>
       <c r="AN41" s="5"/>
-      <c r="AO41" s="5"/>
+      <c r="AO41" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP41" s="5"/>
       <c r="AQ41" s="5"/>
       <c r="AR41" s="5"/>
@@ -21133,7 +21209,9 @@
       <c r="AL42" s="5"/>
       <c r="AM42" s="5"/>
       <c r="AN42" s="5"/>
-      <c r="AO42" s="5"/>
+      <c r="AO42" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP42" s="5"/>
       <c r="AQ42" s="5"/>
       <c r="AR42" s="5"/>
@@ -21591,7 +21669,9 @@
       <c r="AL43" s="5"/>
       <c r="AM43" s="5"/>
       <c r="AN43" s="5"/>
-      <c r="AO43" s="5"/>
+      <c r="AO43" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP43" s="5"/>
       <c r="AQ43" s="5"/>
       <c r="AR43" s="5"/>
@@ -22049,7 +22129,9 @@
       <c r="AL44" s="5"/>
       <c r="AM44" s="5"/>
       <c r="AN44" s="5"/>
-      <c r="AO44" s="5"/>
+      <c r="AO44" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP44" s="5"/>
       <c r="AQ44" s="5"/>
       <c r="AR44" s="5"/>
@@ -22507,7 +22589,9 @@
       <c r="AL45" s="5"/>
       <c r="AM45" s="5"/>
       <c r="AN45" s="5"/>
-      <c r="AO45" s="5"/>
+      <c r="AO45" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP45" s="5"/>
       <c r="AQ45" s="5"/>
       <c r="AR45" s="5"/>
@@ -22965,7 +23049,9 @@
       <c r="AL46" s="5"/>
       <c r="AM46" s="5"/>
       <c r="AN46" s="5"/>
-      <c r="AO46" s="5"/>
+      <c r="AO46" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP46" s="5"/>
       <c r="AQ46" s="5"/>
       <c r="AR46" s="5"/>
@@ -23423,7 +23509,9 @@
       <c r="AL47" s="5"/>
       <c r="AM47" s="5"/>
       <c r="AN47" s="5"/>
-      <c r="AO47" s="5"/>
+      <c r="AO47" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP47" s="5"/>
       <c r="AQ47" s="5"/>
       <c r="AR47" s="5"/>
@@ -23881,7 +23969,9 @@
       <c r="AL48" s="5"/>
       <c r="AM48" s="5"/>
       <c r="AN48" s="5"/>
-      <c r="AO48" s="5"/>
+      <c r="AO48" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP48" s="5"/>
       <c r="AQ48" s="5"/>
       <c r="AR48" s="5"/>
@@ -24339,7 +24429,9 @@
       <c r="AL49" s="5"/>
       <c r="AM49" s="5"/>
       <c r="AN49" s="5"/>
-      <c r="AO49" s="5"/>
+      <c r="AO49" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP49" s="5"/>
       <c r="AQ49" s="5"/>
       <c r="AR49" s="5"/>
@@ -24797,7 +24889,9 @@
       <c r="AL50" s="5"/>
       <c r="AM50" s="5"/>
       <c r="AN50" s="5"/>
-      <c r="AO50" s="5"/>
+      <c r="AO50" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP50" s="5"/>
       <c r="AQ50" s="5"/>
       <c r="AR50" s="5"/>
@@ -25255,7 +25349,9 @@
       <c r="AL51" s="5"/>
       <c r="AM51" s="5"/>
       <c r="AN51" s="5"/>
-      <c r="AO51" s="5"/>
+      <c r="AO51" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP51" s="5"/>
       <c r="AQ51" s="5"/>
       <c r="AR51" s="5"/>
@@ -25713,7 +25809,9 @@
       <c r="AL52" s="5"/>
       <c r="AM52" s="5"/>
       <c r="AN52" s="5"/>
-      <c r="AO52" s="5"/>
+      <c r="AO52" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP52" s="5"/>
       <c r="AQ52" s="5"/>
       <c r="AR52" s="5"/>
@@ -26171,7 +26269,9 @@
       <c r="AL53" s="5"/>
       <c r="AM53" s="5"/>
       <c r="AN53" s="5"/>
-      <c r="AO53" s="5"/>
+      <c r="AO53" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP53" s="5"/>
       <c r="AQ53" s="5"/>
       <c r="AR53" s="5"/>
@@ -26629,7 +26729,9 @@
       <c r="AL54" s="5"/>
       <c r="AM54" s="5"/>
       <c r="AN54" s="5"/>
-      <c r="AO54" s="5"/>
+      <c r="AO54" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP54" s="5"/>
       <c r="AQ54" s="5"/>
       <c r="AR54" s="5"/>
@@ -27087,7 +27189,9 @@
       <c r="AL55" s="5"/>
       <c r="AM55" s="5"/>
       <c r="AN55" s="5"/>
-      <c r="AO55" s="5"/>
+      <c r="AO55" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP55" s="5"/>
       <c r="AQ55" s="5"/>
       <c r="AR55" s="5"/>
@@ -27545,7 +27649,9 @@
       <c r="AL56" s="5"/>
       <c r="AM56" s="5"/>
       <c r="AN56" s="5"/>
-      <c r="AO56" s="5"/>
+      <c r="AO56" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP56" s="5"/>
       <c r="AQ56" s="5"/>
       <c r="AR56" s="5"/>
@@ -28003,7 +28109,9 @@
       <c r="AL57" s="5"/>
       <c r="AM57" s="5"/>
       <c r="AN57" s="5"/>
-      <c r="AO57" s="5"/>
+      <c r="AO57" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP57" s="5"/>
       <c r="AQ57" s="5"/>
       <c r="AR57" s="5"/>
@@ -28461,7 +28569,9 @@
       <c r="AL58" s="5"/>
       <c r="AM58" s="5"/>
       <c r="AN58" s="5"/>
-      <c r="AO58" s="5"/>
+      <c r="AO58" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP58" s="5"/>
       <c r="AQ58" s="5"/>
       <c r="AR58" s="5"/>
@@ -28919,7 +29029,9 @@
       <c r="AL59" s="5"/>
       <c r="AM59" s="5"/>
       <c r="AN59" s="5"/>
-      <c r="AO59" s="5"/>
+      <c r="AO59" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP59" s="5"/>
       <c r="AQ59" s="5"/>
       <c r="AR59" s="5"/>
@@ -29377,7 +29489,9 @@
       <c r="AL60" s="5"/>
       <c r="AM60" s="5"/>
       <c r="AN60" s="5"/>
-      <c r="AO60" s="5"/>
+      <c r="AO60" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP60" s="5"/>
       <c r="AQ60" s="5"/>
       <c r="AR60" s="5"/>
@@ -29835,7 +29949,9 @@
       <c r="AL61" s="5"/>
       <c r="AM61" s="5"/>
       <c r="AN61" s="5"/>
-      <c r="AO61" s="5"/>
+      <c r="AO61" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP61" s="5"/>
       <c r="AQ61" s="5"/>
       <c r="AR61" s="5"/>
@@ -30293,7 +30409,9 @@
       <c r="AL62" s="5"/>
       <c r="AM62" s="5"/>
       <c r="AN62" s="5"/>
-      <c r="AO62" s="5"/>
+      <c r="AO62" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP62" s="5"/>
       <c r="AQ62" s="5"/>
       <c r="AR62" s="5"/>
@@ -30751,7 +30869,9 @@
       <c r="AL63" s="5"/>
       <c r="AM63" s="5"/>
       <c r="AN63" s="5"/>
-      <c r="AO63" s="5"/>
+      <c r="AO63" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP63" s="5"/>
       <c r="AQ63" s="5"/>
       <c r="AR63" s="5"/>
@@ -31209,7 +31329,9 @@
       <c r="AL64" s="5"/>
       <c r="AM64" s="5"/>
       <c r="AN64" s="5"/>
-      <c r="AO64" s="5"/>
+      <c r="AO64" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP64" s="5"/>
       <c r="AQ64" s="5"/>
       <c r="AR64" s="5"/>
@@ -31667,7 +31789,9 @@
       <c r="AL65" s="5"/>
       <c r="AM65" s="5"/>
       <c r="AN65" s="5"/>
-      <c r="AO65" s="5"/>
+      <c r="AO65" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP65" s="5"/>
       <c r="AQ65" s="5"/>
       <c r="AR65" s="5"/>
@@ -32125,7 +32249,9 @@
       <c r="AL66" s="5"/>
       <c r="AM66" s="5"/>
       <c r="AN66" s="5"/>
-      <c r="AO66" s="5"/>
+      <c r="AO66" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP66" s="5"/>
       <c r="AQ66" s="5"/>
       <c r="AR66" s="5"/>
@@ -32583,7 +32709,9 @@
       <c r="AL67" s="5"/>
       <c r="AM67" s="5"/>
       <c r="AN67" s="5"/>
-      <c r="AO67" s="5"/>
+      <c r="AO67" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP67" s="5"/>
       <c r="AQ67" s="5"/>
       <c r="AR67" s="5"/>
@@ -33041,7 +33169,9 @@
       <c r="AL68" s="5"/>
       <c r="AM68" s="5"/>
       <c r="AN68" s="5"/>
-      <c r="AO68" s="5"/>
+      <c r="AO68" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AP68" s="5"/>
       <c r="AQ68" s="5"/>
       <c r="AR68" s="5"/>
